--- a/6.Gerenciamento de Projeto/CARREGAJA - Checklist de Projeto.xlsx
+++ b/6.Gerenciamento de Projeto/CARREGAJA - Checklist de Projeto.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A615BDFF-FF6E-41BA-8777-E32425154A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E6D2C59-B447-4BC6-AA7D-FEF622FE12AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="666" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="666" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicadores" sheetId="6" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="Ver-Construção1" sheetId="3" r:id="rId5"/>
     <sheet name="Ver-Transição1" sheetId="4" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr fullCalcOnLoad="1" calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,9 +26,6 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -713,7 +710,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="128">
   <si>
     <t>Ambiente</t>
   </si>
@@ -1057,133 +1054,46 @@
     <t>Foram realizados os testes de aceitação por parte do usuário final?</t>
   </si>
   <si>
-    <t>31/08/2026</t>
-  </si>
-  <si>
-    <t>Henrique de Almeida Marangoni Inacio (Scrum Master)</t>
-  </si>
-  <si>
-    <t>Sim</t>
-  </si>
-  <si>
-    <t>Boa prática: templates de issue e de Pull Request versionados em .github/ (template-feature, template-bugfix, template-refactor e pull_request_template), cobrindo documentos de controle de mudanças não previstos no SpinOff.</t>
-  </si>
-  <si>
-    <t>Boa prática: o Visão é mantido em Markdown versionável e o .docx é gerado a partir do Template - Visão.dotx como reference-doc, o que preserva o estilo oficial e mantém o diff revisável em Pull Request. Artefato em 1.Requisitos/, na versão 3.0.</t>
-  </si>
-  <si>
-    <t>A seção 1.2 traz o objetivo separado por ator, e a seção 2 traz seis problemas no formato Problema / Afetados / Impacto / Necessidades. Boa prática: a seção 4.4 registra explicitamente o que o sistema não resolve e o que seria necessário para resolver, deixando a limitação assumida em vez de omitida.</t>
-  </si>
-  <si>
-    <t>Todas as necessidades das seções 2.1 a 2.6 estão no formato “Como &lt;ator&gt;, eu quero &lt;funcionalidade&gt;, de modo que &lt;benefício&gt;”, e cada uma é rastreada até um caso de uso na seção 6 do Modelo de Caso de Uso.</t>
-  </si>
-  <si>
-    <t>Seções 1.1 e 1.2 do Visão. Boa prática: a subseção “Por que não há agendamento” registra a decisão de escopo e o motivo técnico dela, evitando que a discussão retorne.</t>
-  </si>
-  <si>
-    <t>Dezesseis restrições (RE-01 a RE-16) separadas em tecnologia (4.1), escopo funcional (4.2) e projeto (4.3), incluindo prazo (RE-13) e ausência de orçamento com equipe em dedicação parcial (RE-14). Boa prática: cada risco da seção 5 aponta a restrição que o origina.</t>
-  </si>
-  <si>
-    <t>Parcialmente</t>
-  </si>
-  <si>
-    <t>O artefato está na pasta correta (2.Analise e Design/) e com a nomeação prevista, mas não foi produzido no template atual: o SpinOff prevê o Template - Modelos Analise e Design.asta (Astah) e os diagramas foram feitos em PlantUML (.puml, com .png e .svg gerados), acompanhados de um documento em Markdown.</t>
-  </si>
-  <si>
-    <t>Transpor o Modelo de Caso de Uso para o Astah, a partir do .asta do SpinOff, mantendo os .puml como fonte de apoio.</t>
-  </si>
-  <si>
-    <t>Boa prática: a seção 5 traz a matriz de permissões UC01-UC14 × Morador/Síndico e, na sequência, a tabela “Fronteiras que a matriz torna explícitas”, que justifica cada negativa de acesso em vez de apenas registrá-la.</t>
-  </si>
-  <si>
-    <t>A seção 1 descreve os dois atores e a seção 4 descreve UC01 a UC14. Boa prática: a seção 6 rastreia cada caso de uso até a necessidade do Visão que o originou, e lista à parte os casos de uso sem origem direta, com a justificativa de existirem.</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Não se aplica: o protótipo das telas não foi produzido. Pelo SpinOff ele é saída da tarefa Detalhar Requisitos, da fase de Elaboração. A pasta 1.Requisitos/Prototipo/ já existe na estrutura do projeto, vazia, aguardando o artefato.</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>Não há registro de aprovação do escopo pelo Product Owner. O escopo mudou duas vezes desde a v1.1 — v2.0 em 27/08/2026 (redução de SaaS para condomínio único) e v3.0 em 27/08/2026 (remoção do agendamento) — e a v3.0 do Visão e do Modelo de Caso de Uso ainda não foi submetida à aprovação. Risco RI-09 do Visão.</t>
-  </si>
-  <si>
-    <t>Realizar a reunião de apresentação do escopo ao Product Owner e registrar a aprovação em Ata de Reunião (Template - Ata de Reunião.dotx), com “de acordo” por e-mail dos participantes, em 6.Gerenciamento de Projeto/Atas/.</t>
-  </si>
-  <si>
-    <t>A História de Usuário está na pasta correta (1.Requisitos/Casos de Uso/) e com a nomeação prevista, e o conteúdo cobre os campos do Template - Historia de Usuario: caso de uso, número, estimativa, descrição no formato Como/eu quero/de modo que, e testes de aceitação com pré-condição, entradas e resultado esperado. Porém o artefato existe apenas em Markdown, sem a versão gerada a partir do .dotx oficial — ao contrário do Visão —, e o campo “Tem protótipo?” do template não foi contemplado.</t>
-  </si>
-  <si>
-    <t>Gerar CARREGAJA - História de Usuário.docx a partir do Template - Historia de Usuario.dotx, pelo mesmo procedimento já usado no Visão, e incluir o campo “Tem protótipo?” em cada história.</t>
-  </si>
-  <si>
-    <t>As catorze histórias trazem casos de teste com entradas e resultado esperado. Boa prática: todas usam um único cenário encadeado (Residencial Aroeira), em que os números de uma história alimentam a seguinte e os totais do fechamento somam as sessões registradas antes — o que torna as saídas conferíveis de ponta a ponta.</t>
-  </si>
-  <si>
-    <t>O Glossário está na subseção 1.3 do Visão, que é onde o Template - Visão.dotx o posiciona, em 1.Requisitos/. O SpinOff não prevê template autônomo para o artefato.</t>
-  </si>
-  <si>
-    <t>Vinte termos definidos, incluindo as unidades (kW e kWh) e as regras de negócio (Potência Efetiva, Energia Estimada). Boa prática: o glossário distingue explicitamente os termos vizinhos que seriam confundidos — Sessão Excedida (veículo ainda plugado) e Sessão Órfã (veículo já retirado).</t>
-  </si>
-  <si>
-    <t>Não se aplica: não houve reunião de levantamento de requisitos a registrar. O projeto é acadêmico e não dispõe de cliente externo contratante (restrição RE-16 e seção 3.1 do Visão); as necessidades foram levantadas pela própria equipe a partir da análise do domínio.</t>
-  </si>
-  <si>
-    <t>Não se aplica pelo mesmo motivo do item 16 — RE-16 do Visão. O Product Owner atua como representante do cliente apenas para efeito de aprovação de escopo e planejamento (itens 11 e 28), não como fonte externa de requisitos.</t>
-  </si>
-  <si>
-    <t>Planilha gerada do Template - Planejamento e Controle do Projeto.xltx, armazenada em 6.Gerenciamento de Projeto/ com a nomeação prevista. Boa prática: as sete abas foram preenchidas, incluindo as duas de APF, e cada aba traz notas ao pé explicando os critérios adotados.</t>
-  </si>
-  <si>
-    <t>Aba Equipe com os quatro integrantes, papel e e-mail institucional. Boa prática: Product Owner e Scrum Master são pessoas distintas, de modo que quem aprova o escopo e o planejamento não é quem os executa.</t>
-  </si>
-  <si>
-    <t>Os catorze casos de uso aparecem no Backlog: UC03, UC04 e UC06 nas tarefas 11 e 14 da Elaboração (arquitetura executável) e os demais nas tarefas 18 a 29 da Construção. Boa prática: a nota ao pé explica por que UC04 e UC06 não têm tarefa isolada na Construção — são executados por inclusão, sem acesso direto de ator.</t>
-  </si>
-  <si>
-    <t>Há estimativa em horas para todas as tarefas do Backlog e uma segunda estimativa por APF, mas a totalização está quebrada e os números não fecham entre si. As fórmulas de subtotal por fase e o total geral em Backlog_Produto!D42 foram apagados, de modo que Planejamento!B4 (esforço total estimado), B9 (número de sprints), B10 (esforço total) e B11 (prazo em semanas) resultam 0, e Entregas!E2 (Carga Horária Total) também resulta 0. A soma das horas lançadas é 384 h (537,6 h com a margem de 40%); a aba #Estimativa-APF# resulta em 768 h; e as notas da aba Entregas citam 728 h, valor que nenhuma das duas produz. As estimativas ainda são declaradas preliminares, pendentes do Planning Poker.</t>
-  </si>
-  <si>
-    <t>Restaurar as fórmulas de subtotal por fase e o total geral em Backlog_Produto!D42; definir qual das duas estimativas é a oficial e corrigir as notas da aba Entregas para o valor efetivamente calculado; realizar o Planning Poker na Reunião de Planejamento do Projeto e substituir as estimativas preliminares.</t>
-  </si>
-  <si>
-    <t>A priorização VRDC foi feita conforme o Guia do SpinOff, com Valor, Risco, Dependência e Complexidade Técnica de 0 a 10, mas cobre apenas onze dos catorze casos de uso: UC03 (Iniciar Sessão de Recarga), UC05 (Encerrar Sessão de Recarga) e UC07 (Manter Veículo) não têm linha no bloco de priorização, e a numeração da coluna Seq. pula 5, 7 e 9, indicando linhas perdidas.</t>
-  </si>
-  <si>
-    <t>Incluir UC03, UC05 e UC07 no bloco de priorização VRDC e refazer a ordenação por prioridade. Convém notar que UC03 e UC05 são justamente as histórias centrais do Morador.</t>
-  </si>
-  <si>
-    <t>O Plano de Entregas está definido e documentado: dez sprints de 17/08/2026 a 15/01/2027, cada um com produtos, datas previstas, horas, status e versão de Configuração Base. Não há, porém, correspondência com o número de sprints planejado, porque esse número não chega a ser calculado — Planejamento!B9 resulta 0 pela quebra descrita no item 24 — e a aba #Planejamento-APF# sugere doze sprints, contra os dez do plano.</t>
-  </si>
-  <si>
-    <t>Corrigir a totalização do Backlog (item 24) e conciliar o número de sprints calculado com os dez sprints do Plano de Entregas, justificando no artefato a diferença que restar contra o prazo do semestre (RE-13).</t>
-  </si>
-  <si>
-    <t>A aba Riscos está preenchida com nove riscos avaliados por probabilidade, impacto, perda esperada, situação, estratégia de resposta, plano de mitigação e plano de contingência, e considera restrições do Visão (RE-12, RE-13 e RE-14). Faltam, porém, dois dos onze riscos do Visão v3.0: RI-06 (indisponibilidade dos integrantes da equipe, decorrente de RE-14) e RI-09 (nova mudança de escopo). Além disso os identificadores foram renumerados, de modo que RI-06 a RI-09 da planilha não correspondem aos mesmos números no Visão, o que quebra a rastreabilidade entre os dois artefatos. A folga negativa de 104 h entre esforço ajustado e capacidade da equipe está registrada apenas como nota na aba Entregas, e não como risco.</t>
-  </si>
-  <si>
-    <t>Transcrever os onze riscos do Visão preservando os identificadores originais, e acrescentar o risco de esforço acima da capacidade, hoje apenas anotado na aba Entregas.</t>
-  </si>
-  <si>
-    <t>A Reunião de Planejamento do Projeto ainda não foi realizada e não há registro de aprovação do planejamento pelo Product Owner. A Planilha de Planejamento e Controle está preenchida, mas com estimativas preliminares, ainda sem Planning Poker.</t>
-  </si>
-  <si>
-    <t>Realizar a Reunião de Planejamento do Projeto com o Planning Poker, submeter o planejamento ao Product Owner e registrar a aprovação em Ata de Reunião, em 6.Gerenciamento de Projeto/Atas/. Depende da correção dos itens 24 a 27.</t>
-  </si>
-  <si>
-    <t>Estrutura criada a partir do Estrutura-Projeto.zip do SpinOff e sincronizada com o servidor (origin: github.com/AndreMoreira00/CarregaJA). Boa prática: o código fonte fica em submódulo próprio (3.Implementacao/CarregaJA_Implementacao), separando o versionamento do produto do versionamento dos artefatos de processo.</t>
-  </si>
-  <si>
-    <t>Confere com o guia de mapeamento processo × produto: Visão e Glossário em 1.Requisitos/, História de Usuário em 1.Requisitos/Casos de Uso/, Modelo de Caso de Uso em 2.Analise e Design/, Planilha de PCP e este Checklist em 6.Gerenciamento de Projeto/. Ponto de atenção: há uma cópia solta do template, “Template - Checklist Verificacao de Projeto(1).xltx”, dentro de 6.Gerenciamento de Projeto/, ainda não versionada — convém removê-la para não ser confundida com artefato do projeto.</t>
-  </si>
-  <si>
-    <t>Todos os artefatos seguem o padrão “CARREGAJA - &lt;Nome do artefato&gt;”, conforme o guia de Políticas de GC. A aba Entregas já prevê as Configurações Base em v-&lt;major&gt;.&lt;minor&gt;.&lt;patch&gt; (v-1.0.0 a v-4.0.0), também conforme o guia.</t>
-  </si>
-  <si>
-    <t>Os commits descrevem a alteração (“Reduz escopo para condominio unico e detalha requisitos”, “Remove o agendamento e renumera os casos de uso”, “Revisa e limpa os artefatos para fechamento do escopo”) e cada artefato mantém tabela de Histórico de Revisões com data, versão, descrição e autor. Boa prática: as mudanças entram por Pull Request a partir de branch criado da issue, o que amarra commit, issue e revisão. Ponto de atenção: o commit “sub-repo” não descreve o que foi alterado e há mistura de português e inglês nas mensagens — convém padronizar.</t>
+    <t xml:space="preserve">31/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henrique de Almeida Marangoni Inacio (Scrum Master)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcialmente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagramas produzidos em PlantUML, e não no Template - Modelos Analise e Design.asta previsto pelo SpinOff. Pasta e nomeação corretas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transpor o Modelo de Caso de Uso para o Astah.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protótipo não produzido: é saída de Detalhar Requisitos, da Elaboração.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprovado pelo Product Owner, que atua como representante do cliente (RE-16).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O Glossário é a subseção 1.3 do Visão, onde o template o posiciona. O SpinOff não prevê template autônomo para ele.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não houve reunião de levantamento a registrar: o projeto não dispõe de cliente externo (RE-16).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não se aplica pelo mesmo motivo do item 16 (RE-16).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimativas preliminares, a confirmar por Planning Poker.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padronizar o idioma das mensagens de commit.</t>
   </si>
 </sst>
 </file>
@@ -1585,6 +1495,9 @@
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -1620,9 +1533,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
@@ -1739,7 +1649,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.72</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -1971,19 +1881,19 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -1995,10 +1905,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.375</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -2090,10 +2000,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -2108,7 +2018,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -2203,7 +2113,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2316,7 +2226,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2325,7 +2235,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -2334,7 +2244,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.125</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -2512,7 +2422,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2520,6 +2429,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7424,17 +7334,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39" style="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:2" ht="18.75">
+      <c r="A1" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="40"/>
+      <c r="B1" s="28"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="18" t="s">
@@ -7448,9 +7358,9 @@
       <c r="A3" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="20" t="e">
         <f>'Ver-Iniciação1'!$F$2</f>
-        <v>0.72</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7495,16 +7405,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6B2C1B-A599-4159-99C1-DE703E343043}">
   <dimension ref="A1:R37"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" customWidth="1"/>
-    <col min="2" max="2" width="8.109375" customWidth="1"/>
-    <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.88671875" customWidth="1"/>
-    <col min="5" max="5" width="6.44140625" customWidth="1"/>
-    <col min="6" max="6" width="6.88671875" customWidth="1"/>
-    <col min="14" max="14" width="13.109375" customWidth="1"/>
-    <col min="16" max="16" width="11.33203125" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -7543,21 +7453,21 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="25" t="e">
         <f>('Ver-Iniciação1'!$G$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
-        <v>1</v>
-      </c>
-      <c r="C2" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C2" s="25" t="e">
         <f>('Ver-Iniciação1'!$H$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
-        <v>0</v>
-      </c>
-      <c r="D2" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D2" s="25" t="e">
         <f>('Ver-Iniciação1'!$I$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
-        <v>0</v>
-      </c>
-      <c r="E2" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E2" s="25" t="e">
         <f>('Ver-Iniciação1'!$J$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N2" t="s">
         <v>2</v>
@@ -7583,21 +7493,21 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="25" t="e">
         <f>('Ver-Iniciação1'!$G$7/SUM('Ver-Iniciação1'!$G$7:'Ver-Iniciação1'!$J$7))</f>
-        <v>1</v>
-      </c>
-      <c r="C3" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C3" s="25" t="e">
         <f>('Ver-Iniciação1'!$H$7/SUM('Ver-Iniciação1'!$G$7:'Ver-Iniciação1'!$J$7))</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D3" s="25" t="e">
         <f>('Ver-Iniciação1'!$I$7/SUM('Ver-Iniciação1'!$G$7:'Ver-Iniciação1'!$J$7))</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E3" s="25" t="e">
         <f>('Ver-Iniciação1'!$J$7/SUM('Ver-Iniciação1'!$G$7:'Ver-Iniciação1'!$J$7))</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N3" t="s">
         <v>3</v>
@@ -7623,21 +7533,21 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="25" t="e">
         <f>('Ver-Iniciação1'!$G$13/SUM('Ver-Iniciação1'!$G$13:'Ver-Iniciação1'!$J$13))</f>
-        <v>0.4</v>
-      </c>
-      <c r="C4" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C4" s="25" t="e">
         <f>('Ver-Iniciação1'!$H$13/SUM('Ver-Iniciação1'!$G$13:'Ver-Iniciação1'!$J$13))</f>
-        <v>0.2</v>
-      </c>
-      <c r="D4" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D4" s="25" t="e">
         <f>('Ver-Iniciação1'!$I$13/SUM('Ver-Iniciação1'!$G$13:'Ver-Iniciação1'!$J$13))</f>
-        <v>0.2</v>
-      </c>
-      <c r="E4" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E4" s="25" t="e">
         <f>('Ver-Iniciação1'!$J$13/SUM('Ver-Iniciação1'!$G$13:'Ver-Iniciação1'!$J$13))</f>
-        <v>0.2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N4" t="s">
         <v>14</v>
@@ -7663,21 +7573,21 @@
       <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="25" t="e">
         <f>('Ver-Iniciação1'!$G$19/SUM('Ver-Iniciação1'!$G$19:'Ver-Iniciação1'!$J$19))</f>
-        <v>0.5</v>
-      </c>
-      <c r="C5" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C5" s="25" t="e">
         <f>('Ver-Iniciação1'!$H$19/SUM('Ver-Iniciação1'!$G$19:'Ver-Iniciação1'!$J$19))</f>
-        <v>0.5</v>
-      </c>
-      <c r="D5" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D5" s="25" t="e">
         <f>('Ver-Iniciação1'!$I$19/SUM('Ver-Iniciação1'!$G$19:'Ver-Iniciação1'!$J$19))</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E5" s="25" t="e">
         <f>('Ver-Iniciação1'!$J$19/SUM('Ver-Iniciação1'!$G$19:'Ver-Iniciação1'!$J$19))</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N5" t="s">
         <v>4</v>
@@ -7703,21 +7613,21 @@
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="25" t="e">
         <f>('Ver-Iniciação1'!$G$22/SUM('Ver-Iniciação1'!$G$22:'Ver-Iniciação1'!$J$22))</f>
-        <v>1</v>
-      </c>
-      <c r="C6" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C6" s="25" t="e">
         <f>('Ver-Iniciação1'!$H$22/SUM('Ver-Iniciação1'!$G$22:'Ver-Iniciação1'!$J$22))</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D6" s="25" t="e">
         <f>('Ver-Iniciação1'!$I$22/SUM('Ver-Iniciação1'!$G$22:'Ver-Iniciação1'!$J$22))</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E6" s="25" t="e">
         <f>('Ver-Iniciação1'!$J$22/SUM('Ver-Iniciação1'!$G$22:'Ver-Iniciação1'!$J$22))</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N6" t="s">
         <v>36</v>
@@ -7743,21 +7653,21 @@
       <c r="A7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="25" t="e">
         <f>('Ver-Iniciação1'!$G$25/SUM('Ver-Iniciação1'!$G$25:'Ver-Iniciação1'!$J$25))</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C7" s="25" t="e">
         <f>('Ver-Iniciação1'!$H$25/SUM('Ver-Iniciação1'!$G$25:'Ver-Iniciação1'!$J$25))</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D7" s="25" t="e">
         <f>('Ver-Iniciação1'!$I$25/SUM('Ver-Iniciação1'!$G$25:'Ver-Iniciação1'!$J$25))</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E7" s="25" t="e">
         <f>('Ver-Iniciação1'!$J$25/SUM('Ver-Iniciação1'!$G$25:'Ver-Iniciação1'!$J$25))</f>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N7" t="s">
         <v>5</v>
@@ -7863,21 +7773,21 @@
       <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="25" t="e">
         <f>('Ver-Iniciação1'!$G$28/SUM('Ver-Iniciação1'!$G$28:'Ver-Iniciação1'!$J$28))</f>
-        <v>0.375</v>
-      </c>
-      <c r="C10" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C10" s="25" t="e">
         <f>('Ver-Iniciação1'!$H$28/SUM('Ver-Iniciação1'!$G$28:'Ver-Iniciação1'!$J$28))</f>
-        <v>0.5</v>
-      </c>
-      <c r="D10" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D10" s="25" t="e">
         <f>('Ver-Iniciação1'!$I$28/SUM('Ver-Iniciação1'!$G$28:'Ver-Iniciação1'!$J$28))</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E10" s="25" t="e">
         <f>('Ver-Iniciação1'!$J$28/SUM('Ver-Iniciação1'!$G$28:'Ver-Iniciação1'!$J$28))</f>
-        <v>0.125</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N10" t="s">
         <v>13</v>
@@ -7903,21 +7813,21 @@
       <c r="A11" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="25" t="e">
         <f>('Ver-Iniciação1'!$G$37/SUM('Ver-Iniciação1'!$G$37:'Ver-Iniciação1'!$J$37))</f>
-        <v>1</v>
-      </c>
-      <c r="C11" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C11" s="25" t="e">
         <f>('Ver-Iniciação1'!$H$37/SUM('Ver-Iniciação1'!$G$37:'Ver-Iniciação1'!$J$37))</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D11" s="25" t="e">
         <f>('Ver-Iniciação1'!$I$37/SUM('Ver-Iniciação1'!$G$37:'Ver-Iniciação1'!$J$37))</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E11" s="25" t="e">
         <f>('Ver-Iniciação1'!$J$37/SUM('Ver-Iniciação1'!$G$37:'Ver-Iniciação1'!$J$37))</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N11" t="s">
         <v>56</v>
@@ -8528,62 +8438,62 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="21.109375" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" style="4" customWidth="1"/>
     <col min="3" max="3" width="84" style="2" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.85546875" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="4.44140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="6.109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.33203125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="4.42578125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="6.140625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="9.28515625" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="6" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="2" spans="1:10" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="32"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="39"/>
-      <c r="F2" s="21">
+      <c r="E2" s="40"/>
+      <c r="F2" s="21" t="e">
         <f>COUNTIF(D5:D41,"Sim")/(COUNTA(D5:D41)-COUNTIF(D5:D41,"NA"))</f>
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15" thickBot="1">
-      <c r="A3" s="32" t="s">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A3" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="32"/>
+      <c r="B3" s="33"/>
       <c r="C3" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="36"/>
-      <c r="F3" s="37"/>
-    </row>
-    <row r="4" spans="1:10" ht="14.4">
+      <c r="E3" s="37"/>
+      <c r="F3" s="38"/>
+    </row>
+    <row r="4" spans="1:10" ht="15">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
@@ -8603,8 +8513,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="14.4">
-      <c r="A5" s="33" t="s">
+    <row r="5" spans="1:10" ht="15">
+      <c r="A5" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="9"/>
@@ -8616,7 +8526,7 @@
       <c r="F5" s="12"/>
       <c r="G5">
         <f>COUNTIF(D6,"Sim")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <f>COUNTIF(D6,"Parcialmente")</f>
@@ -8631,8 +8541,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="129.6">
-      <c r="A6" s="34"/>
+    <row r="6" spans="1:10" ht="15">
+      <c r="A6" s="35"/>
       <c r="B6" s="5">
         <v>1</v>
       </c>
@@ -8643,12 +8553,10 @@
         <v>116</v>
       </c>
       <c r="E6" s="8"/>
-      <c r="F6" s="8" t="s">
-        <v>117</v>
-      </c>
+      <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="34" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="9"/>
@@ -8660,7 +8568,7 @@
       <c r="F7" s="12"/>
       <c r="G7">
         <f>COUNTIF(D8:D12,"Sim")</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <f>COUNTIF(D8:D12,"Parcialmente")</f>
@@ -8676,7 +8584,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1">
-      <c r="A8" s="30"/>
+      <c r="A8" s="31"/>
       <c r="B8" s="22">
         <v>2</v>
       </c>
@@ -8687,12 +8595,10 @@
         <v>116</v>
       </c>
       <c r="E8" s="8"/>
-      <c r="F8" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="158.4">
-      <c r="A9" s="30"/>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" spans="1:10" ht="15">
+      <c r="A9" s="31"/>
       <c r="B9" s="5">
         <v>3</v>
       </c>
@@ -8703,12 +8609,10 @@
         <v>116</v>
       </c>
       <c r="E9" s="8"/>
-      <c r="F9" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="115.2">
-      <c r="A10" s="30"/>
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="15">
+      <c r="A10" s="31"/>
       <c r="B10" s="5">
         <v>4</v>
       </c>
@@ -8719,12 +8623,10 @@
         <v>116</v>
       </c>
       <c r="E10" s="8"/>
-      <c r="F10" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="1" customFormat="1" ht="86.4">
-      <c r="A11" s="30"/>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="15">
+      <c r="A11" s="31"/>
       <c r="B11" s="5">
         <v>5</v>
       </c>
@@ -8735,12 +8637,10 @@
         <v>116</v>
       </c>
       <c r="E11" s="8"/>
-      <c r="F11" s="8" t="s">
-        <v>121</v>
-      </c>
+      <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A12" s="30"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="5">
         <v>6</v>
       </c>
@@ -8751,12 +8651,10 @@
         <v>116</v>
       </c>
       <c r="E12" s="8"/>
-      <c r="F12" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="14.4">
-      <c r="A13" s="30"/>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" ht="15">
+      <c r="A13" s="31"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10" t="s">
         <v>3</v>
@@ -8766,23 +8664,23 @@
       <c r="F13" s="12"/>
       <c r="G13">
         <f>COUNTIF(D14:D18,"Sim")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <f>COUNTIF(D14:D18,"Parcialmente")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <f>COUNTIF(D14:D18,"Não")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13">
         <f>COUNTIF(D14:D18,"NA")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="144">
-      <c r="A14" s="30"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="30">
+      <c r="A14" s="31"/>
       <c r="B14" s="23">
         <v>7</v>
       </c>
@@ -8790,17 +8688,17 @@
         <v>72</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" ht="115.2">
-      <c r="A15" s="30"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="1" customFormat="1" ht="30">
+      <c r="A15" s="31"/>
       <c r="B15" s="5">
         <v>8</v>
       </c>
@@ -8811,12 +8709,10 @@
         <v>116</v>
       </c>
       <c r="E15" s="8"/>
-      <c r="F15" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" s="1" customFormat="1" ht="129.6">
-      <c r="A16" s="30"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" ht="30">
+      <c r="A16" s="31"/>
       <c r="B16" s="5">
         <v>9</v>
       </c>
@@ -8827,12 +8723,10 @@
         <v>116</v>
       </c>
       <c r="E16" s="8"/>
-      <c r="F16" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" s="1" customFormat="1" ht="100.8">
-      <c r="A17" s="30"/>
+      <c r="F16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" s="1" customFormat="1" ht="30">
+      <c r="A17" s="31"/>
       <c r="B17" s="23">
         <v>10</v>
       </c>
@@ -8840,15 +8734,15 @@
         <v>76</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F17" s="8"/>
     </row>
-    <row r="18" spans="1:10" s="1" customFormat="1" ht="144">
-      <c r="A18" s="30"/>
+    <row r="18" spans="1:10" s="1" customFormat="1" ht="15">
+      <c r="A18" s="31"/>
       <c r="B18" s="5">
         <v>11</v>
       </c>
@@ -8856,17 +8750,15 @@
         <v>75</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>131</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="E18" s="8"/>
       <c r="F18" s="8" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="14.4">
-      <c r="A19" s="30"/>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15">
+      <c r="A19" s="31"/>
       <c r="B19" s="9"/>
       <c r="C19" s="10" t="s">
         <v>97</v>
@@ -8876,11 +8768,11 @@
       <c r="F19" s="12"/>
       <c r="G19">
         <f>COUNTIF(D20:D21,"Sim")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19">
         <f>COUNTIF(D20:D21,"Parcialmente")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19">
         <f>COUNTIF(D20:D21,"Não")</f>
@@ -8891,8 +8783,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="230.4">
-      <c r="A20" s="30"/>
+    <row r="20" spans="1:10" ht="30">
+      <c r="A20" s="31"/>
       <c r="B20" s="23">
         <v>12</v>
       </c>
@@ -8900,17 +8792,13 @@
         <v>78</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="172.8">
-      <c r="A21" s="30"/>
+        <v>116</v>
+      </c>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+    </row>
+    <row r="21" spans="1:10" ht="30">
+      <c r="A21" s="31"/>
       <c r="B21" s="5">
         <v>13</v>
       </c>
@@ -8921,12 +8809,10 @@
         <v>116</v>
       </c>
       <c r="E21" s="8"/>
-      <c r="F21" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="14.4">
-      <c r="A22" s="30"/>
+      <c r="F21" s="8"/>
+    </row>
+    <row r="22" spans="1:10" ht="15">
+      <c r="A22" s="31"/>
       <c r="B22" s="9"/>
       <c r="C22" s="10" t="s">
         <v>4</v>
@@ -8936,7 +8822,7 @@
       <c r="F22" s="12"/>
       <c r="G22">
         <f>COUNTIF(D23:D24,"Sim")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <f>COUNTIF(D23:D24,"Parcialmente")</f>
@@ -8951,8 +8837,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="86.4">
-      <c r="A23" s="30"/>
+    <row r="23" spans="1:10" ht="30">
+      <c r="A23" s="31"/>
       <c r="B23" s="23">
         <v>14</v>
       </c>
@@ -8964,11 +8850,11 @@
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="172.8">
-      <c r="A24" s="30"/>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15">
+      <c r="A24" s="31"/>
       <c r="B24" s="5">
         <v>15</v>
       </c>
@@ -8979,12 +8865,10 @@
         <v>116</v>
       </c>
       <c r="E24" s="8"/>
-      <c r="F24" s="8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="14.4">
-      <c r="A25" s="30"/>
+      <c r="F24" s="8"/>
+    </row>
+    <row r="25" spans="1:10" ht="15">
+      <c r="A25" s="31"/>
       <c r="B25" s="9"/>
       <c r="C25" s="10" t="s">
         <v>36</v>
@@ -9006,11 +8890,11 @@
       </c>
       <c r="J25">
         <f>COUNTIF(D26:D27,"NA")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="129.6">
-      <c r="A26" s="30"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="30">
+      <c r="A26" s="31"/>
       <c r="B26" s="23">
         <v>16</v>
       </c>
@@ -9018,15 +8902,15 @@
         <v>72</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:10" ht="115.2">
-      <c r="A27" s="30"/>
+    <row r="27" spans="1:10" ht="15">
+      <c r="A27" s="31"/>
       <c r="B27" s="5">
         <v>17</v>
       </c>
@@ -9034,15 +8918,15 @@
         <v>37</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:10" ht="14.4">
-      <c r="A28" s="30"/>
+    <row r="28" spans="1:10" ht="15">
+      <c r="A28" s="31"/>
       <c r="B28" s="9"/>
       <c r="C28" s="10" t="s">
         <v>13</v>
@@ -9052,11 +8936,11 @@
       <c r="F28" s="12"/>
       <c r="G28">
         <f>COUNTIF(D29:D36,"Sim")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <f>COUNTIF(D29:D36,"Parcialmente")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I28">
         <f>COUNTIF(D29:D36,"Não")</f>
@@ -9064,11 +8948,11 @@
       </c>
       <c r="J28">
         <f>COUNTIF(D29:D36,"NA")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="144">
-      <c r="A29" s="30"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="30">
+      <c r="A29" s="31"/>
       <c r="B29" s="23">
         <v>21</v>
       </c>
@@ -9079,12 +8963,10 @@
         <v>116</v>
       </c>
       <c r="E29" s="8"/>
-      <c r="F29" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="115.2">
-      <c r="A30" s="30"/>
+      <c r="F29" s="8"/>
+    </row>
+    <row r="30" spans="1:10" ht="15">
+      <c r="A30" s="31"/>
       <c r="B30" s="5">
         <v>22</v>
       </c>
@@ -9095,12 +8977,10 @@
         <v>116</v>
       </c>
       <c r="E30" s="8"/>
-      <c r="F30" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="172.8">
-      <c r="A31" s="30"/>
+      <c r="F30" s="8"/>
+    </row>
+    <row r="31" spans="1:10" ht="15">
+      <c r="A31" s="31"/>
       <c r="B31" s="5">
         <v>23</v>
       </c>
@@ -9111,12 +8991,10 @@
         <v>116</v>
       </c>
       <c r="E31" s="8"/>
-      <c r="F31" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="331.2">
-      <c r="A32" s="30"/>
+      <c r="F31" s="8"/>
+    </row>
+    <row r="32" spans="1:10" ht="15">
+      <c r="A32" s="31"/>
       <c r="B32" s="5">
         <v>24</v>
       </c>
@@ -9124,17 +9002,15 @@
         <v>82</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>143</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="E32" s="8"/>
       <c r="F32" s="8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="172.8">
-      <c r="A33" s="30"/>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15">
+      <c r="A33" s="31"/>
       <c r="B33" s="5">
         <v>25</v>
       </c>
@@ -9142,17 +9018,13 @@
         <v>83</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="201.6">
-      <c r="A34" s="30"/>
+        <v>116</v>
+      </c>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+    </row>
+    <row r="34" spans="1:10" ht="30">
+      <c r="A34" s="31"/>
       <c r="B34" s="5">
         <v>26</v>
       </c>
@@ -9160,17 +9032,12 @@
         <v>87</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>148</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A35" s="30"/>
+      <c r="A35" s="31"/>
       <c r="B35" s="5">
         <v>27</v>
       </c>
@@ -9178,35 +9045,29 @@
         <v>84</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="129.6">
-      <c r="A36" s="30"/>
+        <v>116</v>
+      </c>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+    </row>
+    <row r="36" spans="1:10" ht="15">
+      <c r="A36" s="31"/>
       <c r="B36" s="5">
         <v>28</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>151</v>
-      </c>
+      <c r="D36" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E36" s="8"/>
       <c r="F36" s="8" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15" customHeight="1">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="29" t="s">
         <v>30</v>
       </c>
       <c r="B37" s="9"/>
@@ -9218,7 +9079,7 @@
       <c r="F37" s="12"/>
       <c r="G37">
         <f>COUNTIF(D38:D41,"Sim")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H37">
         <f>COUNTIF(D38:D41,"Parcialmente")</f>
@@ -9233,8 +9094,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="187.2">
-      <c r="A38" s="29"/>
+    <row r="38" spans="1:10" ht="30">
+      <c r="A38" s="30"/>
       <c r="B38" s="23">
         <v>30</v>
       </c>
@@ -9245,12 +9106,10 @@
         <v>116</v>
       </c>
       <c r="E38" s="8"/>
-      <c r="F38" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="273.60000000000002">
-      <c r="A39" s="29"/>
+      <c r="F38" s="8"/>
+    </row>
+    <row r="39" spans="1:10" ht="30">
+      <c r="A39" s="30"/>
       <c r="B39" s="5">
         <v>31</v>
       </c>
@@ -9261,12 +9120,10 @@
         <v>116</v>
       </c>
       <c r="E39" s="8"/>
-      <c r="F39" s="8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="129.6">
-      <c r="A40" s="29"/>
+      <c r="F39" s="8"/>
+    </row>
+    <row r="40" spans="1:10" ht="15">
+      <c r="A40" s="30"/>
       <c r="B40" s="5">
         <v>32</v>
       </c>
@@ -9277,12 +9134,10 @@
         <v>116</v>
       </c>
       <c r="E40" s="8"/>
-      <c r="F40" s="8" t="s">
-        <v>155</v>
-      </c>
+      <c r="F40" s="8"/>
     </row>
     <row r="41" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A41" s="29"/>
+      <c r="A41" s="30"/>
       <c r="B41" s="5">
         <v>33</v>
       </c>
@@ -9294,7 +9149,7 @@
       </c>
       <c r="E41" s="8"/>
       <c r="F41" s="8" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -9323,47 +9178,47 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="21.109375" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" style="4" customWidth="1"/>
     <col min="3" max="3" width="68" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.6640625" customWidth="1"/>
-    <col min="6" max="6" width="32.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="6" max="6" width="32.7109375" customWidth="1"/>
     <col min="7" max="10" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="2" spans="1:10" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="32"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="39"/>
+      <c r="E2" s="40"/>
       <c r="F2" s="21" t="e">
         <f>COUNTIF(D5:D41,"Sim")/(COUNTA(D5:D42)-COUNTIF(D5:D42,"NA"))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" thickBot="1">
-      <c r="A3" s="32" t="s">
+    <row r="3" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A3" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="32"/>
+      <c r="B3" s="33"/>
       <c r="C3" s="13"/>
       <c r="D3" s="42" t="s">
         <v>43</v>
@@ -9371,7 +9226,7 @@
       <c r="E3" s="43"/>
       <c r="F3" s="44"/>
     </row>
-    <row r="4" spans="1:10" ht="14.4">
+    <row r="4" spans="1:10" ht="15">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
@@ -9392,7 +9247,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="34" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="9"/>
@@ -9403,8 +9258,8 @@
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
     </row>
-    <row r="6" spans="1:10" ht="14.4">
-      <c r="A6" s="30"/>
+    <row r="6" spans="1:10" ht="15">
+      <c r="A6" s="31"/>
       <c r="B6" s="5">
         <v>1</v>
       </c>
@@ -9431,8 +9286,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="14.4">
-      <c r="A7" s="30"/>
+    <row r="7" spans="1:10" ht="15">
+      <c r="A7" s="31"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
         <v>3</v>
@@ -9441,8 +9296,8 @@
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="28.8">
-      <c r="A8" s="30"/>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="30">
+      <c r="A8" s="31"/>
       <c r="B8" s="5">
         <v>2</v>
       </c>
@@ -9469,8 +9324,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="1" customFormat="1" ht="28.8">
-      <c r="A9" s="30"/>
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="30">
+      <c r="A9" s="31"/>
       <c r="B9" s="5">
         <v>3</v>
       </c>
@@ -9485,8 +9340,8 @@
       <c r="I9"/>
       <c r="J9"/>
     </row>
-    <row r="10" spans="1:10" ht="14.4">
-      <c r="A10" s="30"/>
+    <row r="10" spans="1:10" ht="15">
+      <c r="A10" s="31"/>
       <c r="B10" s="9"/>
       <c r="C10" s="10" t="s">
         <v>97</v>
@@ -9495,8 +9350,8 @@
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
     </row>
-    <row r="11" spans="1:10" ht="28.8">
-      <c r="A11" s="30"/>
+    <row r="11" spans="1:10" ht="30">
+      <c r="A11" s="31"/>
       <c r="B11" s="23">
         <v>4</v>
       </c>
@@ -9523,8 +9378,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="28.8">
-      <c r="A12" s="30"/>
+    <row r="12" spans="1:10" ht="30">
+      <c r="A12" s="31"/>
       <c r="B12" s="23">
         <v>5</v>
       </c>
@@ -9535,8 +9390,8 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:10" ht="14.4">
-      <c r="A13" s="30"/>
+    <row r="13" spans="1:10" ht="30">
+      <c r="A13" s="31"/>
       <c r="B13" s="5">
         <v>6</v>
       </c>
@@ -9547,8 +9402,8 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
     </row>
-    <row r="14" spans="1:10" ht="28.8">
-      <c r="A14" s="30"/>
+    <row r="14" spans="1:10" ht="30">
+      <c r="A14" s="31"/>
       <c r="B14" s="5">
         <v>7</v>
       </c>
@@ -9559,8 +9414,8 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:10" ht="14.4">
-      <c r="A15" s="30"/>
+    <row r="15" spans="1:10" ht="15">
+      <c r="A15" s="31"/>
       <c r="B15" s="9"/>
       <c r="C15" s="10" t="s">
         <v>4</v>
@@ -9569,8 +9424,8 @@
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:10" ht="14.4">
-      <c r="A16" s="30"/>
+    <row r="16" spans="1:10" ht="15">
+      <c r="A16" s="31"/>
       <c r="B16" s="5">
         <v>7</v>
       </c>
@@ -9598,7 +9453,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1">
-      <c r="A17" s="33" t="s">
+      <c r="A17" s="34" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="9"/>
@@ -9609,8 +9464,8 @@
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
     </row>
-    <row r="18" spans="1:10" ht="28.8">
-      <c r="A18" s="30"/>
+    <row r="18" spans="1:10" ht="30">
+      <c r="A18" s="31"/>
       <c r="B18" s="5">
         <v>9</v>
       </c>
@@ -9637,8 +9492,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="28.8">
-      <c r="A19" s="30"/>
+    <row r="19" spans="1:10" ht="30">
+      <c r="A19" s="31"/>
       <c r="B19" s="23">
         <v>10</v>
       </c>
@@ -9649,8 +9504,8 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="1:10" s="1" customFormat="1" ht="28.8">
-      <c r="A20" s="30"/>
+    <row r="20" spans="1:10" s="1" customFormat="1" ht="30">
+      <c r="A20" s="31"/>
       <c r="B20" s="5">
         <v>11</v>
       </c>
@@ -9661,8 +9516,8 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:10" ht="28.8">
-      <c r="A21" s="30"/>
+    <row r="21" spans="1:10" ht="45">
+      <c r="A21" s="31"/>
       <c r="B21" s="5">
         <v>12</v>
       </c>
@@ -9673,8 +9528,8 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:10" ht="14.4">
-      <c r="A22" s="33" t="s">
+    <row r="22" spans="1:10" ht="15">
+      <c r="A22" s="34" t="s">
         <v>19</v>
       </c>
       <c r="B22" s="9"/>
@@ -9685,8 +9540,8 @@
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
     </row>
-    <row r="23" spans="1:10" ht="28.8">
-      <c r="A23" s="30"/>
+    <row r="23" spans="1:10" ht="30">
+      <c r="A23" s="31"/>
       <c r="B23" s="5">
         <v>17</v>
       </c>
@@ -9713,8 +9568,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="28.8">
-      <c r="A24" s="30"/>
+    <row r="24" spans="1:10" ht="30">
+      <c r="A24" s="31"/>
       <c r="B24" s="5">
         <v>18</v>
       </c>
@@ -9725,8 +9580,8 @@
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="1:10" ht="28.8">
-      <c r="A25" s="30"/>
+    <row r="25" spans="1:10" ht="30">
+      <c r="A25" s="31"/>
       <c r="B25" s="5">
         <v>19</v>
       </c>
@@ -9737,8 +9592,8 @@
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
     </row>
-    <row r="26" spans="1:10" ht="14.4">
-      <c r="A26" s="30"/>
+    <row r="26" spans="1:10" ht="15">
+      <c r="A26" s="31"/>
       <c r="B26" s="5">
         <v>21</v>
       </c>
@@ -9749,8 +9604,8 @@
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:10" ht="14.4">
-      <c r="A27" s="30"/>
+    <row r="27" spans="1:10" ht="15">
+      <c r="A27" s="31"/>
       <c r="B27" s="5">
         <v>22</v>
       </c>
@@ -9761,7 +9616,7 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:10" ht="14.4">
+    <row r="28" spans="1:10" ht="15">
       <c r="A28" s="41" t="s">
         <v>11</v>
       </c>
@@ -9773,7 +9628,7 @@
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:10" ht="14.4">
+    <row r="29" spans="1:10" ht="15">
       <c r="A29" s="41"/>
       <c r="B29" s="5">
         <v>23</v>
@@ -9801,7 +9656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="14.4">
+    <row r="30" spans="1:10" ht="15">
       <c r="A30" s="41"/>
       <c r="B30" s="5">
         <v>24</v>
@@ -9813,7 +9668,7 @@
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
     </row>
-    <row r="31" spans="1:10" ht="28.8">
+    <row r="31" spans="1:10" ht="30">
       <c r="A31" s="41"/>
       <c r="B31" s="5">
         <v>25</v>
@@ -9825,7 +9680,7 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
     </row>
-    <row r="32" spans="1:10" ht="14.4">
+    <row r="32" spans="1:10" ht="15">
       <c r="A32" s="41"/>
       <c r="B32" s="5">
         <v>26</v>
@@ -9837,7 +9692,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:10" ht="14.4">
+    <row r="33" spans="1:10" ht="15">
       <c r="A33" s="41"/>
       <c r="B33" s="5">
         <v>27</v>
@@ -9849,7 +9704,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:10" ht="14.4">
+    <row r="34" spans="1:10" ht="15">
       <c r="A34" s="41"/>
       <c r="B34" s="5">
         <v>28</v>
@@ -9862,7 +9717,7 @@
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1">
-      <c r="A35" s="28" t="s">
+      <c r="A35" s="29" t="s">
         <v>30</v>
       </c>
       <c r="B35" s="9"/>
@@ -9873,8 +9728,8 @@
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:10" ht="28.8">
-      <c r="A36" s="29"/>
+    <row r="36" spans="1:10" ht="30">
+      <c r="A36" s="30"/>
       <c r="B36" s="5">
         <v>29</v>
       </c>
@@ -9901,8 +9756,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="14.4">
-      <c r="A37" s="29"/>
+    <row r="37" spans="1:10" ht="15">
+      <c r="A37" s="30"/>
       <c r="B37" s="5">
         <v>30</v>
       </c>
@@ -9913,8 +9768,8 @@
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
     </row>
-    <row r="38" spans="1:10" ht="28.8">
-      <c r="A38" s="29"/>
+    <row r="38" spans="1:10" ht="30">
+      <c r="A38" s="30"/>
       <c r="B38" s="5">
         <v>31</v>
       </c>
@@ -9925,8 +9780,8 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:10" ht="14.4">
-      <c r="A39" s="29"/>
+    <row r="39" spans="1:10" ht="15">
+      <c r="A39" s="30"/>
       <c r="B39" s="9"/>
       <c r="C39" s="10" t="s">
         <v>15</v>
@@ -9935,8 +9790,8 @@
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:10" ht="14.4">
-      <c r="A40" s="29"/>
+    <row r="40" spans="1:10" ht="15">
+      <c r="A40" s="30"/>
       <c r="B40" s="5">
         <v>32</v>
       </c>
@@ -9963,8 +9818,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="14.4">
-      <c r="A41" s="29"/>
+    <row r="41" spans="1:10" ht="15">
+      <c r="A41" s="30"/>
       <c r="B41" s="5">
         <v>33</v>
       </c>
@@ -10004,47 +9859,47 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J57"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="21.109375" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="71.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.6640625" customWidth="1"/>
-    <col min="6" max="6" width="32.6640625" customWidth="1"/>
-    <col min="7" max="10" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="71.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="6" max="6" width="32.7109375" customWidth="1"/>
+    <col min="7" max="10" width="9.140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="2" spans="1:10" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="32"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="39"/>
+      <c r="E2" s="40"/>
       <c r="F2" s="21" t="e">
         <f>COUNTIF(D5:D42,"Sim")/(COUNTA(D5:D41)-COUNTIF(D5:D41,"NA"))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" thickBot="1">
-      <c r="A3" s="32" t="s">
+    <row r="3" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A3" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="32"/>
+      <c r="B3" s="33"/>
       <c r="C3" s="13"/>
       <c r="D3" s="42" t="s">
         <v>43</v>
@@ -10052,7 +9907,7 @@
       <c r="E3" s="43"/>
       <c r="F3" s="44"/>
     </row>
-    <row r="4" spans="1:10" ht="14.4">
+    <row r="4" spans="1:10" ht="15">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
@@ -10073,7 +9928,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="34" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="9"/>
@@ -10084,8 +9939,8 @@
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
     </row>
-    <row r="6" spans="1:10" ht="14.4">
-      <c r="A6" s="30"/>
+    <row r="6" spans="1:10" ht="15">
+      <c r="A6" s="31"/>
       <c r="B6" s="5">
         <v>1</v>
       </c>
@@ -10112,8 +9967,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="14.4">
-      <c r="A7" s="30"/>
+    <row r="7" spans="1:10" ht="15">
+      <c r="A7" s="31"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
         <v>3</v>
@@ -10122,8 +9977,8 @@
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="28.8">
-      <c r="A8" s="30"/>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="30">
+      <c r="A8" s="31"/>
       <c r="B8" s="5">
         <v>2</v>
       </c>
@@ -10150,8 +10005,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="14.4">
-      <c r="A9" s="30"/>
+    <row r="9" spans="1:10" ht="15">
+      <c r="A9" s="31"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10" t="s">
         <v>97</v>
@@ -10160,8 +10015,8 @@
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
     </row>
-    <row r="10" spans="1:10" ht="28.8">
-      <c r="A10" s="30"/>
+    <row r="10" spans="1:10" ht="30">
+      <c r="A10" s="31"/>
       <c r="B10" s="5">
         <v>3</v>
       </c>
@@ -10188,8 +10043,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="28.8">
-      <c r="A11" s="30"/>
+    <row r="11" spans="1:10" ht="30">
+      <c r="A11" s="31"/>
       <c r="B11" s="5">
         <v>4</v>
       </c>
@@ -10201,7 +10056,7 @@
       <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A12" s="30"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="5">
         <v>5</v>
       </c>
@@ -10212,8 +10067,8 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:10" ht="14.4">
-      <c r="A13" s="30"/>
+    <row r="13" spans="1:10" ht="15">
+      <c r="A13" s="31"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10" t="s">
         <v>4</v>
@@ -10222,8 +10077,8 @@
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
     </row>
-    <row r="14" spans="1:10" ht="14.4">
-      <c r="A14" s="30"/>
+    <row r="14" spans="1:10" ht="15">
+      <c r="A14" s="31"/>
       <c r="B14" s="5">
         <v>6</v>
       </c>
@@ -10251,7 +10106,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="34" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="9"/>
@@ -10262,8 +10117,8 @@
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:10" ht="14.4">
-      <c r="A16" s="30"/>
+    <row r="16" spans="1:10" ht="15">
+      <c r="A16" s="31"/>
       <c r="B16" s="5">
         <v>8</v>
       </c>
@@ -10290,8 +10145,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="14.4">
-      <c r="A17" s="33" t="s">
+    <row r="17" spans="1:10" ht="15">
+      <c r="A17" s="34" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="9"/>
@@ -10302,8 +10157,8 @@
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
     </row>
-    <row r="18" spans="1:10" ht="14.4">
-      <c r="A18" s="30"/>
+    <row r="18" spans="1:10" ht="15">
+      <c r="A18" s="31"/>
       <c r="B18" s="5">
         <v>11</v>
       </c>
@@ -10330,8 +10185,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="28.8">
-      <c r="A19" s="30"/>
+    <row r="19" spans="1:10" ht="30">
+      <c r="A19" s="31"/>
       <c r="B19" s="5">
         <v>13</v>
       </c>
@@ -10342,8 +10197,8 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="1:10" ht="28.8">
-      <c r="A20" s="30"/>
+    <row r="20" spans="1:10" ht="30">
+      <c r="A20" s="31"/>
       <c r="B20" s="5">
         <v>14</v>
       </c>
@@ -10354,8 +10209,8 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:10" ht="14.4">
-      <c r="A21" s="30"/>
+    <row r="21" spans="1:10" ht="15">
+      <c r="A21" s="31"/>
       <c r="B21" s="5">
         <v>15</v>
       </c>
@@ -10366,8 +10221,8 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:10" ht="14.4">
-      <c r="A22" s="30"/>
+    <row r="22" spans="1:10" ht="15">
+      <c r="A22" s="31"/>
       <c r="B22" s="5">
         <v>16</v>
       </c>
@@ -10378,8 +10233,8 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
     </row>
-    <row r="23" spans="1:10" ht="14.4">
-      <c r="A23" s="33" t="s">
+    <row r="23" spans="1:10" ht="15">
+      <c r="A23" s="34" t="s">
         <v>20</v>
       </c>
       <c r="B23" s="9"/>
@@ -10390,8 +10245,8 @@
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
     </row>
-    <row r="24" spans="1:10" ht="28.8">
-      <c r="A24" s="30"/>
+    <row r="24" spans="1:10" ht="30">
+      <c r="A24" s="31"/>
       <c r="B24" s="23">
         <v>17</v>
       </c>
@@ -10418,8 +10273,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="28.8">
-      <c r="A25" s="30"/>
+    <row r="25" spans="1:10" ht="30">
+      <c r="A25" s="31"/>
       <c r="B25" s="5">
         <v>18</v>
       </c>
@@ -10430,8 +10285,8 @@
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
     </row>
-    <row r="26" spans="1:10" ht="14.4">
-      <c r="A26" s="30"/>
+    <row r="26" spans="1:10" ht="15">
+      <c r="A26" s="31"/>
       <c r="B26" s="5">
         <v>19</v>
       </c>
@@ -10442,8 +10297,8 @@
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:10" ht="14.4">
-      <c r="A27" s="30"/>
+    <row r="27" spans="1:10" ht="15">
+      <c r="A27" s="31"/>
       <c r="B27" s="5">
         <v>21</v>
       </c>
@@ -10454,8 +10309,8 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:10" ht="14.4">
-      <c r="A28" s="30"/>
+    <row r="28" spans="1:10" ht="15">
+      <c r="A28" s="31"/>
       <c r="B28" s="5">
         <v>22</v>
       </c>
@@ -10466,7 +10321,7 @@
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
     </row>
-    <row r="29" spans="1:10" ht="14.4">
+    <row r="29" spans="1:10" ht="15">
       <c r="A29" s="41" t="s">
         <v>11</v>
       </c>
@@ -10478,7 +10333,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="1:10" ht="14.4">
+    <row r="30" spans="1:10" ht="15">
       <c r="A30" s="41"/>
       <c r="B30" s="5">
         <v>24</v>
@@ -10506,7 +10361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="28.8">
+    <row r="31" spans="1:10" ht="30">
       <c r="A31" s="41"/>
       <c r="B31" s="5">
         <v>26</v>
@@ -10518,7 +10373,7 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
     </row>
-    <row r="32" spans="1:10" ht="14.4">
+    <row r="32" spans="1:10" ht="15">
       <c r="A32" s="41"/>
       <c r="B32" s="5">
         <v>27</v>
@@ -10530,7 +10385,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:10" ht="14.4">
+    <row r="33" spans="1:10" ht="15">
       <c r="A33" s="41"/>
       <c r="B33" s="5">
         <v>28</v>
@@ -10542,7 +10397,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:10" ht="14.4">
+    <row r="34" spans="1:10" ht="15">
       <c r="A34" s="41"/>
       <c r="B34" s="5">
         <v>29</v>
@@ -10555,7 +10410,7 @@
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1">
-      <c r="A35" s="28" t="s">
+      <c r="A35" s="29" t="s">
         <v>30</v>
       </c>
       <c r="B35" s="9"/>
@@ -10566,8 +10421,8 @@
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:10" ht="28.8">
-      <c r="A36" s="29"/>
+    <row r="36" spans="1:10" ht="30">
+      <c r="A36" s="30"/>
       <c r="B36" s="5">
         <v>30</v>
       </c>
@@ -10594,8 +10449,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="14.4">
-      <c r="A37" s="29"/>
+    <row r="37" spans="1:10" ht="15">
+      <c r="A37" s="30"/>
       <c r="B37" s="5">
         <v>31</v>
       </c>
@@ -10606,8 +10461,8 @@
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
     </row>
-    <row r="38" spans="1:10" ht="28.8">
-      <c r="A38" s="29"/>
+    <row r="38" spans="1:10" ht="30">
+      <c r="A38" s="30"/>
       <c r="B38" s="5">
         <v>32</v>
       </c>
@@ -10618,8 +10473,8 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:10" ht="14.4">
-      <c r="A39" s="29"/>
+    <row r="39" spans="1:10" ht="15">
+      <c r="A39" s="30"/>
       <c r="B39" s="5"/>
       <c r="C39" s="8" t="s">
         <v>105</v>
@@ -10628,8 +10483,8 @@
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
     </row>
-    <row r="40" spans="1:10" ht="14.4">
-      <c r="A40" s="29"/>
+    <row r="40" spans="1:10" ht="15">
+      <c r="A40" s="30"/>
       <c r="B40" s="9"/>
       <c r="C40" s="10" t="s">
         <v>15</v>
@@ -10638,8 +10493,8 @@
       <c r="E40" s="12"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:10" ht="14.4">
-      <c r="A41" s="29"/>
+    <row r="41" spans="1:10" ht="15">
+      <c r="A41" s="30"/>
       <c r="B41" s="5">
         <v>33</v>
       </c>
@@ -10666,8 +10521,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="14.4">
-      <c r="A42" s="29"/>
+    <row r="42" spans="1:10" ht="15">
+      <c r="A42" s="30"/>
       <c r="B42" s="5">
         <v>34</v>
       </c>
@@ -10678,47 +10533,47 @@
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
     </row>
-    <row r="51" spans="2:3" ht="14.4">
+    <row r="51" spans="2:3" ht="15">
       <c r="B51"/>
       <c r="C51"/>
     </row>
-    <row r="52" spans="2:3" ht="14.4">
+    <row r="52" spans="2:3" ht="15">
       <c r="B52"/>
       <c r="C52"/>
     </row>
-    <row r="53" spans="2:3" ht="14.4">
+    <row r="53" spans="2:3" ht="15">
       <c r="B53"/>
       <c r="C53"/>
     </row>
-    <row r="54" spans="2:3" ht="14.4">
+    <row r="54" spans="2:3" ht="15">
       <c r="B54"/>
       <c r="C54"/>
     </row>
-    <row r="55" spans="2:3" ht="14.4">
+    <row r="55" spans="2:3" ht="15">
       <c r="B55"/>
       <c r="C55"/>
     </row>
-    <row r="56" spans="2:3" ht="14.4">
+    <row r="56" spans="2:3" ht="15">
       <c r="B56"/>
       <c r="C56"/>
     </row>
-    <row r="57" spans="2:3" ht="14.4">
+    <row r="57" spans="2:3" ht="15">
       <c r="B57"/>
       <c r="C57"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:F3"/>
     <mergeCell ref="A5:A14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A17:A22"/>
     <mergeCell ref="A29:A34"/>
     <mergeCell ref="A35:A42"/>
     <mergeCell ref="A23:A28"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:F3"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23 D15 D17 D40 D35 D29" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -10736,47 +10591,47 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J58"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="21.109375" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="71.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.6640625" customWidth="1"/>
-    <col min="6" max="6" width="32.6640625" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="71.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="6" max="6" width="32.7109375" customWidth="1"/>
     <col min="7" max="10" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="2" spans="1:10" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="32"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="39"/>
+      <c r="E2" s="40"/>
       <c r="F2" s="21" t="e">
         <f>COUNTIF(D5:D43,"Sim")/(COUNTA(D5:D43)-COUNTIF(D5:D43,"NA"))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" thickBot="1">
-      <c r="A3" s="32" t="s">
+    <row r="3" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A3" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="32"/>
+      <c r="B3" s="33"/>
       <c r="C3" s="13"/>
       <c r="D3" s="42" t="s">
         <v>43</v>
@@ -10784,7 +10639,7 @@
       <c r="E3" s="43"/>
       <c r="F3" s="44"/>
     </row>
-    <row r="4" spans="1:10" ht="14.4">
+    <row r="4" spans="1:10" ht="15">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
@@ -10805,7 +10660,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="34" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="9"/>
@@ -10816,8 +10671,8 @@
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
     </row>
-    <row r="6" spans="1:10" ht="14.4">
-      <c r="A6" s="30"/>
+    <row r="6" spans="1:10" ht="15">
+      <c r="A6" s="31"/>
       <c r="B6" s="5">
         <v>1</v>
       </c>
@@ -10844,8 +10699,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="14.4">
-      <c r="A7" s="30"/>
+    <row r="7" spans="1:10" ht="15">
+      <c r="A7" s="31"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
         <v>3</v>
@@ -10854,8 +10709,8 @@
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="28.8">
-      <c r="A8" s="30"/>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="30">
+      <c r="A8" s="31"/>
       <c r="B8" s="5">
         <v>2</v>
       </c>
@@ -10882,8 +10737,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="14.4">
-      <c r="A9" s="30"/>
+    <row r="9" spans="1:10" ht="15">
+      <c r="A9" s="31"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10" t="s">
         <v>14</v>
@@ -10892,8 +10747,8 @@
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
     </row>
-    <row r="10" spans="1:10" ht="28.8">
-      <c r="A10" s="30"/>
+    <row r="10" spans="1:10" ht="30">
+      <c r="A10" s="31"/>
       <c r="B10" s="5">
         <v>3</v>
       </c>
@@ -10920,8 +10775,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="28.8">
-      <c r="A11" s="30"/>
+    <row r="11" spans="1:10" ht="30">
+      <c r="A11" s="31"/>
       <c r="B11" s="5">
         <v>4</v>
       </c>
@@ -10933,7 +10788,7 @@
       <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:10" ht="29.25" customHeight="1">
-      <c r="A12" s="30"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="5">
         <v>5</v>
       </c>
@@ -10944,8 +10799,8 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:10" ht="14.4">
-      <c r="A13" s="30"/>
+    <row r="13" spans="1:10" ht="15">
+      <c r="A13" s="31"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10" t="s">
         <v>4</v>
@@ -10954,8 +10809,8 @@
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
     </row>
-    <row r="14" spans="1:10" ht="14.4">
-      <c r="A14" s="30"/>
+    <row r="14" spans="1:10" ht="15">
+      <c r="A14" s="31"/>
       <c r="B14" s="5">
         <v>6</v>
       </c>
@@ -10983,7 +10838,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="34" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="9"/>
@@ -10994,8 +10849,8 @@
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:10" ht="14.4">
-      <c r="A16" s="30"/>
+    <row r="16" spans="1:10" ht="15">
+      <c r="A16" s="31"/>
       <c r="B16" s="5">
         <v>8</v>
       </c>
@@ -11023,7 +10878,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1">
-      <c r="A17" s="33" t="s">
+      <c r="A17" s="34" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="9"/>
@@ -11034,8 +10889,8 @@
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
     </row>
-    <row r="18" spans="1:10" ht="14.4">
-      <c r="A18" s="30"/>
+    <row r="18" spans="1:10" ht="30">
+      <c r="A18" s="31"/>
       <c r="B18" s="5">
         <v>9</v>
       </c>
@@ -11062,8 +10917,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="14.4">
-      <c r="A19" s="30"/>
+    <row r="19" spans="1:10" ht="15">
+      <c r="A19" s="31"/>
       <c r="B19" s="5">
         <v>10</v>
       </c>
@@ -11074,8 +10929,8 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="1:10" ht="28.8">
-      <c r="A20" s="30"/>
+    <row r="20" spans="1:10" ht="30">
+      <c r="A20" s="31"/>
       <c r="B20" s="5">
         <v>11</v>
       </c>
@@ -11086,8 +10941,8 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:10" ht="14.4">
-      <c r="A21" s="34"/>
+    <row r="21" spans="1:10" ht="15">
+      <c r="A21" s="35"/>
       <c r="B21" s="5">
         <v>13</v>
       </c>
@@ -11098,8 +10953,8 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:10" ht="14.4">
-      <c r="A22" s="33" t="s">
+    <row r="22" spans="1:10" ht="15">
+      <c r="A22" s="34" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="9"/>
@@ -11110,8 +10965,8 @@
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
     </row>
-    <row r="23" spans="1:10" ht="14.4">
-      <c r="A23" s="30"/>
+    <row r="23" spans="1:10" ht="15">
+      <c r="A23" s="31"/>
       <c r="B23" s="5">
         <v>14</v>
       </c>
@@ -11138,8 +10993,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="14.4">
-      <c r="A24" s="30"/>
+    <row r="24" spans="1:10" ht="15">
+      <c r="A24" s="31"/>
       <c r="B24" s="5">
         <v>15</v>
       </c>
@@ -11151,7 +11006,7 @@
       <c r="F24" s="8"/>
     </row>
     <row r="25" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="34" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="9"/>
@@ -11162,8 +11017,8 @@
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="1:10" s="1" customFormat="1" ht="28.8">
-      <c r="A26" s="30"/>
+    <row r="26" spans="1:10" s="1" customFormat="1" ht="30">
+      <c r="A26" s="31"/>
       <c r="B26" s="23">
         <v>24</v>
       </c>
@@ -11190,8 +11045,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="1" customFormat="1" ht="43.2">
-      <c r="A27" s="30"/>
+    <row r="27" spans="1:10" s="1" customFormat="1" ht="45">
+      <c r="A27" s="31"/>
       <c r="B27" s="5">
         <v>25</v>
       </c>
@@ -11202,8 +11057,8 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:10" ht="14.4">
-      <c r="A28" s="30"/>
+    <row r="28" spans="1:10" ht="15">
+      <c r="A28" s="31"/>
       <c r="B28" s="9"/>
       <c r="C28" s="10" t="s">
         <v>10</v>
@@ -11212,8 +11067,8 @@
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:10" ht="28.8">
-      <c r="A29" s="30"/>
+    <row r="29" spans="1:10" ht="30">
+      <c r="A29" s="31"/>
       <c r="B29" s="23">
         <v>26</v>
       </c>
@@ -11240,7 +11095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="14.4">
+    <row r="30" spans="1:10" ht="15">
       <c r="A30" s="41" t="s">
         <v>11</v>
       </c>
@@ -11252,7 +11107,7 @@
       <c r="E30" s="12"/>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:10" ht="14.4">
+    <row r="31" spans="1:10" ht="15">
       <c r="A31" s="41"/>
       <c r="B31" s="5">
         <v>19</v>
@@ -11280,7 +11135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="28.8">
+    <row r="32" spans="1:10" ht="30">
       <c r="A32" s="41"/>
       <c r="B32" s="5">
         <v>20</v>
@@ -11292,7 +11147,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:10" ht="14.4">
+    <row r="33" spans="1:10" ht="15">
       <c r="A33" s="41"/>
       <c r="B33" s="5">
         <v>21</v>
@@ -11304,7 +11159,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:10" ht="14.4">
+    <row r="34" spans="1:10" ht="15">
       <c r="A34" s="41"/>
       <c r="B34" s="5">
         <v>24</v>
@@ -11316,7 +11171,7 @@
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
     </row>
-    <row r="35" spans="1:10" ht="14.4">
+    <row r="35" spans="1:10" ht="15">
       <c r="A35" s="41"/>
       <c r="B35" s="5">
         <v>25</v>
@@ -11329,7 +11184,7 @@
       <c r="F35" s="8"/>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1">
-      <c r="A36" s="28" t="s">
+      <c r="A36" s="29" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="9"/>
@@ -11340,8 +11195,8 @@
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:10" ht="28.8">
-      <c r="A37" s="29"/>
+    <row r="37" spans="1:10" ht="30">
+      <c r="A37" s="30"/>
       <c r="B37" s="5">
         <v>26</v>
       </c>
@@ -11368,8 +11223,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="14.4">
-      <c r="A38" s="29"/>
+    <row r="38" spans="1:10" ht="15">
+      <c r="A38" s="30"/>
       <c r="B38" s="5">
         <v>27</v>
       </c>
@@ -11380,8 +11235,8 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:10" ht="28.8">
-      <c r="A39" s="29"/>
+    <row r="39" spans="1:10" ht="30">
+      <c r="A39" s="30"/>
       <c r="B39" s="5">
         <v>28</v>
       </c>
@@ -11392,8 +11247,8 @@
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
     </row>
-    <row r="40" spans="1:10" ht="14.4">
-      <c r="A40" s="29"/>
+    <row r="40" spans="1:10" ht="15">
+      <c r="A40" s="30"/>
       <c r="B40" s="5"/>
       <c r="C40" s="8" t="s">
         <v>105</v>
@@ -11402,8 +11257,8 @@
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
     </row>
-    <row r="41" spans="1:10" ht="14.4">
-      <c r="A41" s="29"/>
+    <row r="41" spans="1:10" ht="15">
+      <c r="A41" s="30"/>
       <c r="B41" s="9"/>
       <c r="C41" s="10" t="s">
         <v>15</v>
@@ -11412,8 +11267,8 @@
       <c r="E41" s="12"/>
       <c r="F41" s="12"/>
     </row>
-    <row r="42" spans="1:10" ht="14.4">
-      <c r="A42" s="29"/>
+    <row r="42" spans="1:10" ht="15">
+      <c r="A42" s="30"/>
       <c r="B42" s="5">
         <v>29</v>
       </c>
@@ -11440,8 +11295,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="14.4">
-      <c r="A43" s="29"/>
+    <row r="43" spans="1:10" ht="15">
+      <c r="A43" s="30"/>
       <c r="B43" s="5">
         <v>30</v>
       </c>
@@ -11452,36 +11307,41 @@
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
     </row>
-    <row r="52" spans="2:3" ht="14.4">
+    <row r="52" spans="2:3" ht="15">
       <c r="B52"/>
       <c r="C52"/>
     </row>
-    <row r="53" spans="2:3" ht="14.4">
+    <row r="53" spans="2:3" ht="15">
       <c r="B53"/>
       <c r="C53"/>
     </row>
-    <row r="54" spans="2:3" ht="14.4">
+    <row r="54" spans="2:3" ht="15">
       <c r="B54"/>
       <c r="C54"/>
     </row>
-    <row r="55" spans="2:3" ht="14.4">
+    <row r="55" spans="2:3" ht="15">
       <c r="B55"/>
       <c r="C55"/>
     </row>
-    <row r="56" spans="2:3" ht="14.4">
+    <row r="56" spans="2:3" ht="15">
       <c r="B56"/>
       <c r="C56"/>
     </row>
-    <row r="57" spans="2:3" ht="14.4">
+    <row r="57" spans="2:3" ht="15">
       <c r="B57"/>
       <c r="C57"/>
     </row>
-    <row r="58" spans="2:3" ht="14.4">
+    <row r="58" spans="2:3" ht="15">
       <c r="B58"/>
       <c r="C58"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A30:A35"/>
+    <mergeCell ref="A36:A43"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A25:A29"/>
     <mergeCell ref="A5:A14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A1:F1"/>
@@ -11489,11 +11349,6 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A30:A35"/>
-    <mergeCell ref="A36:A43"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A25:A29"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25 D17 D15 D22 D41 D36 D30 D28" xr:uid="{00000000-0002-0000-0400-000000000000}">

--- a/6.Gerenciamento de Projeto/CARREGAJA - Checklist de Projeto.xlsx
+++ b/6.Gerenciamento de Projeto/CARREGAJA - Checklist de Projeto.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E6D2C59-B447-4BC6-AA7D-FEF622FE12AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1506729-BD29-4FDC-A8F6-3BD22061EEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="666" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="666" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicadores" sheetId="6" r:id="rId1"/>
@@ -26,6 +26,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -710,7 +713,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="127">
   <si>
     <t>Ambiente</t>
   </si>
@@ -1054,52 +1057,52 @@
     <t>Foram realizados os testes de aceitação por parte do usuário final?</t>
   </si>
   <si>
-    <t xml:space="preserve">31/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henrique de Almeida Marangoni Inacio (Scrum Master)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcialmente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diagramas produzidos em PlantUML, e não no Template - Modelos Analise e Design.asta previsto pelo SpinOff. Pasta e nomeação corretas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transpor o Modelo de Caso de Uso para o Astah.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protótipo não produzido: é saída de Detalhar Requisitos, da Elaboração.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aprovado pelo Product Owner, que atua como representante do cliente (RE-16).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O Glossário é a subseção 1.3 do Visão, onde o template o posiciona. O SpinOff não prevê template autônomo para ele.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não houve reunião de levantamento a registrar: o projeto não dispõe de cliente externo (RE-16).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não se aplica pelo mesmo motivo do item 16 (RE-16).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimativas preliminares, a confirmar por Planning Poker.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Padronizar o idioma das mensagens de commit.</t>
+    <t>31/08/2026</t>
+  </si>
+  <si>
+    <t>Henrique de Almeida Marangoni Inacio (Scrum Master)</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Parcialmente</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Diagramas produzidos em PlantUML, e não no Template - Modelos Analise e Design.asta previsto pelo SpinOff. Pasta e nomeação corretas.</t>
+  </si>
+  <si>
+    <t>Transpor o Modelo de Caso de Uso para o Astah.</t>
+  </si>
+  <si>
+    <t>Protótipo não produzido: é saída de Detalhar Requisitos, da Elaboração.</t>
+  </si>
+  <si>
+    <t>Aprovado pelo Product Owner, que atua como representante do cliente (RE-16).</t>
+  </si>
+  <si>
+    <t>O Glossário é a subseção 1.3 do Visão, onde o template o posiciona. O SpinOff não prevê template autônomo para ele.</t>
+  </si>
+  <si>
+    <t>Não houve reunião de levantamento a registrar: o projeto não dispõe de cliente externo (RE-16).</t>
+  </si>
+  <si>
+    <t>Não se aplica pelo mesmo motivo do item 16 (RE-16).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelo mantido em CARREGAJA - Modelo de Caso de Uso.asta, no formato do Template - Modelos Analise e Design do SpinOff, com os dois atores, os catorze casos de uso UC01–UC14 e as relações de inclusão.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="17">
     <font>
       <sz val="11"/>
@@ -1426,7 +1429,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -1459,12 +1462,6 @@
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1481,9 +1478,6 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -1495,8 +1489,14 @@
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
@@ -1504,7 +1504,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1513,29 +1513,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1545,6 +1527,99 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1649,7 +1724,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.96153846153846156</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -1881,19 +1956,19 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -1905,10 +1980,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -2000,7 +2075,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2226,7 +2301,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2235,7 +2310,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -2422,6 +2497,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2429,7 +2505,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7331,61 +7406,83 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{42432A3B-87A4-4250-B6CB-A5A85616B62F}">
+  <we:reference id="wa200010725" version="1.0.0.1" store="pt-BR" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200010725" version="1.0.0.1" store="wa200010725" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;980d1984-b891-49ff-a88b-1ef10bc5a613&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39" style="17" customWidth="1"/>
+    <col min="2" max="2" width="39" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="28"/>
+      <c r="B1" s="38"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="17" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="20" t="e">
+      <c r="B3" s="18">
         <f>'Ver-Iniciação1'!$F$2</f>
-        <v>#DIV/0!</v>
+        <v>0.96153846153846156</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="20" t="e">
+      <c r="B4" s="18" t="e">
         <f>'Ver-Elaboração1'!$F$2</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="20" t="e">
+      <c r="B5" s="18" t="e">
         <f>'Ver-Construção1'!$F$2</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="20" t="e">
+      <c r="B6" s="18" t="e">
         <f>'Ver-Transição1'!$F$2</f>
         <v>#DIV/0!</v>
       </c>
@@ -7453,38 +7550,38 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="25" t="e">
+      <c r="B2" s="22">
         <f>('Ver-Iniciação1'!$G$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C2" s="25" t="e">
+        <v>1</v>
+      </c>
+      <c r="C2" s="22">
         <f>('Ver-Iniciação1'!$H$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D2" s="25" t="e">
+        <v>0</v>
+      </c>
+      <c r="D2" s="22">
         <f>('Ver-Iniciação1'!$I$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E2" s="25" t="e">
+        <v>0</v>
+      </c>
+      <c r="E2" s="22">
         <f>('Ver-Iniciação1'!$J$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="N2" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="25" t="e">
+      <c r="O2" s="22" t="e">
         <f>('Ver-Elaboração1'!$G$6/SUM('Ver-Elaboração1'!$G$6:'Ver-Elaboração1'!$J$6))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P2" s="25" t="e">
+      <c r="P2" s="22" t="e">
         <f>('Ver-Elaboração1'!$H$6/SUM('Ver-Elaboração1'!$G$6:'Ver-Elaboração1'!$J$6))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q2" s="25" t="e">
+      <c r="Q2" s="22" t="e">
         <f>('Ver-Elaboração1'!$I$6/SUM('Ver-Elaboração1'!$G$6:'Ver-Elaboração1'!$J$6))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R2" s="25" t="e">
+      <c r="R2" s="22" t="e">
         <f>('Ver-Elaboração1'!$J$6/SUM('Ver-Elaboração1'!$G$6:'Ver-Elaboração1'!$J$6))</f>
         <v>#DIV/0!</v>
       </c>
@@ -7493,38 +7590,38 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="25" t="e">
+      <c r="B3" s="22">
         <f>('Ver-Iniciação1'!$G$7/SUM('Ver-Iniciação1'!$G$7:'Ver-Iniciação1'!$J$7))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C3" s="25" t="e">
+        <v>1</v>
+      </c>
+      <c r="C3" s="22">
         <f>('Ver-Iniciação1'!$H$7/SUM('Ver-Iniciação1'!$G$7:'Ver-Iniciação1'!$J$7))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D3" s="25" t="e">
+        <v>0</v>
+      </c>
+      <c r="D3" s="22">
         <f>('Ver-Iniciação1'!$I$7/SUM('Ver-Iniciação1'!$G$7:'Ver-Iniciação1'!$J$7))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E3" s="25" t="e">
+        <v>0</v>
+      </c>
+      <c r="E3" s="22">
         <f>('Ver-Iniciação1'!$J$7/SUM('Ver-Iniciação1'!$G$7:'Ver-Iniciação1'!$J$7))</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="N3" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="25" t="e">
+      <c r="O3" s="22" t="e">
         <f>('Ver-Elaboração1'!$G$8/SUM('Ver-Elaboração1'!$G$8:'Ver-Elaboração1'!$J$8))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P3" s="25" t="e">
+      <c r="P3" s="22" t="e">
         <f>('Ver-Elaboração1'!$H$8/SUM('Ver-Elaboração1'!$G$8:'Ver-Elaboração1'!$J$8))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q3" s="25" t="e">
+      <c r="Q3" s="22" t="e">
         <f>('Ver-Elaboração1'!$I$8/SUM('Ver-Elaboração1'!$G$8:'Ver-Elaboração1'!$J$8))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R3" s="25" t="e">
+      <c r="R3" s="22" t="e">
         <f>('Ver-Elaboração1'!$J$8/SUM('Ver-Elaboração1'!$G$8:'Ver-Elaboração1'!$J$8))</f>
         <v>#DIV/0!</v>
       </c>
@@ -7533,38 +7630,38 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="25" t="e">
+      <c r="B4" s="22">
         <f>('Ver-Iniciação1'!$G$13/SUM('Ver-Iniciação1'!$G$13:'Ver-Iniciação1'!$J$13))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C4" s="25" t="e">
+        <v>0.6</v>
+      </c>
+      <c r="C4" s="22">
         <f>('Ver-Iniciação1'!$H$13/SUM('Ver-Iniciação1'!$G$13:'Ver-Iniciação1'!$J$13))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D4" s="25" t="e">
+        <v>0.2</v>
+      </c>
+      <c r="D4" s="22">
         <f>('Ver-Iniciação1'!$I$13/SUM('Ver-Iniciação1'!$G$13:'Ver-Iniciação1'!$J$13))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E4" s="25" t="e">
+        <v>0</v>
+      </c>
+      <c r="E4" s="22">
         <f>('Ver-Iniciação1'!$J$13/SUM('Ver-Iniciação1'!$G$13:'Ver-Iniciação1'!$J$13))</f>
-        <v>#DIV/0!</v>
+        <v>0.2</v>
       </c>
       <c r="N4" t="s">
         <v>14</v>
       </c>
-      <c r="O4" s="25" t="e">
+      <c r="O4" s="22" t="e">
         <f>('Ver-Elaboração1'!$G$11/SUM('Ver-Elaboração1'!$G$11:'Ver-Elaboração1'!$J$11))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P4" s="25" t="e">
+      <c r="P4" s="22" t="e">
         <f>('Ver-Elaboração1'!$H$11/SUM('Ver-Elaboração1'!$G$11:'Ver-Elaboração1'!$J$11))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q4" s="25" t="e">
+      <c r="Q4" s="22" t="e">
         <f>('Ver-Elaboração1'!$I$11/SUM('Ver-Elaboração1'!$G$11:'Ver-Elaboração1'!$J$11))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R4" s="25" t="e">
+      <c r="R4" s="22" t="e">
         <f>('Ver-Elaboração1'!$J$11/SUM('Ver-Elaboração1'!$G$11:'Ver-Elaboração1'!$J$11))</f>
         <v>#DIV/0!</v>
       </c>
@@ -7573,38 +7670,38 @@
       <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="25" t="e">
+      <c r="B5" s="22">
         <f>('Ver-Iniciação1'!$G$19/SUM('Ver-Iniciação1'!$G$19:'Ver-Iniciação1'!$J$19))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C5" s="25" t="e">
+        <v>1</v>
+      </c>
+      <c r="C5" s="22">
         <f>('Ver-Iniciação1'!$H$19/SUM('Ver-Iniciação1'!$G$19:'Ver-Iniciação1'!$J$19))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D5" s="25" t="e">
+        <v>0</v>
+      </c>
+      <c r="D5" s="22">
         <f>('Ver-Iniciação1'!$I$19/SUM('Ver-Iniciação1'!$G$19:'Ver-Iniciação1'!$J$19))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E5" s="25" t="e">
+        <v>0</v>
+      </c>
+      <c r="E5" s="22">
         <f>('Ver-Iniciação1'!$J$19/SUM('Ver-Iniciação1'!$G$19:'Ver-Iniciação1'!$J$19))</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="N5" t="s">
         <v>4</v>
       </c>
-      <c r="O5" s="25" t="e">
+      <c r="O5" s="22" t="e">
         <f>('Ver-Elaboração1'!$G$16/SUM('Ver-Elaboração1'!$G$16:'Ver-Elaboração1'!$J$16))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P5" s="25" t="e">
+      <c r="P5" s="22" t="e">
         <f>('Ver-Elaboração1'!$H$16/SUM('Ver-Elaboração1'!$G$16:'Ver-Elaboração1'!$J$16))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q5" s="25" t="e">
+      <c r="Q5" s="22" t="e">
         <f>('Ver-Elaboração1'!$I$16/SUM('Ver-Elaboração1'!$G$16:'Ver-Elaboração1'!$J$16))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R5" s="25" t="e">
+      <c r="R5" s="22" t="e">
         <f>('Ver-Elaboração1'!$J$16/SUM('Ver-Elaboração1'!$G$16:'Ver-Elaboração1'!$J$16))</f>
         <v>#DIV/0!</v>
       </c>
@@ -7613,38 +7710,38 @@
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="25" t="e">
+      <c r="B6" s="22">
         <f>('Ver-Iniciação1'!$G$22/SUM('Ver-Iniciação1'!$G$22:'Ver-Iniciação1'!$J$22))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C6" s="25" t="e">
+        <v>1</v>
+      </c>
+      <c r="C6" s="22">
         <f>('Ver-Iniciação1'!$H$22/SUM('Ver-Iniciação1'!$G$22:'Ver-Iniciação1'!$J$22))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D6" s="25" t="e">
+        <v>0</v>
+      </c>
+      <c r="D6" s="22">
         <f>('Ver-Iniciação1'!$I$22/SUM('Ver-Iniciação1'!$G$22:'Ver-Iniciação1'!$J$22))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E6" s="25" t="e">
+        <v>0</v>
+      </c>
+      <c r="E6" s="22">
         <f>('Ver-Iniciação1'!$J$22/SUM('Ver-Iniciação1'!$G$22:'Ver-Iniciação1'!$J$22))</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="N6" t="s">
         <v>36</v>
       </c>
-      <c r="O6" s="25" t="e">
+      <c r="O6" s="22" t="e">
         <f>('Ver-Elaboração1'!#REF!/SUM('Ver-Elaboração1'!#REF!:'Ver-Elaboração1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="P6" s="25" t="e">
+      <c r="P6" s="22" t="e">
         <f>('Ver-Elaboração1'!#REF!/SUM('Ver-Elaboração1'!#REF!:'Ver-Elaboração1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="Q6" s="25" t="e">
+      <c r="Q6" s="22" t="e">
         <f>('Ver-Elaboração1'!#REF!/SUM('Ver-Elaboração1'!#REF!:'Ver-Elaboração1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="R6" s="25" t="e">
+      <c r="R6" s="22" t="e">
         <f>('Ver-Elaboração1'!#REF!/SUM('Ver-Elaboração1'!#REF!:'Ver-Elaboração1'!#REF!))</f>
         <v>#REF!</v>
       </c>
@@ -7653,38 +7750,38 @@
       <c r="A7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="25" t="e">
+      <c r="B7" s="22">
         <f>('Ver-Iniciação1'!$G$25/SUM('Ver-Iniciação1'!$G$25:'Ver-Iniciação1'!$J$25))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C7" s="25" t="e">
+        <v>0</v>
+      </c>
+      <c r="C7" s="22">
         <f>('Ver-Iniciação1'!$H$25/SUM('Ver-Iniciação1'!$G$25:'Ver-Iniciação1'!$J$25))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D7" s="25" t="e">
+        <v>0</v>
+      </c>
+      <c r="D7" s="22">
         <f>('Ver-Iniciação1'!$I$25/SUM('Ver-Iniciação1'!$G$25:'Ver-Iniciação1'!$J$25))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E7" s="25" t="e">
+        <v>0</v>
+      </c>
+      <c r="E7" s="22">
         <f>('Ver-Iniciação1'!$J$25/SUM('Ver-Iniciação1'!$G$25:'Ver-Iniciação1'!$J$25))</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="N7" t="s">
         <v>5</v>
       </c>
-      <c r="O7" s="25" t="e">
+      <c r="O7" s="22" t="e">
         <f>('Ver-Elaboração1'!$G$18/SUM('Ver-Elaboração1'!$G$18:'Ver-Elaboração1'!$J$18))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P7" s="25" t="e">
+      <c r="P7" s="22" t="e">
         <f>('Ver-Elaboração1'!$H$18/SUM('Ver-Elaboração1'!$G$18:'Ver-Elaboração1'!$J$18))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q7" s="25" t="e">
+      <c r="Q7" s="22" t="e">
         <f>('Ver-Elaboração1'!$I$18/SUM('Ver-Elaboração1'!$G$18:'Ver-Elaboração1'!$J$18))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R7" s="25" t="e">
+      <c r="R7" s="22" t="e">
         <f>('Ver-Elaboração1'!$J$18/SUM('Ver-Elaboração1'!$G$18:'Ver-Elaboração1'!$J$18))</f>
         <v>#DIV/0!</v>
       </c>
@@ -7693,38 +7790,38 @@
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="25" t="e">
+      <c r="B8" s="22" t="e">
         <f>('Ver-Iniciação1'!#REF!/SUM('Ver-Iniciação1'!#REF!:'Ver-Iniciação1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="C8" s="25" t="e">
+      <c r="C8" s="22" t="e">
         <f>('Ver-Iniciação1'!#REF!/SUM('Ver-Iniciação1'!#REF!:'Ver-Iniciação1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="D8" s="25" t="e">
+      <c r="D8" s="22" t="e">
         <f>('Ver-Iniciação1'!#REF!/SUM('Ver-Iniciação1'!#REF!:'Ver-Iniciação1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="E8" s="25" t="e">
+      <c r="E8" s="22" t="e">
         <f>('Ver-Iniciação1'!#REF!/SUM('Ver-Iniciação1'!#REF!:'Ver-Iniciação1'!#REF!))</f>
         <v>#REF!</v>
       </c>
       <c r="N8" t="s">
         <v>7</v>
       </c>
-      <c r="O8" s="25" t="e">
+      <c r="O8" s="22" t="e">
         <f>('Ver-Elaboração1'!#REF!/SUM('Ver-Elaboração1'!#REF!:'Ver-Elaboração1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="P8" s="25" t="e">
+      <c r="P8" s="22" t="e">
         <f>('Ver-Elaboração1'!#REF!/SUM('Ver-Elaboração1'!#REF!:'Ver-Elaboração1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="Q8" s="25" t="e">
+      <c r="Q8" s="22" t="e">
         <f>('Ver-Elaboração1'!#REF!/SUM('Ver-Elaboração1'!#REF!:'Ver-Elaboração1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="R8" s="25" t="e">
+      <c r="R8" s="22" t="e">
         <f>('Ver-Elaboração1'!#REF!/SUM('Ver-Elaboração1'!#REF!:'Ver-Elaboração1'!#REF!))</f>
         <v>#REF!</v>
       </c>
@@ -7733,38 +7830,38 @@
       <c r="A9" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="25" t="e">
+      <c r="B9" s="22" t="e">
         <f>('Ver-Iniciação1'!#REF!/SUM('Ver-Iniciação1'!#REF!:'Ver-Iniciação1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="C9" s="25" t="e">
+      <c r="C9" s="22" t="e">
         <f>('Ver-Iniciação1'!#REF!/SUM('Ver-Iniciação1'!#REF!:'Ver-Iniciação1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="D9" s="25" t="e">
+      <c r="D9" s="22" t="e">
         <f>('Ver-Iniciação1'!#REF!/SUM('Ver-Iniciação1'!#REF!:'Ver-Iniciação1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="E9" s="25" t="e">
+      <c r="E9" s="22" t="e">
         <f>('Ver-Iniciação1'!#REF!/SUM('Ver-Iniciação1'!#REF!:'Ver-Iniciação1'!#REF!))</f>
         <v>#REF!</v>
       </c>
       <c r="N9" t="s">
         <v>6</v>
       </c>
-      <c r="O9" s="25" t="e">
+      <c r="O9" s="22" t="e">
         <f>('Ver-Elaboração1'!$G$23/SUM('Ver-Elaboração1'!$G$23:'Ver-Elaboração1'!$J$23))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P9" s="25" t="e">
+      <c r="P9" s="22" t="e">
         <f>('Ver-Elaboração1'!$H$23/SUM('Ver-Elaboração1'!$G$23:'Ver-Elaboração1'!$J$23))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q9" s="25" t="e">
+      <c r="Q9" s="22" t="e">
         <f>('Ver-Elaboração1'!$I$23/SUM('Ver-Elaboração1'!$G$23:'Ver-Elaboração1'!$J$23))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R9" s="25" t="e">
+      <c r="R9" s="22" t="e">
         <f>('Ver-Elaboração1'!$J$23/SUM('Ver-Elaboração1'!$G$23:'Ver-Elaboração1'!$J$23))</f>
         <v>#DIV/0!</v>
       </c>
@@ -7773,38 +7870,38 @@
       <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="25" t="e">
+      <c r="B10" s="22">
         <f>('Ver-Iniciação1'!$G$28/SUM('Ver-Iniciação1'!$G$28:'Ver-Iniciação1'!$J$28))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C10" s="25" t="e">
+        <v>1</v>
+      </c>
+      <c r="C10" s="22">
         <f>('Ver-Iniciação1'!$H$28/SUM('Ver-Iniciação1'!$G$28:'Ver-Iniciação1'!$J$28))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D10" s="25" t="e">
+        <v>0</v>
+      </c>
+      <c r="D10" s="22">
         <f>('Ver-Iniciação1'!$I$28/SUM('Ver-Iniciação1'!$G$28:'Ver-Iniciação1'!$J$28))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E10" s="25" t="e">
+        <v>0</v>
+      </c>
+      <c r="E10" s="22">
         <f>('Ver-Iniciação1'!$J$28/SUM('Ver-Iniciação1'!$G$28:'Ver-Iniciação1'!$J$28))</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="N10" t="s">
         <v>13</v>
       </c>
-      <c r="O10" s="25" t="e">
+      <c r="O10" s="22" t="e">
         <f>('Ver-Elaboração1'!$G$29/SUM('Ver-Elaboração1'!$G$29:'Ver-Elaboração1'!$J$29))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P10" s="25" t="e">
+      <c r="P10" s="22" t="e">
         <f>('Ver-Elaboração1'!$H$29/SUM('Ver-Elaboração1'!$G$29:'Ver-Elaboração1'!$J$29))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q10" s="25" t="e">
+      <c r="Q10" s="22" t="e">
         <f>('Ver-Elaboração1'!$I$29/SUM('Ver-Elaboração1'!$G$29:'Ver-Elaboração1'!$J$29))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R10" s="25" t="e">
+      <c r="R10" s="22" t="e">
         <f>('Ver-Elaboração1'!$J$29/SUM('Ver-Elaboração1'!$G$29:'Ver-Elaboração1'!$J$29))</f>
         <v>#DIV/0!</v>
       </c>
@@ -7813,38 +7910,38 @@
       <c r="A11" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="25" t="e">
+      <c r="B11" s="22">
         <f>('Ver-Iniciação1'!$G$37/SUM('Ver-Iniciação1'!$G$37:'Ver-Iniciação1'!$J$37))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C11" s="25" t="e">
+        <v>1</v>
+      </c>
+      <c r="C11" s="22">
         <f>('Ver-Iniciação1'!$H$37/SUM('Ver-Iniciação1'!$G$37:'Ver-Iniciação1'!$J$37))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D11" s="25" t="e">
+        <v>0</v>
+      </c>
+      <c r="D11" s="22">
         <f>('Ver-Iniciação1'!$I$37/SUM('Ver-Iniciação1'!$G$37:'Ver-Iniciação1'!$J$37))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E11" s="25" t="e">
+        <v>0</v>
+      </c>
+      <c r="E11" s="22">
         <f>('Ver-Iniciação1'!$J$37/SUM('Ver-Iniciação1'!$G$37:'Ver-Iniciação1'!$J$37))</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="N11" t="s">
         <v>56</v>
       </c>
-      <c r="O11" s="25" t="e">
+      <c r="O11" s="22" t="e">
         <f>('Ver-Elaboração1'!$G$36/SUM('Ver-Elaboração1'!$G$36:'Ver-Elaboração1'!$J$36))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P11" s="25" t="e">
+      <c r="P11" s="22" t="e">
         <f>('Ver-Elaboração1'!$H$36/SUM('Ver-Elaboração1'!$G$36:'Ver-Elaboração1'!$J$36))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q11" s="25" t="e">
+      <c r="Q11" s="22" t="e">
         <f>('Ver-Elaboração1'!$I$36/SUM('Ver-Elaboração1'!$G$36:'Ver-Elaboração1'!$J$36))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R11" s="25" t="e">
+      <c r="R11" s="22" t="e">
         <f>('Ver-Elaboração1'!$J$36/SUM('Ver-Elaboração1'!$G$36:'Ver-Elaboração1'!$J$36))</f>
         <v>#DIV/0!</v>
       </c>
@@ -7853,38 +7950,38 @@
       <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="25" t="e">
+      <c r="B12" s="22" t="e">
         <f>('Ver-Iniciação1'!#REF!/SUM('Ver-Iniciação1'!#REF!:'Ver-Iniciação1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="C12" s="25" t="e">
+      <c r="C12" s="22" t="e">
         <f>('Ver-Iniciação1'!#REF!/SUM('Ver-Iniciação1'!#REF!:'Ver-Iniciação1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="D12" s="25" t="e">
+      <c r="D12" s="22" t="e">
         <f>('Ver-Iniciação1'!#REF!/SUM('Ver-Iniciação1'!#REF!:'Ver-Iniciação1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="E12" s="25" t="e">
+      <c r="E12" s="22" t="e">
         <f>('Ver-Iniciação1'!#REF!/SUM('Ver-Iniciação1'!#REF!:'Ver-Iniciação1'!#REF!))</f>
         <v>#REF!</v>
       </c>
       <c r="N12" t="s">
         <v>15</v>
       </c>
-      <c r="O12" s="25" t="e">
+      <c r="O12" s="22" t="e">
         <f>('Ver-Elaboração1'!$G$40/SUM('Ver-Elaboração1'!$G$40:'Ver-Elaboração1'!$J$40))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P12" s="25" t="e">
+      <c r="P12" s="22" t="e">
         <f>('Ver-Elaboração1'!$H$40/SUM('Ver-Elaboração1'!$G$40:'Ver-Elaboração1'!$J$40))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q12" s="25" t="e">
+      <c r="Q12" s="22" t="e">
         <f>('Ver-Elaboração1'!$I$40/SUM('Ver-Elaboração1'!$G$40:'Ver-Elaboração1'!$J$40))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R12" s="25" t="e">
+      <c r="R12" s="22" t="e">
         <f>('Ver-Elaboração1'!$J$40/SUM('Ver-Elaboração1'!$G$40:'Ver-Elaboração1'!$J$40))</f>
         <v>#DIV/0!</v>
       </c>
@@ -7910,19 +8007,19 @@
       <c r="A23" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="26" t="e">
+      <c r="B23" s="23" t="e">
         <f>('Ver-Construção1'!$G$6/SUM('Ver-Construção1'!$G$6:'Ver-Construção1'!$J$6))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C23" s="27" t="e">
+      <c r="C23" s="24" t="e">
         <f>('Ver-Construção1'!$H$6/SUM('Ver-Construção1'!$G$6:'Ver-Construção1'!$J$6))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D23" s="27" t="e">
+      <c r="D23" s="24" t="e">
         <f>('Ver-Construção1'!$I$6/SUM('Ver-Construção1'!$G$6:'Ver-Construção1'!$J$6))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E23" s="27" t="e">
+      <c r="E23" s="24" t="e">
         <f>('Ver-Construção1'!$J$6/SUM('Ver-Construção1'!$G$6:'Ver-Construção1'!$J$6))</f>
         <v>#DIV/0!</v>
       </c>
@@ -7931,19 +8028,19 @@
       <c r="A24" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="26" t="e">
+      <c r="B24" s="23" t="e">
         <f>('Ver-Construção1'!$G$8/SUM('Ver-Construção1'!$G$8:'Ver-Construção1'!$J$8))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C24" s="27" t="e">
+      <c r="C24" s="24" t="e">
         <f>('Ver-Construção1'!$H$8/SUM('Ver-Construção1'!$G$8:'Ver-Construção1'!$J$8))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D24" s="27" t="e">
+      <c r="D24" s="24" t="e">
         <f>('Ver-Construção1'!$I$8/SUM('Ver-Construção1'!$G$8:'Ver-Construção1'!$J$8))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E24" s="27" t="e">
+      <c r="E24" s="24" t="e">
         <f>('Ver-Construção1'!$J$8/SUM('Ver-Construção1'!$G$8:'Ver-Construção1'!$J$8))</f>
         <v>#DIV/0!</v>
       </c>
@@ -7967,38 +8064,38 @@
       <c r="A25" t="s">
         <v>14</v>
       </c>
-      <c r="B25" s="26" t="e">
+      <c r="B25" s="23" t="e">
         <f>('Ver-Construção1'!$G$10/SUM('Ver-Construção1'!$G$10:'Ver-Construção1'!$J$10))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C25" s="27" t="e">
+      <c r="C25" s="24" t="e">
         <f>('Ver-Construção1'!$G$10/SUM('Ver-Construção1'!$G$10:'Ver-Construção1'!$J$10))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D25" s="27" t="e">
+      <c r="D25" s="24" t="e">
         <f>('Ver-Construção1'!$I$10/SUM('Ver-Construção1'!$G$10:'Ver-Construção1'!$J$10))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E25" s="27" t="e">
+      <c r="E25" s="24" t="e">
         <f>('Ver-Construção1'!$J$10/SUM('Ver-Construção1'!$G$10:'Ver-Construção1'!$J$10))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M25" t="s">
         <v>2</v>
       </c>
-      <c r="N25" s="27" t="e">
+      <c r="N25" s="24" t="e">
         <f>('Ver-Transição1'!$G$6/SUM('Ver-Transição1'!$G$6:'Ver-Transição1'!$J$6))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O25" s="27" t="e">
+      <c r="O25" s="24" t="e">
         <f>('Ver-Transição1'!$H$6/SUM('Ver-Transição1'!$G$6:'Ver-Transição1'!$J$6))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P25" s="27" t="e">
+      <c r="P25" s="24" t="e">
         <f>('Ver-Transição1'!$I$6/SUM('Ver-Transição1'!$G$6:'Ver-Transição1'!$J$6))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q25" s="27" t="e">
+      <c r="Q25" s="24" t="e">
         <f>('Ver-Transição1'!$J$6/SUM('Ver-Transição1'!$G$6:'Ver-Transição1'!$J$6))</f>
         <v>#DIV/0!</v>
       </c>
@@ -8007,38 +8104,38 @@
       <c r="A26" t="s">
         <v>4</v>
       </c>
-      <c r="B26" s="27" t="e">
+      <c r="B26" s="24" t="e">
         <f>('Ver-Construção1'!$G$14/SUM('Ver-Construção1'!$G$14:'Ver-Construção1'!$J$14))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C26" s="27" t="e">
+      <c r="C26" s="24" t="e">
         <f>('Ver-Construção1'!$H$14/SUM('Ver-Construção1'!$G$14:'Ver-Construção1'!$J$14))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D26" s="27" t="e">
+      <c r="D26" s="24" t="e">
         <f>('Ver-Construção1'!$I$14/SUM('Ver-Construção1'!$G$14:'Ver-Construção1'!$J$14))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E26" s="27" t="e">
+      <c r="E26" s="24" t="e">
         <f>('Ver-Construção1'!$J$14/SUM('Ver-Construção1'!$G$14:'Ver-Construção1'!$J$14))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M26" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="27" t="e">
+      <c r="N26" s="24" t="e">
         <f>('Ver-Transição1'!$G$8/SUM('Ver-Transição1'!$G$8:'Ver-Transição1'!$J$8))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O26" s="27" t="e">
+      <c r="O26" s="24" t="e">
         <f>('Ver-Transição1'!$H$8/SUM('Ver-Transição1'!$G$8:'Ver-Transição1'!$J$8))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P26" s="27" t="e">
+      <c r="P26" s="24" t="e">
         <f>('Ver-Transição1'!$I$8/SUM('Ver-Transição1'!$G$8:'Ver-Transição1'!$J$8))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q26" s="27" t="e">
+      <c r="Q26" s="24" t="e">
         <f>('Ver-Transição1'!$J$8/SUM('Ver-Transição1'!$G$8:'Ver-Transição1'!$J$8))</f>
         <v>#DIV/0!</v>
       </c>
@@ -8047,38 +8144,38 @@
       <c r="A27" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="27" t="e">
+      <c r="B27" s="24" t="e">
         <f>('Ver-Construção1'!#REF!/SUM('Ver-Construção1'!#REF!:'Ver-Construção1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="C27" s="27" t="e">
+      <c r="C27" s="24" t="e">
         <f>('Ver-Construção1'!#REF!/SUM('Ver-Construção1'!#REF!:'Ver-Construção1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="D27" s="27" t="e">
+      <c r="D27" s="24" t="e">
         <f>('Ver-Construção1'!#REF!/SUM('Ver-Construção1'!#REF!:'Ver-Construção1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="E27" s="27" t="e">
+      <c r="E27" s="24" t="e">
         <f>('Ver-Construção1'!#REF!/SUM('Ver-Construção1'!#REF!:'Ver-Construção1'!#REF!))</f>
         <v>#REF!</v>
       </c>
       <c r="M27" t="s">
         <v>14</v>
       </c>
-      <c r="N27" s="27" t="e">
+      <c r="N27" s="24" t="e">
         <f>('Ver-Transição1'!$G$10/SUM('Ver-Transição1'!$G$10:'Ver-Transição1'!$J$10))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O27" s="27" t="e">
+      <c r="O27" s="24" t="e">
         <f>('Ver-Transição1'!$H$10/SUM('Ver-Transição1'!$G$10:'Ver-Transição1'!$J$10))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P27" s="27" t="e">
+      <c r="P27" s="24" t="e">
         <f>('Ver-Transição1'!$I$10/SUM('Ver-Transição1'!$G$10:'Ver-Transição1'!$J$10))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q27" s="27" t="e">
+      <c r="Q27" s="24" t="e">
         <f>('Ver-Transição1'!$J$10/SUM('Ver-Transição1'!$G$10:'Ver-Transição1'!$J$10))</f>
         <v>#DIV/0!</v>
       </c>
@@ -8087,38 +8184,38 @@
       <c r="A28" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="27" t="e">
+      <c r="B28" s="24" t="e">
         <f>('Ver-Construção1'!$G$16/SUM('Ver-Construção1'!$G$16:'Ver-Construção1'!$J$16))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C28" s="27" t="e">
+      <c r="C28" s="24" t="e">
         <f>('Ver-Construção1'!$H$16/SUM('Ver-Construção1'!$G$16:'Ver-Construção1'!$J$16))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D28" s="27" t="e">
+      <c r="D28" s="24" t="e">
         <f>('Ver-Construção1'!$I$16/SUM('Ver-Construção1'!$G$16:'Ver-Construção1'!$J$16))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E28" s="27" t="e">
+      <c r="E28" s="24" t="e">
         <f>('Ver-Construção1'!$J$16/SUM('Ver-Construção1'!$G$16:'Ver-Construção1'!$J$16))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M28" t="s">
         <v>4</v>
       </c>
-      <c r="N28" s="27" t="e">
+      <c r="N28" s="24" t="e">
         <f>('Ver-Transição1'!$G$14/SUM('Ver-Transição1'!$G$14:'Ver-Transição1'!$J$14))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O28" s="27" t="e">
+      <c r="O28" s="24" t="e">
         <f>('Ver-Transição1'!$H$14/SUM('Ver-Transição1'!$G$14:'Ver-Transição1'!$J$14))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P28" s="27" t="e">
+      <c r="P28" s="24" t="e">
         <f>('Ver-Transição1'!$I$14/SUM('Ver-Transição1'!$G$14:'Ver-Transição1'!$J$14))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q28" s="27" t="e">
+      <c r="Q28" s="24" t="e">
         <f>('Ver-Transição1'!$J$14/SUM('Ver-Transição1'!$G$14:'Ver-Transição1'!$J$14))</f>
         <v>#DIV/0!</v>
       </c>
@@ -8127,38 +8224,38 @@
       <c r="A29" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="27" t="e">
+      <c r="B29" s="24" t="e">
         <f>('Ver-Construção1'!#REF!/SUM('Ver-Construção1'!#REF!:'Ver-Construção1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="C29" s="27" t="e">
+      <c r="C29" s="24" t="e">
         <f>('Ver-Construção1'!#REF!/SUM('Ver-Construção1'!#REF!:'Ver-Construção1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="D29" s="27" t="e">
+      <c r="D29" s="24" t="e">
         <f>('Ver-Construção1'!#REF!/SUM('Ver-Construção1'!#REF!:'Ver-Construção1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="E29" s="27" t="e">
+      <c r="E29" s="24" t="e">
         <f>('Ver-Construção1'!#REF!/SUM('Ver-Construção1'!#REF!:'Ver-Construção1'!#REF!))</f>
         <v>#REF!</v>
       </c>
       <c r="M29" t="s">
         <v>36</v>
       </c>
-      <c r="N29" s="27" t="e">
+      <c r="N29" s="24" t="e">
         <f>('Ver-Transição1'!#REF!/SUM('Ver-Transição1'!#REF!:'Ver-Transição1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="O29" s="27" t="e">
+      <c r="O29" s="24" t="e">
         <f>('Ver-Transição1'!#REF!/SUM('Ver-Transição1'!#REF!:'Ver-Transição1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="P29" s="27" t="e">
+      <c r="P29" s="24" t="e">
         <f>('Ver-Transição1'!#REF!/SUM('Ver-Transição1'!#REF!:'Ver-Transição1'!#REF!))</f>
         <v>#REF!</v>
       </c>
-      <c r="Q29" s="27" t="e">
+      <c r="Q29" s="24" t="e">
         <f>('Ver-Transição1'!#REF!/SUM('Ver-Transição1'!#REF!:'Ver-Transição1'!#REF!))</f>
         <v>#REF!</v>
       </c>
@@ -8167,38 +8264,38 @@
       <c r="A30" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="27" t="e">
+      <c r="B30" s="24" t="e">
         <f>('Ver-Construção1'!$G$18/SUM('Ver-Construção1'!$G$18:'Ver-Construção1'!$J$18))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C30" s="27" t="e">
+      <c r="C30" s="24" t="e">
         <f>('Ver-Construção1'!$H$18/SUM('Ver-Construção1'!$G$18:'Ver-Construção1'!$J$18))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D30" s="27" t="e">
+      <c r="D30" s="24" t="e">
         <f>('Ver-Construção1'!$I$18/SUM('Ver-Construção1'!$G$18:'Ver-Construção1'!$J$18))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E30" s="27" t="e">
+      <c r="E30" s="24" t="e">
         <f>('Ver-Construção1'!$J$18/SUM('Ver-Construção1'!$G$18:'Ver-Construção1'!$J$18))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M30" t="s">
         <v>5</v>
       </c>
-      <c r="N30" s="27" t="e">
+      <c r="N30" s="24" t="e">
         <f>('Ver-Transição1'!$G$16/SUM('Ver-Transição1'!$G$16:'Ver-Transição1'!$J$16))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O30" s="27" t="e">
+      <c r="O30" s="24" t="e">
         <f>('Ver-Transição1'!$H$16/SUM('Ver-Transição1'!$G$16:'Ver-Transição1'!$J$16))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P30" s="27" t="e">
+      <c r="P30" s="24" t="e">
         <f>('Ver-Transição1'!$I$16/SUM('Ver-Transição1'!$G$16:'Ver-Transição1'!$J$16))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q30" s="27" t="e">
+      <c r="Q30" s="24" t="e">
         <f>('Ver-Transição1'!$J$16/SUM('Ver-Transição1'!$G$16:'Ver-Transição1'!$J$16))</f>
         <v>#DIV/0!</v>
       </c>
@@ -8207,38 +8304,38 @@
       <c r="A31" t="s">
         <v>8</v>
       </c>
-      <c r="B31" s="27" t="e">
+      <c r="B31" s="24" t="e">
         <f>('Ver-Construção1'!$G$24/SUM('Ver-Construção1'!$G$24:'Ver-Construção1'!$J$24))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C31" s="27" t="e">
+      <c r="C31" s="24" t="e">
         <f>('Ver-Construção1'!$H$24/SUM('Ver-Construção1'!$G$24:'Ver-Construção1'!$J$24))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D31" s="27" t="e">
+      <c r="D31" s="24" t="e">
         <f>('Ver-Construção1'!$I$24/SUM('Ver-Construção1'!$G$24:'Ver-Construção1'!$J$24))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E31" s="27" t="e">
+      <c r="E31" s="24" t="e">
         <f>('Ver-Construção1'!$J$24/SUM('Ver-Construção1'!$G$24:'Ver-Construção1'!$J$24))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M31" t="s">
         <v>6</v>
       </c>
-      <c r="N31" s="27" t="e">
+      <c r="N31" s="24" t="e">
         <f>('Ver-Transição1'!$G$18/SUM('Ver-Transição1'!$G$18:'Ver-Transição1'!$J$18))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O31" s="27" t="e">
+      <c r="O31" s="24" t="e">
         <f>('Ver-Transição1'!$H$18/SUM('Ver-Transição1'!$G$18:'Ver-Transição1'!$J$18))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P31" s="27" t="e">
+      <c r="P31" s="24" t="e">
         <f>('Ver-Transição1'!$I$18/SUM('Ver-Transição1'!$G$18:'Ver-Transição1'!$J$18))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q31" s="27" t="e">
+      <c r="Q31" s="24" t="e">
         <f>('Ver-Transição1'!$J$18/SUM('Ver-Transição1'!$G$18:'Ver-Transição1'!$J$18))</f>
         <v>#DIV/0!</v>
       </c>
@@ -8247,38 +8344,38 @@
       <c r="A32" t="s">
         <v>13</v>
       </c>
-      <c r="B32" s="27" t="e">
+      <c r="B32" s="24" t="e">
         <f>('Ver-Construção1'!$G$30/SUM('Ver-Construção1'!$G$30:'Ver-Construção1'!$J$30))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C32" s="27" t="e">
+      <c r="C32" s="24" t="e">
         <f>('Ver-Construção1'!$H$30/SUM('Ver-Construção1'!$G$30:'Ver-Construção1'!$J$30))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D32" s="27" t="e">
+      <c r="D32" s="24" t="e">
         <f>('Ver-Construção1'!$I$30/SUM('Ver-Construção1'!$G$30:'Ver-Construção1'!$J$30))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E32" s="27" t="e">
+      <c r="E32" s="24" t="e">
         <f>('Ver-Construção1'!$J$30/SUM('Ver-Construção1'!$G$30:'Ver-Construção1'!$J$30))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M32" t="s">
         <v>8</v>
       </c>
-      <c r="N32" s="27" t="e">
+      <c r="N32" s="24" t="e">
         <f>('Ver-Transição1'!$G$23/SUM('Ver-Transição1'!$G$23:'Ver-Transição1'!$J$23))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O32" s="27" t="e">
+      <c r="O32" s="24" t="e">
         <f>('Ver-Transição1'!$H$23/SUM('Ver-Transição1'!$G$23:'Ver-Transição1'!$J$23))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P32" s="27" t="e">
+      <c r="P32" s="24" t="e">
         <f>('Ver-Transição1'!$I$23/SUM('Ver-Transição1'!$G$23:'Ver-Transição1'!$J$23))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q32" s="27" t="e">
+      <c r="Q32" s="24" t="e">
         <f>('Ver-Transição1'!$J$23/SUM('Ver-Transição1'!$G$23:'Ver-Transição1'!$J$23))</f>
         <v>#DIV/0!</v>
       </c>
@@ -8287,38 +8384,38 @@
       <c r="A33" t="s">
         <v>56</v>
       </c>
-      <c r="B33" s="27" t="e">
+      <c r="B33" s="24" t="e">
         <f>('Ver-Construção1'!$G$36/SUM('Ver-Construção1'!$G$36:'Ver-Construção1'!$J$36))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C33" s="27" t="e">
+      <c r="C33" s="24" t="e">
         <f>('Ver-Construção1'!$H$36/SUM('Ver-Construção1'!$G$36:'Ver-Construção1'!$J$36))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D33" s="27" t="e">
+      <c r="D33" s="24" t="e">
         <f>('Ver-Construção1'!$I$36/SUM('Ver-Construção1'!$G$36:'Ver-Construção1'!$J$36))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E33" s="27" t="e">
+      <c r="E33" s="24" t="e">
         <f>('Ver-Construção1'!$J$36/SUM('Ver-Construção1'!$G$36:'Ver-Construção1'!$J$36))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M33" t="s">
         <v>9</v>
       </c>
-      <c r="N33" s="27" t="e">
+      <c r="N33" s="24" t="e">
         <f>('Ver-Transição1'!$G$26/SUM('Ver-Transição1'!$G$26:'Ver-Transição1'!$J$26))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O33" s="27" t="e">
+      <c r="O33" s="24" t="e">
         <f>('Ver-Transição1'!$H$26/SUM('Ver-Transição1'!$G$26:'Ver-Transição1'!$J$26))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P33" s="27" t="e">
+      <c r="P33" s="24" t="e">
         <f>('Ver-Transição1'!$I$26/SUM('Ver-Transição1'!$G$26:'Ver-Transição1'!$J$26))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q33" s="27" t="e">
+      <c r="Q33" s="24" t="e">
         <f>('Ver-Transição1'!$J$26/SUM('Ver-Transição1'!$G$26:'Ver-Transição1'!$J$26))</f>
         <v>#DIV/0!</v>
       </c>
@@ -8327,38 +8424,38 @@
       <c r="A34" t="s">
         <v>15</v>
       </c>
-      <c r="B34" s="27" t="e">
+      <c r="B34" s="24" t="e">
         <f>('Ver-Construção1'!$G$41/SUM('Ver-Construção1'!$G$41:'Ver-Construção1'!$J$41))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C34" s="27" t="e">
+      <c r="C34" s="24" t="e">
         <f>('Ver-Construção1'!$H$41/SUM('Ver-Construção1'!$G$41:'Ver-Construção1'!$J$41))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D34" s="27" t="e">
+      <c r="D34" s="24" t="e">
         <f>('Ver-Construção1'!$I$41/SUM('Ver-Construção1'!$G$41:'Ver-Construção1'!$J$41))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E34" s="27" t="e">
+      <c r="E34" s="24" t="e">
         <f>('Ver-Construção1'!$J$41/SUM('Ver-Construção1'!$G$41:'Ver-Construção1'!$J$41))</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M34" t="s">
         <v>10</v>
       </c>
-      <c r="N34" s="26" t="e">
+      <c r="N34" s="23" t="e">
         <f>('Ver-Transição1'!$G$29/SUM('Ver-Transição1'!$G$29:'Ver-Transição1'!$J$29))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O34" s="27" t="e">
+      <c r="O34" s="24" t="e">
         <f>('Ver-Transição1'!$H$29/SUM('Ver-Transição1'!$G$29:'Ver-Transição1'!$J$29))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P34" s="27" t="e">
+      <c r="P34" s="24" t="e">
         <f>('Ver-Transição1'!$I$29/SUM('Ver-Transição1'!$G$29:'Ver-Transição1'!$J$29))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q34" s="27" t="e">
+      <c r="Q34" s="24" t="e">
         <f>('Ver-Transição1'!$J$29/SUM('Ver-Transição1'!$G$29:'Ver-Transição1'!$J$29))</f>
         <v>#DIV/0!</v>
       </c>
@@ -8367,19 +8464,19 @@
       <c r="M35" t="s">
         <v>13</v>
       </c>
-      <c r="N35" s="27" t="e">
+      <c r="N35" s="24" t="e">
         <f>('Ver-Transição1'!$G$31/SUM('Ver-Transição1'!$G$31:'Ver-Transição1'!$J$31))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O35" s="27" t="e">
+      <c r="O35" s="24" t="e">
         <f>('Ver-Transição1'!$H$31/SUM('Ver-Transição1'!$G$31:'Ver-Transição1'!$J$31))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P35" s="27" t="e">
+      <c r="P35" s="24" t="e">
         <f>('Ver-Transição1'!$I$31/SUM('Ver-Transição1'!$G$31:'Ver-Transição1'!$J$31))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q35" s="27" t="e">
+      <c r="Q35" s="24" t="e">
         <f>('Ver-Transição1'!$J$31/SUM('Ver-Transição1'!$G$31:'Ver-Transição1'!$J$31))</f>
         <v>#DIV/0!</v>
       </c>
@@ -8388,19 +8485,19 @@
       <c r="M36" t="s">
         <v>56</v>
       </c>
-      <c r="N36" s="27" t="e">
+      <c r="N36" s="24" t="e">
         <f>('Ver-Transição1'!$G$37/SUM('Ver-Transição1'!$G$37:'Ver-Transição1'!$J$37))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O36" s="27" t="e">
+      <c r="O36" s="24" t="e">
         <f>('Ver-Transição1'!$H$37/SUM('Ver-Transição1'!$G$37:'Ver-Transição1'!$J$37))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P36" s="27" t="e">
+      <c r="P36" s="24" t="e">
         <f>('Ver-Transição1'!$I$37/SUM('Ver-Transição1'!$G$37:'Ver-Transição1'!$J$37))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q36" s="27" t="e">
+      <c r="Q36" s="24" t="e">
         <f>('Ver-Transição1'!$J$37/SUM('Ver-Transição1'!$G$37:'Ver-Transição1'!$J$37))</f>
         <v>#DIV/0!</v>
       </c>
@@ -8409,19 +8506,19 @@
       <c r="M37" t="s">
         <v>15</v>
       </c>
-      <c r="N37" s="27" t="e">
+      <c r="N37" s="24" t="e">
         <f>('Ver-Transição1'!$G$42/SUM('Ver-Transição1'!$G$42:'Ver-Transição1'!$J$42))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O37" s="27" t="e">
+      <c r="O37" s="24" t="e">
         <f>('Ver-Transição1'!$H$42/SUM('Ver-Transição1'!$G$42:'Ver-Transição1'!$J$42))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="P37" s="27" t="e">
+      <c r="P37" s="24" t="e">
         <f>('Ver-Transição1'!$I$42/SUM('Ver-Transição1'!$G$42:'Ver-Transição1'!$J$42))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q37" s="27" t="e">
+      <c r="Q37" s="24" t="e">
         <f>('Ver-Transição1'!$J$42/SUM('Ver-Transição1'!$G$42:'Ver-Transição1'!$J$42))</f>
         <v>#DIV/0!</v>
       </c>
@@ -8440,717 +8537,842 @@
   <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="21.140625" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="84" style="2" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.85546875" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="4.42578125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="6.140625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="6" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="76.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="5" max="6" width="47.5703125" customWidth="1"/>
+    <col min="7" max="7" width="7.5703125" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" customWidth="1"/>
+    <col min="9" max="10" width="7.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:10" ht="18">
+      <c r="A1" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-    </row>
-    <row r="2" spans="1:10" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A2" s="33" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+    </row>
+    <row r="2" spans="1:10" ht="32.1" customHeight="1" thickBot="1">
+      <c r="A2" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="16" t="s">
+      <c r="B2" s="55"/>
+      <c r="C2" s="66" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="40"/>
-      <c r="F2" s="21" t="e">
+      <c r="E2" s="57"/>
+      <c r="F2" s="68">
         <f>COUNTIF(D5:D41,"Sim")/(COUNTA(D5:D41)-COUNTIF(D5:D41,"NA"))</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A3" s="33" t="s">
+        <v>0.96153846153846156</v>
+      </c>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+    </row>
+    <row r="3" spans="1:10" ht="32.1" customHeight="1" thickBot="1">
+      <c r="A3" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="55"/>
+      <c r="C3" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="37"/>
-      <c r="F3" s="38"/>
-    </row>
-    <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="6" t="s">
+      <c r="E3" s="59"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+    </row>
+    <row r="4" spans="1:10" ht="30">
+      <c r="A4" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="41" t="s">
         <v>27</v>
       </c>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
     </row>
     <row r="5" spans="1:10" ht="15">
-      <c r="A5" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="10" t="s">
+      <c r="A5" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="43"/>
+      <c r="C5" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5">
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="42">
         <f>COUNTIF(D6,"Sim")</f>
-        <v>0</v>
-      </c>
-      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="42">
         <f>COUNTIF(D6,"Parcialmente")</f>
         <v>0</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="42">
         <f>COUNTIF(D6,"Não")</f>
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="42">
         <f>COUNTIF(D6,"NA")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15">
-      <c r="A6" s="35"/>
-      <c r="B6" s="5">
+      <c r="A6" s="62"/>
+      <c r="B6" s="46">
         <v>1</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-    </row>
-    <row r="7" spans="1:10" ht="15" customHeight="1">
-      <c r="A7" s="34" t="s">
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+    </row>
+    <row r="7" spans="1:10" ht="15">
+      <c r="A7" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="43"/>
+      <c r="C7" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7">
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="42">
         <f>COUNTIF(D8:D12,"Sim")</f>
-        <v>0</v>
-      </c>
-      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="H7" s="42">
         <f>COUNTIF(D8:D12,"Parcialmente")</f>
         <v>0</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="42">
         <f>COUNTIF(D8:D12,"Não")</f>
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="42">
         <f>COUNTIF(D8:D12,"NA")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1">
-      <c r="A8" s="31"/>
-      <c r="B8" s="22">
+    <row r="8" spans="1:10" ht="30">
+      <c r="A8" s="63"/>
+      <c r="B8" s="49">
         <v>2</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="47"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
     </row>
     <row r="9" spans="1:10" ht="15">
-      <c r="A9" s="31"/>
-      <c r="B9" s="5">
+      <c r="A9" s="63"/>
+      <c r="B9" s="46">
         <v>3</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
     </row>
     <row r="10" spans="1:10" ht="15">
-      <c r="A10" s="31"/>
-      <c r="B10" s="5">
+      <c r="A10" s="63"/>
+      <c r="B10" s="46">
         <v>4</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
     </row>
     <row r="11" spans="1:10" s="1" customFormat="1" ht="15">
-      <c r="A11" s="31"/>
-      <c r="B11" s="5">
+      <c r="A11" s="63"/>
+      <c r="B11" s="46">
         <v>5</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-    </row>
-    <row r="12" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A12" s="31"/>
-      <c r="B12" s="5">
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+    </row>
+    <row r="12" spans="1:10" ht="30">
+      <c r="A12" s="63"/>
+      <c r="B12" s="46">
         <v>6</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
     </row>
     <row r="13" spans="1:10" ht="15">
-      <c r="A13" s="31"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="10" t="s">
+      <c r="A13" s="63"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13">
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="42">
         <f>COUNTIF(D14:D18,"Sim")</f>
-        <v>0</v>
-      </c>
-      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="H13" s="42">
         <f>COUNTIF(D14:D18,"Parcialmente")</f>
-        <v>0</v>
-      </c>
-      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="I13" s="42">
         <f>COUNTIF(D14:D18,"Não")</f>
         <v>0</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="42">
         <f>COUNTIF(D14:D18,"NA")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="30">
-      <c r="A14" s="31"/>
-      <c r="B14" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="45">
+      <c r="A14" s="63"/>
+      <c r="B14" s="52">
         <v>7</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>120</v>
-      </c>
+      <c r="D14" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
     </row>
     <row r="15" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A15" s="31"/>
-      <c r="B15" s="5">
+      <c r="A15" s="63"/>
+      <c r="B15" s="46">
         <v>8</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
     </row>
     <row r="16" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A16" s="31"/>
-      <c r="B16" s="5">
+      <c r="A16" s="63"/>
+      <c r="B16" s="46">
         <v>9</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
     </row>
     <row r="17" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A17" s="31"/>
-      <c r="B17" s="23">
+      <c r="A17" s="63"/>
+      <c r="B17" s="52">
         <v>10</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="48" t="s">
         <v>118</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="47" t="s">
         <v>121</v>
       </c>
-      <c r="F17" s="8"/>
-    </row>
-    <row r="18" spans="1:10" s="1" customFormat="1" ht="15">
-      <c r="A18" s="31"/>
-      <c r="B18" s="5">
+      <c r="F17" s="47"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+    </row>
+    <row r="18" spans="1:10" s="1" customFormat="1" ht="30">
+      <c r="A18" s="63"/>
+      <c r="B18" s="46">
         <v>11</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8" t="s">
+      <c r="E18" s="47"/>
+      <c r="F18" s="47" t="s">
         <v>122</v>
       </c>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="31"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="10" t="s">
+      <c r="A19" s="63"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19">
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="42">
         <f>COUNTIF(D20:D21,"Sim")</f>
-        <v>0</v>
-      </c>
-      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="H19" s="42">
         <f>COUNTIF(D20:D21,"Parcialmente")</f>
         <v>0</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="42">
         <f>COUNTIF(D20:D21,"Não")</f>
         <v>0</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="42">
         <f>COUNTIF(D20:D21,"NA")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="30">
-      <c r="A20" s="31"/>
-      <c r="B20" s="23">
+      <c r="A20" s="63"/>
+      <c r="B20" s="52">
         <v>12</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-    </row>
-    <row r="21" spans="1:10" ht="30">
-      <c r="A21" s="31"/>
-      <c r="B21" s="5">
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+    </row>
+    <row r="21" spans="1:10" ht="45">
+      <c r="A21" s="63"/>
+      <c r="B21" s="46">
         <v>13</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="47" t="s">
         <v>80</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="31"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="10" t="s">
+      <c r="A22" s="63"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22">
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="42">
         <f>COUNTIF(D23:D24,"Sim")</f>
-        <v>0</v>
-      </c>
-      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="H22" s="42">
         <f>COUNTIF(D23:D24,"Parcialmente")</f>
         <v>0</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="42">
         <f>COUNTIF(D23:D24,"Não")</f>
         <v>0</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="42">
         <f>COUNTIF(D23:D24,"NA")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="30">
-      <c r="A23" s="31"/>
-      <c r="B23" s="23">
+    <row r="23" spans="1:10" ht="45">
+      <c r="A23" s="63"/>
+      <c r="B23" s="52">
         <v>14</v>
       </c>
-      <c r="C23" s="24" t="s">
+      <c r="C23" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8" t="s">
+      <c r="E23" s="47"/>
+      <c r="F23" s="47" t="s">
         <v>123</v>
       </c>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
     </row>
     <row r="24" spans="1:10" ht="15">
-      <c r="A24" s="31"/>
-      <c r="B24" s="5">
+      <c r="A24" s="63"/>
+      <c r="B24" s="46">
         <v>15</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42"/>
     </row>
     <row r="25" spans="1:10" ht="15">
-      <c r="A25" s="31"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="10" t="s">
+      <c r="A25" s="63"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25">
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="42">
         <f>COUNTIF(D26:D27,"Sim")</f>
         <v>0</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="42">
         <f>COUNTIF(D26:D27,"Parcialmente")</f>
         <v>0</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="42">
         <f>COUNTIF(D26:D27,"Não")</f>
         <v>0</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="42">
         <f>COUNTIF(D26:D27,"NA")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="30">
-      <c r="A26" s="31"/>
-      <c r="B26" s="23">
+      <c r="A26" s="63"/>
+      <c r="B26" s="52">
         <v>16</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="48" t="s">
         <v>118</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="F26" s="8"/>
-    </row>
-    <row r="27" spans="1:10" ht="15">
-      <c r="A27" s="31"/>
-      <c r="B27" s="5">
+      <c r="F26" s="47"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="42"/>
+    </row>
+    <row r="27" spans="1:10" ht="30">
+      <c r="A27" s="63"/>
+      <c r="B27" s="46">
         <v>17</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="48" t="s">
         <v>118</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="F27" s="8"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="42"/>
     </row>
     <row r="28" spans="1:10" ht="15">
-      <c r="A28" s="31"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="10" t="s">
+      <c r="A28" s="63"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28">
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="42">
         <f>COUNTIF(D29:D36,"Sim")</f>
-        <v>0</v>
-      </c>
-      <c r="H28">
+        <v>8</v>
+      </c>
+      <c r="H28" s="42">
         <f>COUNTIF(D29:D36,"Parcialmente")</f>
         <v>0</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="42">
         <f>COUNTIF(D29:D36,"Não")</f>
         <v>0</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="42">
         <f>COUNTIF(D29:D36,"NA")</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="30">
-      <c r="A29" s="31"/>
-      <c r="B29" s="23">
+      <c r="A29" s="63"/>
+      <c r="B29" s="52">
         <v>21</v>
       </c>
-      <c r="C29" s="24" t="s">
+      <c r="C29" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
     </row>
     <row r="30" spans="1:10" ht="15">
-      <c r="A30" s="31"/>
-      <c r="B30" s="5">
+      <c r="A30" s="63"/>
+      <c r="B30" s="46">
         <v>22</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="42"/>
     </row>
     <row r="31" spans="1:10" ht="15">
-      <c r="A31" s="31"/>
-      <c r="B31" s="5">
+      <c r="A31" s="63"/>
+      <c r="B31" s="46">
         <v>23</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
     </row>
     <row r="32" spans="1:10" ht="15">
-      <c r="A32" s="31"/>
-      <c r="B32" s="5">
+      <c r="A32" s="63"/>
+      <c r="B32" s="46">
         <v>24</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8" t="s">
-        <v>126</v>
-      </c>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
     </row>
     <row r="33" spans="1:10" ht="15">
-      <c r="A33" s="31"/>
-      <c r="B33" s="5">
+      <c r="A33" s="63"/>
+      <c r="B33" s="46">
         <v>25</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
     </row>
     <row r="34" spans="1:10" ht="30">
-      <c r="A34" s="31"/>
-      <c r="B34" s="5">
+      <c r="A34" s="63"/>
+      <c r="B34" s="46">
         <v>26</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="F34" s="8"/>
-    </row>
-    <row r="35" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A35" s="31"/>
-      <c r="B35" s="5">
+      <c r="E34" s="42"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
+    </row>
+    <row r="35" spans="1:10" ht="30">
+      <c r="A35" s="63"/>
+      <c r="B35" s="46">
         <v>27</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-    </row>
-    <row r="36" spans="1:10" ht="15">
-      <c r="A36" s="31"/>
-      <c r="B36" s="5">
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="42"/>
+    </row>
+    <row r="36" spans="1:10" ht="30">
+      <c r="A36" s="63"/>
+      <c r="B36" s="46">
         <v>28</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8" t="s">
+      <c r="E36" s="47"/>
+      <c r="F36" s="47" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" ht="15" customHeight="1">
-      <c r="A37" s="29" t="s">
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+    </row>
+    <row r="37" spans="1:10" ht="15">
+      <c r="A37" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="10" t="s">
+      <c r="B37" s="43"/>
+      <c r="C37" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37">
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="42">
         <f>COUNTIF(D38:D41,"Sim")</f>
-        <v>0</v>
-      </c>
-      <c r="H37">
+        <v>4</v>
+      </c>
+      <c r="H37" s="42">
         <f>COUNTIF(D38:D41,"Parcialmente")</f>
         <v>0</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="42">
         <f>COUNTIF(D38:D41,"Não")</f>
         <v>0</v>
       </c>
-      <c r="J37">
+      <c r="J37" s="42">
         <f>COUNTIF(D38:D41,"NA")</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="30">
-      <c r="A38" s="30"/>
-      <c r="B38" s="23">
+      <c r="A38" s="65"/>
+      <c r="B38" s="52">
         <v>30</v>
       </c>
-      <c r="C38" s="24" t="s">
+      <c r="C38" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="47"/>
+      <c r="G38" s="42"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
     </row>
     <row r="39" spans="1:10" ht="30">
-      <c r="A39" s="30"/>
-      <c r="B39" s="5">
+      <c r="A39" s="65"/>
+      <c r="B39" s="46">
         <v>31</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="42"/>
     </row>
     <row r="40" spans="1:10" ht="15">
-      <c r="A40" s="30"/>
-      <c r="B40" s="5">
+      <c r="A40" s="65"/>
+      <c r="B40" s="46">
         <v>32</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-    </row>
-    <row r="41" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A41" s="30"/>
-      <c r="B41" s="5">
+      <c r="E40" s="47"/>
+      <c r="F40" s="47"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="42"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="42"/>
+    </row>
+    <row r="41" spans="1:10" ht="30">
+      <c r="A41" s="65"/>
+      <c r="B41" s="46">
         <v>33</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8" t="s">
-        <v>127</v>
-      </c>
+      <c r="E41" s="47"/>
+      <c r="F41" s="47"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -9190,41 +9412,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:10" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="39" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="40"/>
-      <c r="F2" s="21" t="e">
+      <c r="E2" s="34"/>
+      <c r="F2" s="19" t="e">
         <f>COUNTIF(D5:D41,"Sim")/(COUNTA(D5:D42)-COUNTIF(D5:D42,"NA"))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="33"/>
+      <c r="B3" s="32"/>
       <c r="C3" s="13"/>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="43"/>
-      <c r="F3" s="44"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="37"/>
     </row>
     <row r="4" spans="1:10" ht="15">
       <c r="A4" s="6" t="s">
@@ -9247,7 +9469,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="25" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="9"/>
@@ -9259,7 +9481,7 @@
       <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:10" ht="15">
-      <c r="A6" s="31"/>
+      <c r="A6" s="26"/>
       <c r="B6" s="5">
         <v>1</v>
       </c>
@@ -9287,7 +9509,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="15">
-      <c r="A7" s="31"/>
+      <c r="A7" s="26"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
         <v>3</v>
@@ -9297,7 +9519,7 @@
       <c r="F7" s="12"/>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A8" s="31"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="5">
         <v>2</v>
       </c>
@@ -9325,7 +9547,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A9" s="31"/>
+      <c r="A9" s="26"/>
       <c r="B9" s="5">
         <v>3</v>
       </c>
@@ -9341,7 +9563,7 @@
       <c r="J9"/>
     </row>
     <row r="10" spans="1:10" ht="15">
-      <c r="A10" s="31"/>
+      <c r="A10" s="26"/>
       <c r="B10" s="9"/>
       <c r="C10" s="10" t="s">
         <v>97</v>
@@ -9351,11 +9573,11 @@
       <c r="F10" s="12"/>
     </row>
     <row r="11" spans="1:10" ht="30">
-      <c r="A11" s="31"/>
-      <c r="B11" s="23">
+      <c r="A11" s="26"/>
+      <c r="B11" s="20">
         <v>4</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="21" t="s">
         <v>110</v>
       </c>
       <c r="D11" s="3"/>
@@ -9379,11 +9601,11 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="30">
-      <c r="A12" s="31"/>
-      <c r="B12" s="23">
+      <c r="A12" s="26"/>
+      <c r="B12" s="20">
         <v>5</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="21" t="s">
         <v>81</v>
       </c>
       <c r="D12" s="3"/>
@@ -9391,7 +9613,7 @@
       <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:10" ht="30">
-      <c r="A13" s="31"/>
+      <c r="A13" s="26"/>
       <c r="B13" s="5">
         <v>6</v>
       </c>
@@ -9403,7 +9625,7 @@
       <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:10" ht="30">
-      <c r="A14" s="31"/>
+      <c r="A14" s="26"/>
       <c r="B14" s="5">
         <v>7</v>
       </c>
@@ -9415,7 +9637,7 @@
       <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:10" ht="15">
-      <c r="A15" s="31"/>
+      <c r="A15" s="26"/>
       <c r="B15" s="9"/>
       <c r="C15" s="10" t="s">
         <v>4</v>
@@ -9425,7 +9647,7 @@
       <c r="F15" s="12"/>
     </row>
     <row r="16" spans="1:10" ht="15">
-      <c r="A16" s="31"/>
+      <c r="A16" s="26"/>
       <c r="B16" s="5">
         <v>7</v>
       </c>
@@ -9453,7 +9675,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="25" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="9"/>
@@ -9465,7 +9687,7 @@
       <c r="F17" s="12"/>
     </row>
     <row r="18" spans="1:10" ht="30">
-      <c r="A18" s="31"/>
+      <c r="A18" s="26"/>
       <c r="B18" s="5">
         <v>9</v>
       </c>
@@ -9493,11 +9715,11 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="30">
-      <c r="A19" s="31"/>
-      <c r="B19" s="23">
+      <c r="A19" s="26"/>
+      <c r="B19" s="20">
         <v>10</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="21" t="s">
         <v>51</v>
       </c>
       <c r="D19" s="3"/>
@@ -9505,7 +9727,7 @@
       <c r="F19" s="8"/>
     </row>
     <row r="20" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A20" s="31"/>
+      <c r="A20" s="26"/>
       <c r="B20" s="5">
         <v>11</v>
       </c>
@@ -9517,7 +9739,7 @@
       <c r="F20" s="8"/>
     </row>
     <row r="21" spans="1:10" ht="45">
-      <c r="A21" s="31"/>
+      <c r="A21" s="26"/>
       <c r="B21" s="5">
         <v>12</v>
       </c>
@@ -9529,7 +9751,7 @@
       <c r="F21" s="8"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="25" t="s">
         <v>19</v>
       </c>
       <c r="B22" s="9"/>
@@ -9541,7 +9763,7 @@
       <c r="F22" s="12"/>
     </row>
     <row r="23" spans="1:10" ht="30">
-      <c r="A23" s="31"/>
+      <c r="A23" s="26"/>
       <c r="B23" s="5">
         <v>17</v>
       </c>
@@ -9569,7 +9791,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="30">
-      <c r="A24" s="31"/>
+      <c r="A24" s="26"/>
       <c r="B24" s="5">
         <v>18</v>
       </c>
@@ -9581,7 +9803,7 @@
       <c r="F24" s="8"/>
     </row>
     <row r="25" spans="1:10" ht="30">
-      <c r="A25" s="31"/>
+      <c r="A25" s="26"/>
       <c r="B25" s="5">
         <v>19</v>
       </c>
@@ -9593,7 +9815,7 @@
       <c r="F25" s="8"/>
     </row>
     <row r="26" spans="1:10" ht="15">
-      <c r="A26" s="31"/>
+      <c r="A26" s="26"/>
       <c r="B26" s="5">
         <v>21</v>
       </c>
@@ -9605,7 +9827,7 @@
       <c r="F26" s="8"/>
     </row>
     <row r="27" spans="1:10" ht="15">
-      <c r="A27" s="31"/>
+      <c r="A27" s="26"/>
       <c r="B27" s="5">
         <v>22</v>
       </c>
@@ -9617,7 +9839,7 @@
       <c r="F27" s="8"/>
     </row>
     <row r="28" spans="1:10" ht="15">
-      <c r="A28" s="41" t="s">
+      <c r="A28" s="27" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="9"/>
@@ -9629,7 +9851,7 @@
       <c r="F28" s="12"/>
     </row>
     <row r="29" spans="1:10" ht="15">
-      <c r="A29" s="41"/>
+      <c r="A29" s="27"/>
       <c r="B29" s="5">
         <v>23</v>
       </c>
@@ -9657,7 +9879,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="15">
-      <c r="A30" s="41"/>
+      <c r="A30" s="27"/>
       <c r="B30" s="5">
         <v>24</v>
       </c>
@@ -9669,7 +9891,7 @@
       <c r="F30" s="8"/>
     </row>
     <row r="31" spans="1:10" ht="30">
-      <c r="A31" s="41"/>
+      <c r="A31" s="27"/>
       <c r="B31" s="5">
         <v>25</v>
       </c>
@@ -9681,7 +9903,7 @@
       <c r="F31" s="8"/>
     </row>
     <row r="32" spans="1:10" ht="15">
-      <c r="A32" s="41"/>
+      <c r="A32" s="27"/>
       <c r="B32" s="5">
         <v>26</v>
       </c>
@@ -9693,7 +9915,7 @@
       <c r="F32" s="8"/>
     </row>
     <row r="33" spans="1:10" ht="15">
-      <c r="A33" s="41"/>
+      <c r="A33" s="27"/>
       <c r="B33" s="5">
         <v>27</v>
       </c>
@@ -9705,7 +9927,7 @@
       <c r="F33" s="8"/>
     </row>
     <row r="34" spans="1:10" ht="15">
-      <c r="A34" s="41"/>
+      <c r="A34" s="27"/>
       <c r="B34" s="5">
         <v>28</v>
       </c>
@@ -9717,7 +9939,7 @@
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1">
-      <c r="A35" s="29" t="s">
+      <c r="A35" s="28" t="s">
         <v>30</v>
       </c>
       <c r="B35" s="9"/>
@@ -9729,7 +9951,7 @@
       <c r="F35" s="12"/>
     </row>
     <row r="36" spans="1:10" ht="30">
-      <c r="A36" s="30"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="5">
         <v>29</v>
       </c>
@@ -9757,7 +9979,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="15">
-      <c r="A37" s="30"/>
+      <c r="A37" s="29"/>
       <c r="B37" s="5">
         <v>30</v>
       </c>
@@ -9769,7 +9991,7 @@
       <c r="F37" s="8"/>
     </row>
     <row r="38" spans="1:10" ht="30">
-      <c r="A38" s="30"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="5">
         <v>31</v>
       </c>
@@ -9781,7 +10003,7 @@
       <c r="F38" s="8"/>
     </row>
     <row r="39" spans="1:10" ht="15">
-      <c r="A39" s="30"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="9"/>
       <c r="C39" s="10" t="s">
         <v>15</v>
@@ -9791,7 +10013,7 @@
       <c r="F39" s="12"/>
     </row>
     <row r="40" spans="1:10" ht="15">
-      <c r="A40" s="30"/>
+      <c r="A40" s="29"/>
       <c r="B40" s="5">
         <v>32</v>
       </c>
@@ -9819,7 +10041,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="15">
-      <c r="A41" s="30"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="5">
         <v>33</v>
       </c>
@@ -9871,41 +10093,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:10" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="39" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="40"/>
-      <c r="F2" s="21" t="e">
+      <c r="E2" s="34"/>
+      <c r="F2" s="19" t="e">
         <f>COUNTIF(D5:D42,"Sim")/(COUNTA(D5:D41)-COUNTIF(D5:D41,"NA"))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="33"/>
+      <c r="B3" s="32"/>
       <c r="C3" s="13"/>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="43"/>
-      <c r="F3" s="44"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="37"/>
     </row>
     <row r="4" spans="1:10" ht="15">
       <c r="A4" s="6" t="s">
@@ -9928,7 +10150,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="25" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="9"/>
@@ -9940,7 +10162,7 @@
       <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:10" ht="15">
-      <c r="A6" s="31"/>
+      <c r="A6" s="26"/>
       <c r="B6" s="5">
         <v>1</v>
       </c>
@@ -9968,7 +10190,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="15">
-      <c r="A7" s="31"/>
+      <c r="A7" s="26"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
         <v>3</v>
@@ -9978,7 +10200,7 @@
       <c r="F7" s="12"/>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A8" s="31"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="5">
         <v>2</v>
       </c>
@@ -10006,7 +10228,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="15">
-      <c r="A9" s="31"/>
+      <c r="A9" s="26"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10" t="s">
         <v>97</v>
@@ -10016,7 +10238,7 @@
       <c r="F9" s="12"/>
     </row>
     <row r="10" spans="1:10" ht="30">
-      <c r="A10" s="31"/>
+      <c r="A10" s="26"/>
       <c r="B10" s="5">
         <v>3</v>
       </c>
@@ -10044,7 +10266,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="30">
-      <c r="A11" s="31"/>
+      <c r="A11" s="26"/>
       <c r="B11" s="5">
         <v>4</v>
       </c>
@@ -10056,7 +10278,7 @@
       <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A12" s="31"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="5">
         <v>5</v>
       </c>
@@ -10068,7 +10290,7 @@
       <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:10" ht="15">
-      <c r="A13" s="31"/>
+      <c r="A13" s="26"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10" t="s">
         <v>4</v>
@@ -10078,7 +10300,7 @@
       <c r="F13" s="12"/>
     </row>
     <row r="14" spans="1:10" ht="15">
-      <c r="A14" s="31"/>
+      <c r="A14" s="26"/>
       <c r="B14" s="5">
         <v>6</v>
       </c>
@@ -10106,7 +10328,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="25" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="9"/>
@@ -10118,7 +10340,7 @@
       <c r="F15" s="12"/>
     </row>
     <row r="16" spans="1:10" ht="15">
-      <c r="A16" s="31"/>
+      <c r="A16" s="26"/>
       <c r="B16" s="5">
         <v>8</v>
       </c>
@@ -10146,7 +10368,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="25" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="9"/>
@@ -10158,7 +10380,7 @@
       <c r="F17" s="12"/>
     </row>
     <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="31"/>
+      <c r="A18" s="26"/>
       <c r="B18" s="5">
         <v>11</v>
       </c>
@@ -10186,7 +10408,7 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="30">
-      <c r="A19" s="31"/>
+      <c r="A19" s="26"/>
       <c r="B19" s="5">
         <v>13</v>
       </c>
@@ -10198,7 +10420,7 @@
       <c r="F19" s="8"/>
     </row>
     <row r="20" spans="1:10" ht="30">
-      <c r="A20" s="31"/>
+      <c r="A20" s="26"/>
       <c r="B20" s="5">
         <v>14</v>
       </c>
@@ -10210,7 +10432,7 @@
       <c r="F20" s="8"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="31"/>
+      <c r="A21" s="26"/>
       <c r="B21" s="5">
         <v>15</v>
       </c>
@@ -10222,7 +10444,7 @@
       <c r="F21" s="8"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="31"/>
+      <c r="A22" s="26"/>
       <c r="B22" s="5">
         <v>16</v>
       </c>
@@ -10234,7 +10456,7 @@
       <c r="F22" s="8"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="34" t="s">
+      <c r="A23" s="25" t="s">
         <v>20</v>
       </c>
       <c r="B23" s="9"/>
@@ -10246,11 +10468,11 @@
       <c r="F23" s="12"/>
     </row>
     <row r="24" spans="1:10" ht="30">
-      <c r="A24" s="31"/>
-      <c r="B24" s="23">
+      <c r="A24" s="26"/>
+      <c r="B24" s="20">
         <v>17</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="21" t="s">
         <v>72</v>
       </c>
       <c r="D24" s="3"/>
@@ -10274,7 +10496,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="30">
-      <c r="A25" s="31"/>
+      <c r="A25" s="26"/>
       <c r="B25" s="5">
         <v>18</v>
       </c>
@@ -10286,7 +10508,7 @@
       <c r="F25" s="8"/>
     </row>
     <row r="26" spans="1:10" ht="15">
-      <c r="A26" s="31"/>
+      <c r="A26" s="26"/>
       <c r="B26" s="5">
         <v>19</v>
       </c>
@@ -10298,7 +10520,7 @@
       <c r="F26" s="8"/>
     </row>
     <row r="27" spans="1:10" ht="15">
-      <c r="A27" s="31"/>
+      <c r="A27" s="26"/>
       <c r="B27" s="5">
         <v>21</v>
       </c>
@@ -10310,7 +10532,7 @@
       <c r="F27" s="8"/>
     </row>
     <row r="28" spans="1:10" ht="15">
-      <c r="A28" s="31"/>
+      <c r="A28" s="26"/>
       <c r="B28" s="5">
         <v>22</v>
       </c>
@@ -10322,7 +10544,7 @@
       <c r="F28" s="8"/>
     </row>
     <row r="29" spans="1:10" ht="15">
-      <c r="A29" s="41" t="s">
+      <c r="A29" s="27" t="s">
         <v>11</v>
       </c>
       <c r="B29" s="9"/>
@@ -10334,7 +10556,7 @@
       <c r="F29" s="12"/>
     </row>
     <row r="30" spans="1:10" ht="15">
-      <c r="A30" s="41"/>
+      <c r="A30" s="27"/>
       <c r="B30" s="5">
         <v>24</v>
       </c>
@@ -10362,7 +10584,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="30">
-      <c r="A31" s="41"/>
+      <c r="A31" s="27"/>
       <c r="B31" s="5">
         <v>26</v>
       </c>
@@ -10374,7 +10596,7 @@
       <c r="F31" s="8"/>
     </row>
     <row r="32" spans="1:10" ht="15">
-      <c r="A32" s="41"/>
+      <c r="A32" s="27"/>
       <c r="B32" s="5">
         <v>27</v>
       </c>
@@ -10386,7 +10608,7 @@
       <c r="F32" s="8"/>
     </row>
     <row r="33" spans="1:10" ht="15">
-      <c r="A33" s="41"/>
+      <c r="A33" s="27"/>
       <c r="B33" s="5">
         <v>28</v>
       </c>
@@ -10398,7 +10620,7 @@
       <c r="F33" s="8"/>
     </row>
     <row r="34" spans="1:10" ht="15">
-      <c r="A34" s="41"/>
+      <c r="A34" s="27"/>
       <c r="B34" s="5">
         <v>29</v>
       </c>
@@ -10410,7 +10632,7 @@
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1">
-      <c r="A35" s="29" t="s">
+      <c r="A35" s="28" t="s">
         <v>30</v>
       </c>
       <c r="B35" s="9"/>
@@ -10422,7 +10644,7 @@
       <c r="F35" s="12"/>
     </row>
     <row r="36" spans="1:10" ht="30">
-      <c r="A36" s="30"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="5">
         <v>30</v>
       </c>
@@ -10450,7 +10672,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="15">
-      <c r="A37" s="30"/>
+      <c r="A37" s="29"/>
       <c r="B37" s="5">
         <v>31</v>
       </c>
@@ -10462,7 +10684,7 @@
       <c r="F37" s="8"/>
     </row>
     <row r="38" spans="1:10" ht="30">
-      <c r="A38" s="30"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="5">
         <v>32</v>
       </c>
@@ -10474,7 +10696,7 @@
       <c r="F38" s="8"/>
     </row>
     <row r="39" spans="1:10" ht="15">
-      <c r="A39" s="30"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="5"/>
       <c r="C39" s="8" t="s">
         <v>105</v>
@@ -10484,7 +10706,7 @@
       <c r="F39" s="8"/>
     </row>
     <row r="40" spans="1:10" ht="15">
-      <c r="A40" s="30"/>
+      <c r="A40" s="29"/>
       <c r="B40" s="9"/>
       <c r="C40" s="10" t="s">
         <v>15</v>
@@ -10494,7 +10716,7 @@
       <c r="F40" s="12"/>
     </row>
     <row r="41" spans="1:10" ht="15">
-      <c r="A41" s="30"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="5">
         <v>33</v>
       </c>
@@ -10522,7 +10744,7 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="15">
-      <c r="A42" s="30"/>
+      <c r="A42" s="29"/>
       <c r="B42" s="5">
         <v>34</v>
       </c>
@@ -10563,17 +10785,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:F3"/>
     <mergeCell ref="A5:A14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A17:A22"/>
     <mergeCell ref="A29:A34"/>
     <mergeCell ref="A35:A42"/>
     <mergeCell ref="A23:A28"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:F3"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23 D15 D17 D40 D35 D29" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -10603,41 +10825,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:10" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="39" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="40"/>
-      <c r="F2" s="21" t="e">
+      <c r="E2" s="34"/>
+      <c r="F2" s="19" t="e">
         <f>COUNTIF(D5:D43,"Sim")/(COUNTA(D5:D43)-COUNTIF(D5:D43,"NA"))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="33"/>
+      <c r="B3" s="32"/>
       <c r="C3" s="13"/>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="43"/>
-      <c r="F3" s="44"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="37"/>
     </row>
     <row r="4" spans="1:10" ht="15">
       <c r="A4" s="6" t="s">
@@ -10660,7 +10882,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="25" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="9"/>
@@ -10672,7 +10894,7 @@
       <c r="F5" s="12"/>
     </row>
     <row r="6" spans="1:10" ht="15">
-      <c r="A6" s="31"/>
+      <c r="A6" s="26"/>
       <c r="B6" s="5">
         <v>1</v>
       </c>
@@ -10700,7 +10922,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="15">
-      <c r="A7" s="31"/>
+      <c r="A7" s="26"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
         <v>3</v>
@@ -10710,7 +10932,7 @@
       <c r="F7" s="12"/>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A8" s="31"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="5">
         <v>2</v>
       </c>
@@ -10738,7 +10960,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="15">
-      <c r="A9" s="31"/>
+      <c r="A9" s="26"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10" t="s">
         <v>14</v>
@@ -10748,7 +10970,7 @@
       <c r="F9" s="12"/>
     </row>
     <row r="10" spans="1:10" ht="30">
-      <c r="A10" s="31"/>
+      <c r="A10" s="26"/>
       <c r="B10" s="5">
         <v>3</v>
       </c>
@@ -10776,7 +10998,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="30">
-      <c r="A11" s="31"/>
+      <c r="A11" s="26"/>
       <c r="B11" s="5">
         <v>4</v>
       </c>
@@ -10788,7 +11010,7 @@
       <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:10" ht="29.25" customHeight="1">
-      <c r="A12" s="31"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="5">
         <v>5</v>
       </c>
@@ -10800,7 +11022,7 @@
       <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:10" ht="15">
-      <c r="A13" s="31"/>
+      <c r="A13" s="26"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10" t="s">
         <v>4</v>
@@ -10810,7 +11032,7 @@
       <c r="F13" s="12"/>
     </row>
     <row r="14" spans="1:10" ht="15">
-      <c r="A14" s="31"/>
+      <c r="A14" s="26"/>
       <c r="B14" s="5">
         <v>6</v>
       </c>
@@ -10838,7 +11060,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="25" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="9"/>
@@ -10850,7 +11072,7 @@
       <c r="F15" s="12"/>
     </row>
     <row r="16" spans="1:10" ht="15">
-      <c r="A16" s="31"/>
+      <c r="A16" s="26"/>
       <c r="B16" s="5">
         <v>8</v>
       </c>
@@ -10878,7 +11100,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="25" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="9"/>
@@ -10890,7 +11112,7 @@
       <c r="F17" s="12"/>
     </row>
     <row r="18" spans="1:10" ht="30">
-      <c r="A18" s="31"/>
+      <c r="A18" s="26"/>
       <c r="B18" s="5">
         <v>9</v>
       </c>
@@ -10918,7 +11140,7 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="31"/>
+      <c r="A19" s="26"/>
       <c r="B19" s="5">
         <v>10</v>
       </c>
@@ -10930,7 +11152,7 @@
       <c r="F19" s="8"/>
     </row>
     <row r="20" spans="1:10" ht="30">
-      <c r="A20" s="31"/>
+      <c r="A20" s="26"/>
       <c r="B20" s="5">
         <v>11</v>
       </c>
@@ -10942,7 +11164,7 @@
       <c r="F20" s="8"/>
     </row>
     <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="35"/>
+      <c r="A21" s="30"/>
       <c r="B21" s="5">
         <v>13</v>
       </c>
@@ -10954,7 +11176,7 @@
       <c r="F21" s="8"/>
     </row>
     <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="34" t="s">
+      <c r="A22" s="25" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="9"/>
@@ -10966,7 +11188,7 @@
       <c r="F22" s="12"/>
     </row>
     <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="31"/>
+      <c r="A23" s="26"/>
       <c r="B23" s="5">
         <v>14</v>
       </c>
@@ -10994,7 +11216,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="15">
-      <c r="A24" s="31"/>
+      <c r="A24" s="26"/>
       <c r="B24" s="5">
         <v>15</v>
       </c>
@@ -11006,7 +11228,7 @@
       <c r="F24" s="8"/>
     </row>
     <row r="25" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="25" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="9"/>
@@ -11018,11 +11240,11 @@
       <c r="F25" s="12"/>
     </row>
     <row r="26" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A26" s="31"/>
-      <c r="B26" s="23">
+      <c r="A26" s="26"/>
+      <c r="B26" s="20">
         <v>24</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="21" t="s">
         <v>72</v>
       </c>
       <c r="D26" s="3"/>
@@ -11046,7 +11268,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" s="1" customFormat="1" ht="45">
-      <c r="A27" s="31"/>
+      <c r="A27" s="26"/>
       <c r="B27" s="5">
         <v>25</v>
       </c>
@@ -11058,7 +11280,7 @@
       <c r="F27" s="8"/>
     </row>
     <row r="28" spans="1:10" ht="15">
-      <c r="A28" s="31"/>
+      <c r="A28" s="26"/>
       <c r="B28" s="9"/>
       <c r="C28" s="10" t="s">
         <v>10</v>
@@ -11068,11 +11290,11 @@
       <c r="F28" s="12"/>
     </row>
     <row r="29" spans="1:10" ht="30">
-      <c r="A29" s="31"/>
-      <c r="B29" s="23">
+      <c r="A29" s="26"/>
+      <c r="B29" s="20">
         <v>26</v>
       </c>
-      <c r="C29" s="24" t="s">
+      <c r="C29" s="21" t="s">
         <v>72</v>
       </c>
       <c r="D29" s="3"/>
@@ -11096,7 +11318,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="15">
-      <c r="A30" s="41" t="s">
+      <c r="A30" s="27" t="s">
         <v>11</v>
       </c>
       <c r="B30" s="9"/>
@@ -11108,7 +11330,7 @@
       <c r="F30" s="12"/>
     </row>
     <row r="31" spans="1:10" ht="15">
-      <c r="A31" s="41"/>
+      <c r="A31" s="27"/>
       <c r="B31" s="5">
         <v>19</v>
       </c>
@@ -11136,7 +11358,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="30">
-      <c r="A32" s="41"/>
+      <c r="A32" s="27"/>
       <c r="B32" s="5">
         <v>20</v>
       </c>
@@ -11148,7 +11370,7 @@
       <c r="F32" s="8"/>
     </row>
     <row r="33" spans="1:10" ht="15">
-      <c r="A33" s="41"/>
+      <c r="A33" s="27"/>
       <c r="B33" s="5">
         <v>21</v>
       </c>
@@ -11160,7 +11382,7 @@
       <c r="F33" s="8"/>
     </row>
     <row r="34" spans="1:10" ht="15">
-      <c r="A34" s="41"/>
+      <c r="A34" s="27"/>
       <c r="B34" s="5">
         <v>24</v>
       </c>
@@ -11172,7 +11394,7 @@
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:10" ht="15">
-      <c r="A35" s="41"/>
+      <c r="A35" s="27"/>
       <c r="B35" s="5">
         <v>25</v>
       </c>
@@ -11184,7 +11406,7 @@
       <c r="F35" s="8"/>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1">
-      <c r="A36" s="29" t="s">
+      <c r="A36" s="28" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="9"/>
@@ -11196,7 +11418,7 @@
       <c r="F36" s="12"/>
     </row>
     <row r="37" spans="1:10" ht="30">
-      <c r="A37" s="30"/>
+      <c r="A37" s="29"/>
       <c r="B37" s="5">
         <v>26</v>
       </c>
@@ -11224,7 +11446,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="15">
-      <c r="A38" s="30"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="5">
         <v>27</v>
       </c>
@@ -11236,7 +11458,7 @@
       <c r="F38" s="8"/>
     </row>
     <row r="39" spans="1:10" ht="30">
-      <c r="A39" s="30"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="5">
         <v>28</v>
       </c>
@@ -11248,7 +11470,7 @@
       <c r="F39" s="8"/>
     </row>
     <row r="40" spans="1:10" ht="15">
-      <c r="A40" s="30"/>
+      <c r="A40" s="29"/>
       <c r="B40" s="5"/>
       <c r="C40" s="8" t="s">
         <v>105</v>
@@ -11258,7 +11480,7 @@
       <c r="F40" s="8"/>
     </row>
     <row r="41" spans="1:10" ht="15">
-      <c r="A41" s="30"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="9"/>
       <c r="C41" s="10" t="s">
         <v>15</v>
@@ -11268,7 +11490,7 @@
       <c r="F41" s="12"/>
     </row>
     <row r="42" spans="1:10" ht="15">
-      <c r="A42" s="30"/>
+      <c r="A42" s="29"/>
       <c r="B42" s="5">
         <v>29</v>
       </c>
@@ -11296,7 +11518,7 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="15">
-      <c r="A43" s="30"/>
+      <c r="A43" s="29"/>
       <c r="B43" s="5">
         <v>30</v>
       </c>
@@ -11337,11 +11559,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A30:A35"/>
-    <mergeCell ref="A36:A43"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A25:A29"/>
     <mergeCell ref="A5:A14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A1:F1"/>
@@ -11349,6 +11566,11 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A30:A35"/>
+    <mergeCell ref="A36:A43"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A25:A29"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25 D17 D15 D22 D41 D36 D30 D28" xr:uid="{00000000-0002-0000-0400-000000000000}">

--- a/6.Gerenciamento de Projeto/CARREGAJA - Checklist de Projeto.xlsx
+++ b/6.Gerenciamento de Projeto/CARREGAJA - Checklist de Projeto.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1506729-BD29-4FDC-A8F6-3BD22061EEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{D1506729-BD29-4FDC-A8F6-3BD22061EEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{204189F8-024C-49FA-A128-1306996FEC74}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="666" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="666" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicadores" sheetId="6" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet name="Ver-Construção1" sheetId="3" r:id="rId5"/>
     <sheet name="Ver-Transição1" sheetId="4" r:id="rId6"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1" calcId="191029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -713,7 +713,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="122">
   <si>
     <t>Ambiente</t>
   </si>
@@ -1066,34 +1066,19 @@
     <t>Sim</t>
   </si>
   <si>
-    <t>Parcialmente</t>
-  </si>
-  <si>
     <t>NA</t>
   </si>
   <si>
-    <t>Diagramas produzidos em PlantUML, e não no Template - Modelos Analise e Design.asta previsto pelo SpinOff. Pasta e nomeação corretas.</t>
-  </si>
-  <si>
-    <t>Transpor o Modelo de Caso de Uso para o Astah.</t>
-  </si>
-  <si>
-    <t>Protótipo não produzido: é saída de Detalhar Requisitos, da Elaboração.</t>
-  </si>
-  <si>
     <t>Aprovado pelo Product Owner, que atua como representante do cliente (RE-16).</t>
   </si>
   <si>
     <t>O Glossário é a subseção 1.3 do Visão, onde o template o posiciona. O SpinOff não prevê template autônomo para ele.</t>
   </si>
   <si>
-    <t>Não houve reunião de levantamento a registrar: o projeto não dispõe de cliente externo (RE-16).</t>
-  </si>
-  <si>
-    <t>Não se aplica pelo mesmo motivo do item 16 (RE-16).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelo mantido em CARREGAJA - Modelo de Caso de Uso.asta, no formato do Template - Modelos Analise e Design do SpinOff, com os dois atores, os catorze casos de uso UC01–UC14 e as relações de inclusão.</t>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Protótipo não produzido</t>
   </si>
 </sst>
 </file>
@@ -1489,48 +1474,6 @@
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1573,20 +1516,38 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1597,29 +1558,53 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1956,13 +1941,13 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.6</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1</c:v>
@@ -2075,7 +2060,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2182,7 +2167,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -7431,17 +7416,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:2" ht="18">
+      <c r="A1" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="38"/>
+      <c r="B1" s="55"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="16" t="s">
@@ -7502,16 +7487,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6B2C1B-A599-4159-99C1-DE703E343043}">
   <dimension ref="A1:R37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" customWidth="1"/>
-    <col min="16" max="16" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" customWidth="1"/>
+    <col min="2" max="2" width="8.109375" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.88671875" customWidth="1"/>
+    <col min="5" max="5" width="6.44140625" customWidth="1"/>
+    <col min="6" max="6" width="6.88671875" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" customWidth="1"/>
+    <col min="16" max="16" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -7552,7 +7537,7 @@
       </c>
       <c r="B2" s="22">
         <f>('Ver-Iniciação1'!$G$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="22">
         <f>('Ver-Iniciação1'!$H$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
@@ -7560,7 +7545,7 @@
       </c>
       <c r="D2" s="22">
         <f>('Ver-Iniciação1'!$I$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="22">
         <f>('Ver-Iniciação1'!$J$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
@@ -7632,11 +7617,11 @@
       </c>
       <c r="B4" s="22">
         <f>('Ver-Iniciação1'!$G$13/SUM('Ver-Iniciação1'!$G$13:'Ver-Iniciação1'!$J$13))</f>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="C4" s="22">
         <f>('Ver-Iniciação1'!$H$13/SUM('Ver-Iniciação1'!$G$13:'Ver-Iniciação1'!$J$13))</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D4" s="22">
         <f>('Ver-Iniciação1'!$I$13/SUM('Ver-Iniciação1'!$G$13:'Ver-Iniciação1'!$J$13))</f>
@@ -8535,844 +8520,838 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="76.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
-    <col min="5" max="6" width="47.5703125" customWidth="1"/>
-    <col min="7" max="7" width="7.5703125" customWidth="1"/>
-    <col min="8" max="8" width="8.5703125" customWidth="1"/>
-    <col min="9" max="10" width="7.5703125" customWidth="1"/>
+    <col min="1" max="1" width="5.6640625" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="76.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+    <col min="5" max="6" width="47.5546875" customWidth="1"/>
+    <col min="7" max="7" width="7.5546875" customWidth="1"/>
+    <col min="8" max="8" width="8.5546875" customWidth="1"/>
+    <col min="9" max="10" width="7.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
     </row>
     <row r="2" spans="1:10" ht="32.1" customHeight="1" thickBot="1">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="66" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="57"/>
-      <c r="F2" s="68">
+      <c r="E2" s="54"/>
+      <c r="F2" s="42">
         <f>COUNTIF(D5:D41,"Sim")/(COUNTA(D5:D41)-COUNTIF(D5:D41,"NA"))</f>
         <v>0.96153846153846156</v>
       </c>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
     </row>
     <row r="3" spans="1:10" ht="32.1" customHeight="1" thickBot="1">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="55"/>
-      <c r="C3" s="67" t="s">
+      <c r="B3" s="47"/>
+      <c r="C3" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="58" t="s">
+      <c r="D3" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="59"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-    </row>
-    <row r="4" spans="1:10" ht="30">
-      <c r="A4" s="39" t="s">
+      <c r="E3" s="51"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+    </row>
+    <row r="4" spans="1:10" ht="28.8">
+      <c r="A4" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
-    </row>
-    <row r="5" spans="1:10" ht="15">
-      <c r="A5" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="44" t="s">
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+    </row>
+    <row r="5" spans="1:10" ht="14.4">
+      <c r="A5" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="42">
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="28">
         <f>COUNTIF(D6,"Sim")</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="28">
+        <f>COUNTIF(D6,"Parcialmente")</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="28">
+        <f>COUNTIF(D6,"Não")</f>
         <v>1</v>
       </c>
-      <c r="H5" s="42">
-        <f>COUNTIF(D6,"Parcialmente")</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="42">
-        <f>COUNTIF(D6,"Não")</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="42">
+      <c r="J5" s="28">
         <f>COUNTIF(D6,"NA")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15">
-      <c r="A6" s="62"/>
-      <c r="B6" s="46">
+    <row r="6" spans="1:10" ht="14.4">
+      <c r="A6" s="49"/>
+      <c r="B6" s="32">
         <v>1</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-    </row>
-    <row r="7" spans="1:10" ht="15">
-      <c r="A7" s="61" t="s">
+      <c r="D6" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+    </row>
+    <row r="7" spans="1:10" ht="14.4">
+      <c r="A7" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="44" t="s">
+      <c r="B7" s="29"/>
+      <c r="C7" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="42">
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="28">
         <f>COUNTIF(D8:D12,"Sim")</f>
         <v>5</v>
       </c>
-      <c r="H7" s="42">
+      <c r="H7" s="28">
         <f>COUNTIF(D8:D12,"Parcialmente")</f>
         <v>0</v>
       </c>
-      <c r="I7" s="42">
+      <c r="I7" s="28">
         <f>COUNTIF(D8:D12,"Não")</f>
         <v>0</v>
       </c>
-      <c r="J7" s="42">
+      <c r="J7" s="28">
         <f>COUNTIF(D8:D12,"NA")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="30">
-      <c r="A8" s="63"/>
-      <c r="B8" s="49">
+    <row r="8" spans="1:10" ht="28.8">
+      <c r="A8" s="45"/>
+      <c r="B8" s="35">
         <v>2</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="D8" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-    </row>
-    <row r="9" spans="1:10" ht="15">
-      <c r="A9" s="63"/>
-      <c r="B9" s="46">
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+    </row>
+    <row r="9" spans="1:10" ht="14.4">
+      <c r="A9" s="45"/>
+      <c r="B9" s="32">
         <v>3</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="48" t="s">
+      <c r="D9" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="42"/>
-    </row>
-    <row r="10" spans="1:10" ht="15">
-      <c r="A10" s="63"/>
-      <c r="B10" s="46">
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+    </row>
+    <row r="10" spans="1:10" ht="14.4">
+      <c r="A10" s="45"/>
+      <c r="B10" s="32">
         <v>4</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
-    </row>
-    <row r="11" spans="1:10" s="1" customFormat="1" ht="15">
-      <c r="A11" s="63"/>
-      <c r="B11" s="46">
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+    </row>
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="14.4">
+      <c r="A11" s="45"/>
+      <c r="B11" s="32">
         <v>5</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="48" t="s">
+      <c r="D11" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-    </row>
-    <row r="12" spans="1:10" ht="30">
-      <c r="A12" s="63"/>
-      <c r="B12" s="46">
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+    </row>
+    <row r="12" spans="1:10" ht="28.8">
+      <c r="A12" s="45"/>
+      <c r="B12" s="32">
         <v>6</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="48" t="s">
+      <c r="D12" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
-    </row>
-    <row r="13" spans="1:10" ht="15">
-      <c r="A13" s="63"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="44" t="s">
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+    </row>
+    <row r="13" spans="1:10" ht="14.4">
+      <c r="A13" s="45"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="42">
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="28">
         <f>COUNTIF(D14:D18,"Sim")</f>
-        <v>3</v>
-      </c>
-      <c r="H13" s="42">
+        <v>4</v>
+      </c>
+      <c r="H13" s="28">
         <f>COUNTIF(D14:D18,"Parcialmente")</f>
-        <v>1</v>
-      </c>
-      <c r="I13" s="42">
+        <v>0</v>
+      </c>
+      <c r="I13" s="28">
         <f>COUNTIF(D14:D18,"Não")</f>
         <v>0</v>
       </c>
-      <c r="J13" s="42">
+      <c r="J13" s="28">
         <f>COUNTIF(D14:D18,"NA")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="45">
-      <c r="A14" s="63"/>
-      <c r="B14" s="52">
+    <row r="14" spans="1:10" ht="28.8">
+      <c r="A14" s="45"/>
+      <c r="B14" s="38">
         <v>7</v>
       </c>
-      <c r="C14" s="50" t="s">
+      <c r="C14" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="48" t="s">
+      <c r="D14" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47" t="s">
-        <v>126</v>
-      </c>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
-    </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A15" s="63"/>
-      <c r="B15" s="46">
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+    </row>
+    <row r="15" spans="1:10" s="1" customFormat="1" ht="28.8">
+      <c r="A15" s="45"/>
+      <c r="B15" s="32">
         <v>8</v>
       </c>
-      <c r="C15" s="47" t="s">
+      <c r="C15" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
-    </row>
-    <row r="16" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A16" s="63"/>
-      <c r="B16" s="46">
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37"/>
+    </row>
+    <row r="16" spans="1:10" s="1" customFormat="1" ht="28.8">
+      <c r="A16" s="45"/>
+      <c r="B16" s="32">
         <v>9</v>
       </c>
-      <c r="C16" s="47" t="s">
+      <c r="C16" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="48" t="s">
+      <c r="D16" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
-    </row>
-    <row r="17" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A17" s="63"/>
-      <c r="B17" s="52">
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
+    </row>
+    <row r="17" spans="1:10" s="1" customFormat="1" ht="28.8">
+      <c r="A17" s="45"/>
+      <c r="B17" s="38">
         <v>10</v>
       </c>
-      <c r="C17" s="50" t="s">
+      <c r="C17" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="48" t="s">
+      <c r="D17" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" s="33"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
+    </row>
+    <row r="18" spans="1:10" s="1" customFormat="1" ht="28.8">
+      <c r="A18" s="45"/>
+      <c r="B18" s="32">
+        <v>11</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="E17" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="F17" s="47"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
-    </row>
-    <row r="18" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A18" s="63"/>
-      <c r="B18" s="46">
-        <v>11</v>
-      </c>
-      <c r="C18" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="51"/>
-    </row>
-    <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="63"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="44" t="s">
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+    </row>
+    <row r="19" spans="1:10" ht="14.4">
+      <c r="A19" s="45"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="42">
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="28">
         <f>COUNTIF(D20:D21,"Sim")</f>
         <v>2</v>
       </c>
-      <c r="H19" s="42">
+      <c r="H19" s="28">
         <f>COUNTIF(D20:D21,"Parcialmente")</f>
         <v>0</v>
       </c>
-      <c r="I19" s="42">
+      <c r="I19" s="28">
         <f>COUNTIF(D20:D21,"Não")</f>
         <v>0</v>
       </c>
-      <c r="J19" s="42">
+      <c r="J19" s="28">
         <f>COUNTIF(D20:D21,"NA")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="30">
-      <c r="A20" s="63"/>
-      <c r="B20" s="52">
+    <row r="20" spans="1:10" ht="28.8">
+      <c r="A20" s="45"/>
+      <c r="B20" s="38">
         <v>12</v>
       </c>
-      <c r="C20" s="50" t="s">
+      <c r="C20" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="48" t="s">
+      <c r="D20" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
-    </row>
-    <row r="21" spans="1:10" ht="45">
-      <c r="A21" s="63"/>
-      <c r="B21" s="46">
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+    </row>
+    <row r="21" spans="1:10" ht="28.8">
+      <c r="A21" s="45"/>
+      <c r="B21" s="32">
         <v>13</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="C21" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="D21" s="48" t="s">
+      <c r="D21" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="42"/>
-    </row>
-    <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="63"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="44" t="s">
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+    </row>
+    <row r="22" spans="1:10" ht="14.4">
+      <c r="A22" s="45"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="42">
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="28">
         <f>COUNTIF(D23:D24,"Sim")</f>
         <v>2</v>
       </c>
-      <c r="H22" s="42">
+      <c r="H22" s="28">
         <f>COUNTIF(D23:D24,"Parcialmente")</f>
         <v>0</v>
       </c>
-      <c r="I22" s="42">
+      <c r="I22" s="28">
         <f>COUNTIF(D23:D24,"Não")</f>
         <v>0</v>
       </c>
-      <c r="J22" s="42">
+      <c r="J22" s="28">
         <f>COUNTIF(D23:D24,"NA")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="45">
-      <c r="A23" s="63"/>
-      <c r="B23" s="52">
+    <row r="23" spans="1:10" ht="43.2">
+      <c r="A23" s="45"/>
+      <c r="B23" s="38">
         <v>14</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="C23" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="48" t="s">
+      <c r="D23" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
-    </row>
-    <row r="24" spans="1:10" ht="15">
-      <c r="A24" s="63"/>
-      <c r="B24" s="46">
+      <c r="E23" s="33"/>
+      <c r="F23" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+    </row>
+    <row r="24" spans="1:10" ht="14.4">
+      <c r="A24" s="45"/>
+      <c r="B24" s="32">
         <v>15</v>
       </c>
-      <c r="C24" s="47" t="s">
+      <c r="C24" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="48" t="s">
+      <c r="D24" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="42"/>
-    </row>
-    <row r="25" spans="1:10" ht="15">
-      <c r="A25" s="63"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="44" t="s">
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+    </row>
+    <row r="25" spans="1:10" ht="14.4">
+      <c r="A25" s="45"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="42">
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="28">
         <f>COUNTIF(D26:D27,"Sim")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="42">
+      <c r="H25" s="28">
         <f>COUNTIF(D26:D27,"Parcialmente")</f>
         <v>0</v>
       </c>
-      <c r="I25" s="42">
+      <c r="I25" s="28">
         <f>COUNTIF(D26:D27,"Não")</f>
         <v>0</v>
       </c>
-      <c r="J25" s="42">
+      <c r="J25" s="28">
         <f>COUNTIF(D26:D27,"NA")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="30">
-      <c r="A26" s="63"/>
-      <c r="B26" s="52">
+    <row r="26" spans="1:10" ht="28.8">
+      <c r="A26" s="45"/>
+      <c r="B26" s="38">
         <v>16</v>
       </c>
-      <c r="C26" s="50" t="s">
+      <c r="C26" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="48" t="s">
-        <v>118</v>
-      </c>
-      <c r="E26" s="47" t="s">
-        <v>124</v>
-      </c>
-      <c r="F26" s="47"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="42"/>
-    </row>
-    <row r="27" spans="1:10" ht="30">
-      <c r="A27" s="63"/>
-      <c r="B27" s="46">
+      <c r="D26" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+    </row>
+    <row r="27" spans="1:10" ht="14.4">
+      <c r="A27" s="45"/>
+      <c r="B27" s="32">
         <v>17</v>
       </c>
-      <c r="C27" s="47" t="s">
+      <c r="C27" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="48" t="s">
-        <v>118</v>
-      </c>
-      <c r="E27" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="F27" s="47"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="42"/>
-    </row>
-    <row r="28" spans="1:10" ht="15">
-      <c r="A28" s="63"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="44" t="s">
+      <c r="D27" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+    </row>
+    <row r="28" spans="1:10" ht="14.4">
+      <c r="A28" s="45"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="42">
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="28">
         <f>COUNTIF(D29:D36,"Sim")</f>
         <v>8</v>
       </c>
-      <c r="H28" s="42">
+      <c r="H28" s="28">
         <f>COUNTIF(D29:D36,"Parcialmente")</f>
         <v>0</v>
       </c>
-      <c r="I28" s="42">
+      <c r="I28" s="28">
         <f>COUNTIF(D29:D36,"Não")</f>
         <v>0</v>
       </c>
-      <c r="J28" s="42">
+      <c r="J28" s="28">
         <f>COUNTIF(D29:D36,"NA")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="30">
-      <c r="A29" s="63"/>
-      <c r="B29" s="52">
+    <row r="29" spans="1:10" ht="28.8">
+      <c r="A29" s="45"/>
+      <c r="B29" s="38">
         <v>21</v>
       </c>
-      <c r="C29" s="50" t="s">
+      <c r="C29" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="48" t="s">
+      <c r="D29" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
-    </row>
-    <row r="30" spans="1:10" ht="15">
-      <c r="A30" s="63"/>
-      <c r="B30" s="46">
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+    </row>
+    <row r="30" spans="1:10" ht="14.4">
+      <c r="A30" s="45"/>
+      <c r="B30" s="32">
         <v>22</v>
       </c>
-      <c r="C30" s="47" t="s">
+      <c r="C30" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="48" t="s">
+      <c r="D30" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="42"/>
-    </row>
-    <row r="31" spans="1:10" ht="15">
-      <c r="A31" s="63"/>
-      <c r="B31" s="46">
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="28"/>
+    </row>
+    <row r="31" spans="1:10" ht="14.4">
+      <c r="A31" s="45"/>
+      <c r="B31" s="32">
         <v>23</v>
       </c>
-      <c r="C31" s="47" t="s">
+      <c r="C31" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="48" t="s">
+      <c r="D31" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="42"/>
-      <c r="J31" s="42"/>
-    </row>
-    <row r="32" spans="1:10" ht="15">
-      <c r="A32" s="63"/>
-      <c r="B32" s="46">
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="28"/>
+    </row>
+    <row r="32" spans="1:10" ht="14.4">
+      <c r="A32" s="45"/>
+      <c r="B32" s="32">
         <v>24</v>
       </c>
-      <c r="C32" s="47" t="s">
+      <c r="C32" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="D32" s="48" t="s">
+      <c r="D32" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
-    </row>
-    <row r="33" spans="1:10" ht="15">
-      <c r="A33" s="63"/>
-      <c r="B33" s="46">
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+    </row>
+    <row r="33" spans="1:10" ht="14.4">
+      <c r="A33" s="45"/>
+      <c r="B33" s="32">
         <v>25</v>
       </c>
-      <c r="C33" s="47" t="s">
+      <c r="C33" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="D33" s="48" t="s">
+      <c r="D33" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="42"/>
-    </row>
-    <row r="34" spans="1:10" ht="30">
-      <c r="A34" s="63"/>
-      <c r="B34" s="46">
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="28"/>
+    </row>
+    <row r="34" spans="1:10" ht="28.8">
+      <c r="A34" s="45"/>
+      <c r="B34" s="32">
         <v>26</v>
       </c>
-      <c r="C34" s="47" t="s">
+      <c r="C34" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="D34" s="48" t="s">
+      <c r="D34" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E34" s="42"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="42"/>
-      <c r="J34" s="42"/>
-    </row>
-    <row r="35" spans="1:10" ht="30">
-      <c r="A35" s="63"/>
-      <c r="B35" s="46">
+      <c r="E34" s="28"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="28"/>
+    </row>
+    <row r="35" spans="1:10" ht="28.8">
+      <c r="A35" s="45"/>
+      <c r="B35" s="32">
         <v>27</v>
       </c>
-      <c r="C35" s="47" t="s">
+      <c r="C35" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="48" t="s">
+      <c r="D35" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="42"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="42"/>
-      <c r="J35" s="42"/>
-    </row>
-    <row r="36" spans="1:10" ht="30">
-      <c r="A36" s="63"/>
-      <c r="B36" s="46">
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="28"/>
+    </row>
+    <row r="36" spans="1:10" ht="28.8">
+      <c r="A36" s="45"/>
+      <c r="B36" s="32">
         <v>28</v>
       </c>
-      <c r="C36" s="47" t="s">
+      <c r="C36" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="D36" s="47" t="s">
+      <c r="D36" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-    </row>
-    <row r="37" spans="1:10" ht="15">
-      <c r="A37" s="64" t="s">
+      <c r="E36" s="33"/>
+      <c r="F36" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
+    </row>
+    <row r="37" spans="1:10" ht="14.4">
+      <c r="A37" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="43"/>
-      <c r="C37" s="44" t="s">
+      <c r="B37" s="29"/>
+      <c r="C37" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="42">
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="28">
         <f>COUNTIF(D38:D41,"Sim")</f>
         <v>4</v>
       </c>
-      <c r="H37" s="42">
+      <c r="H37" s="28">
         <f>COUNTIF(D38:D41,"Parcialmente")</f>
         <v>0</v>
       </c>
-      <c r="I37" s="42">
+      <c r="I37" s="28">
         <f>COUNTIF(D38:D41,"Não")</f>
         <v>0</v>
       </c>
-      <c r="J37" s="42">
+      <c r="J37" s="28">
         <f>COUNTIF(D38:D41,"NA")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="30">
-      <c r="A38" s="65"/>
-      <c r="B38" s="52">
+    <row r="38" spans="1:10" ht="28.8">
+      <c r="A38" s="44"/>
+      <c r="B38" s="38">
         <v>30</v>
       </c>
-      <c r="C38" s="50" t="s">
+      <c r="C38" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="D38" s="48" t="s">
+      <c r="D38" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="42"/>
-      <c r="H38" s="42"/>
-      <c r="I38" s="42"/>
-      <c r="J38" s="42"/>
-    </row>
-    <row r="39" spans="1:10" ht="30">
-      <c r="A39" s="65"/>
-      <c r="B39" s="46">
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="28"/>
+    </row>
+    <row r="39" spans="1:10" ht="28.8">
+      <c r="A39" s="44"/>
+      <c r="B39" s="32">
         <v>31</v>
       </c>
-      <c r="C39" s="47" t="s">
+      <c r="C39" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="D39" s="48" t="s">
+      <c r="D39" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="42"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="42"/>
-      <c r="J39" s="42"/>
-    </row>
-    <row r="40" spans="1:10" ht="15">
-      <c r="A40" s="65"/>
-      <c r="B40" s="46">
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+    </row>
+    <row r="40" spans="1:10" ht="14.4">
+      <c r="A40" s="44"/>
+      <c r="B40" s="32">
         <v>32</v>
       </c>
-      <c r="C40" s="47" t="s">
+      <c r="C40" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="D40" s="48" t="s">
+      <c r="D40" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E40" s="47"/>
-      <c r="F40" s="47"/>
-      <c r="G40" s="42"/>
-      <c r="H40" s="42"/>
-      <c r="I40" s="42"/>
-      <c r="J40" s="42"/>
-    </row>
-    <row r="41" spans="1:10" ht="30">
-      <c r="A41" s="65"/>
-      <c r="B41" s="46">
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+    </row>
+    <row r="41" spans="1:10" ht="28.8">
+      <c r="A41" s="44"/>
+      <c r="B41" s="32">
         <v>33</v>
       </c>
-      <c r="C41" s="47" t="s">
+      <c r="C41" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="48" t="s">
+      <c r="D41" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="E41" s="47"/>
-      <c r="F41" s="47"/>
-      <c r="G41" s="42"/>
-      <c r="H41" s="42"/>
-      <c r="I41" s="42"/>
-      <c r="J41" s="42"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="28"/>
+      <c r="J41" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -9400,55 +9379,55 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="21.140625" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="21.109375" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" style="4" customWidth="1"/>
     <col min="3" max="3" width="68" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.7109375" customWidth="1"/>
-    <col min="6" max="6" width="32.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.6640625" customWidth="1"/>
+    <col min="6" max="6" width="32.6640625" customWidth="1"/>
     <col min="7" max="10" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
     </row>
     <row r="2" spans="1:10" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="32"/>
+      <c r="B2" s="62"/>
       <c r="C2" s="14"/>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="34"/>
+      <c r="E2" s="64"/>
       <c r="F2" s="19" t="e">
         <f>COUNTIF(D5:D41,"Sim")/(COUNTA(D5:D42)-COUNTIF(D5:D42,"NA"))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A3" s="32" t="s">
+    <row r="3" spans="1:10" ht="15" thickBot="1">
+      <c r="A3" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="32"/>
+      <c r="B3" s="62"/>
       <c r="C3" s="13"/>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="36"/>
-      <c r="F3" s="37"/>
-    </row>
-    <row r="4" spans="1:10" ht="15">
+      <c r="E3" s="66"/>
+      <c r="F3" s="67"/>
+    </row>
+    <row r="4" spans="1:10" ht="14.4">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
@@ -9469,7 +9448,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="58" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="9"/>
@@ -9480,8 +9459,8 @@
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
     </row>
-    <row r="6" spans="1:10" ht="15">
-      <c r="A6" s="26"/>
+    <row r="6" spans="1:10" ht="14.4">
+      <c r="A6" s="59"/>
       <c r="B6" s="5">
         <v>1</v>
       </c>
@@ -9508,8 +9487,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15">
-      <c r="A7" s="26"/>
+    <row r="7" spans="1:10" ht="14.4">
+      <c r="A7" s="59"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
         <v>3</v>
@@ -9518,8 +9497,8 @@
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A8" s="26"/>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="28.8">
+      <c r="A8" s="59"/>
       <c r="B8" s="5">
         <v>2</v>
       </c>
@@ -9546,8 +9525,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A9" s="26"/>
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="28.8">
+      <c r="A9" s="59"/>
       <c r="B9" s="5">
         <v>3</v>
       </c>
@@ -9562,8 +9541,8 @@
       <c r="I9"/>
       <c r="J9"/>
     </row>
-    <row r="10" spans="1:10" ht="15">
-      <c r="A10" s="26"/>
+    <row r="10" spans="1:10" ht="14.4">
+      <c r="A10" s="59"/>
       <c r="B10" s="9"/>
       <c r="C10" s="10" t="s">
         <v>97</v>
@@ -9572,8 +9551,8 @@
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
     </row>
-    <row r="11" spans="1:10" ht="30">
-      <c r="A11" s="26"/>
+    <row r="11" spans="1:10" ht="28.8">
+      <c r="A11" s="59"/>
       <c r="B11" s="20">
         <v>4</v>
       </c>
@@ -9600,8 +9579,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="30">
-      <c r="A12" s="26"/>
+    <row r="12" spans="1:10" ht="28.8">
+      <c r="A12" s="59"/>
       <c r="B12" s="20">
         <v>5</v>
       </c>
@@ -9612,8 +9591,8 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:10" ht="30">
-      <c r="A13" s="26"/>
+    <row r="13" spans="1:10" ht="14.4">
+      <c r="A13" s="59"/>
       <c r="B13" s="5">
         <v>6</v>
       </c>
@@ -9624,8 +9603,8 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
     </row>
-    <row r="14" spans="1:10" ht="30">
-      <c r="A14" s="26"/>
+    <row r="14" spans="1:10" ht="28.8">
+      <c r="A14" s="59"/>
       <c r="B14" s="5">
         <v>7</v>
       </c>
@@ -9636,8 +9615,8 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:10" ht="15">
-      <c r="A15" s="26"/>
+    <row r="15" spans="1:10" ht="14.4">
+      <c r="A15" s="59"/>
       <c r="B15" s="9"/>
       <c r="C15" s="10" t="s">
         <v>4</v>
@@ -9646,8 +9625,8 @@
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:10" ht="15">
-      <c r="A16" s="26"/>
+    <row r="16" spans="1:10" ht="14.4">
+      <c r="A16" s="59"/>
       <c r="B16" s="5">
         <v>7</v>
       </c>
@@ -9675,7 +9654,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="58" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="9"/>
@@ -9686,8 +9665,8 @@
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
     </row>
-    <row r="18" spans="1:10" ht="30">
-      <c r="A18" s="26"/>
+    <row r="18" spans="1:10" ht="28.8">
+      <c r="A18" s="59"/>
       <c r="B18" s="5">
         <v>9</v>
       </c>
@@ -9714,8 +9693,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="30">
-      <c r="A19" s="26"/>
+    <row r="19" spans="1:10" ht="28.8">
+      <c r="A19" s="59"/>
       <c r="B19" s="20">
         <v>10</v>
       </c>
@@ -9726,8 +9705,8 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A20" s="26"/>
+    <row r="20" spans="1:10" s="1" customFormat="1" ht="28.8">
+      <c r="A20" s="59"/>
       <c r="B20" s="5">
         <v>11</v>
       </c>
@@ -9738,8 +9717,8 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:10" ht="45">
-      <c r="A21" s="26"/>
+    <row r="21" spans="1:10" ht="28.8">
+      <c r="A21" s="59"/>
       <c r="B21" s="5">
         <v>12</v>
       </c>
@@ -9750,8 +9729,8 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="25" t="s">
+    <row r="22" spans="1:10" ht="14.4">
+      <c r="A22" s="58" t="s">
         <v>19</v>
       </c>
       <c r="B22" s="9"/>
@@ -9762,8 +9741,8 @@
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
     </row>
-    <row r="23" spans="1:10" ht="30">
-      <c r="A23" s="26"/>
+    <row r="23" spans="1:10" ht="28.8">
+      <c r="A23" s="59"/>
       <c r="B23" s="5">
         <v>17</v>
       </c>
@@ -9790,8 +9769,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="30">
-      <c r="A24" s="26"/>
+    <row r="24" spans="1:10" ht="28.8">
+      <c r="A24" s="59"/>
       <c r="B24" s="5">
         <v>18</v>
       </c>
@@ -9802,8 +9781,8 @@
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="1:10" ht="30">
-      <c r="A25" s="26"/>
+    <row r="25" spans="1:10" ht="28.8">
+      <c r="A25" s="59"/>
       <c r="B25" s="5">
         <v>19</v>
       </c>
@@ -9814,8 +9793,8 @@
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
     </row>
-    <row r="26" spans="1:10" ht="15">
-      <c r="A26" s="26"/>
+    <row r="26" spans="1:10" ht="14.4">
+      <c r="A26" s="59"/>
       <c r="B26" s="5">
         <v>21</v>
       </c>
@@ -9826,8 +9805,8 @@
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:10" ht="15">
-      <c r="A27" s="26"/>
+    <row r="27" spans="1:10" ht="14.4">
+      <c r="A27" s="59"/>
       <c r="B27" s="5">
         <v>22</v>
       </c>
@@ -9838,8 +9817,8 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:10" ht="15">
-      <c r="A28" s="27" t="s">
+    <row r="28" spans="1:10" ht="14.4">
+      <c r="A28" s="60" t="s">
         <v>11</v>
       </c>
       <c r="B28" s="9"/>
@@ -9850,8 +9829,8 @@
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:10" ht="15">
-      <c r="A29" s="27"/>
+    <row r="29" spans="1:10" ht="14.4">
+      <c r="A29" s="60"/>
       <c r="B29" s="5">
         <v>23</v>
       </c>
@@ -9878,8 +9857,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15">
-      <c r="A30" s="27"/>
+    <row r="30" spans="1:10" ht="14.4">
+      <c r="A30" s="60"/>
       <c r="B30" s="5">
         <v>24</v>
       </c>
@@ -9890,8 +9869,8 @@
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
     </row>
-    <row r="31" spans="1:10" ht="30">
-      <c r="A31" s="27"/>
+    <row r="31" spans="1:10" ht="28.8">
+      <c r="A31" s="60"/>
       <c r="B31" s="5">
         <v>25</v>
       </c>
@@ -9902,8 +9881,8 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
     </row>
-    <row r="32" spans="1:10" ht="15">
-      <c r="A32" s="27"/>
+    <row r="32" spans="1:10" ht="14.4">
+      <c r="A32" s="60"/>
       <c r="B32" s="5">
         <v>26</v>
       </c>
@@ -9914,8 +9893,8 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:10" ht="15">
-      <c r="A33" s="27"/>
+    <row r="33" spans="1:10" ht="14.4">
+      <c r="A33" s="60"/>
       <c r="B33" s="5">
         <v>27</v>
       </c>
@@ -9926,8 +9905,8 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:10" ht="15">
-      <c r="A34" s="27"/>
+    <row r="34" spans="1:10" ht="14.4">
+      <c r="A34" s="60"/>
       <c r="B34" s="5">
         <v>28</v>
       </c>
@@ -9939,7 +9918,7 @@
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1">
-      <c r="A35" s="28" t="s">
+      <c r="A35" s="56" t="s">
         <v>30</v>
       </c>
       <c r="B35" s="9"/>
@@ -9950,8 +9929,8 @@
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:10" ht="30">
-      <c r="A36" s="29"/>
+    <row r="36" spans="1:10" ht="28.8">
+      <c r="A36" s="57"/>
       <c r="B36" s="5">
         <v>29</v>
       </c>
@@ -9978,8 +9957,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15">
-      <c r="A37" s="29"/>
+    <row r="37" spans="1:10" ht="14.4">
+      <c r="A37" s="57"/>
       <c r="B37" s="5">
         <v>30</v>
       </c>
@@ -9990,8 +9969,8 @@
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
     </row>
-    <row r="38" spans="1:10" ht="30">
-      <c r="A38" s="29"/>
+    <row r="38" spans="1:10" ht="28.8">
+      <c r="A38" s="57"/>
       <c r="B38" s="5">
         <v>31</v>
       </c>
@@ -10002,8 +9981,8 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:10" ht="15">
-      <c r="A39" s="29"/>
+    <row r="39" spans="1:10" ht="14.4">
+      <c r="A39" s="57"/>
       <c r="B39" s="9"/>
       <c r="C39" s="10" t="s">
         <v>15</v>
@@ -10012,8 +9991,8 @@
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:10" ht="15">
-      <c r="A40" s="29"/>
+    <row r="40" spans="1:10" ht="14.4">
+      <c r="A40" s="57"/>
       <c r="B40" s="5">
         <v>32</v>
       </c>
@@ -10040,8 +10019,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15">
-      <c r="A41" s="29"/>
+    <row r="41" spans="1:10" ht="14.4">
+      <c r="A41" s="57"/>
       <c r="B41" s="5">
         <v>33</v>
       </c>
@@ -10081,55 +10060,55 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J57"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="21.140625" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="71.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.7109375" customWidth="1"/>
-    <col min="6" max="6" width="32.7109375" customWidth="1"/>
-    <col min="7" max="10" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="21.109375" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="71.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.6640625" customWidth="1"/>
+    <col min="6" max="6" width="32.6640625" customWidth="1"/>
+    <col min="7" max="10" width="9.109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
     </row>
     <row r="2" spans="1:10" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="32"/>
+      <c r="B2" s="62"/>
       <c r="C2" s="14"/>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="34"/>
+      <c r="E2" s="64"/>
       <c r="F2" s="19" t="e">
         <f>COUNTIF(D5:D42,"Sim")/(COUNTA(D5:D41)-COUNTIF(D5:D41,"NA"))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A3" s="32" t="s">
+    <row r="3" spans="1:10" ht="15" thickBot="1">
+      <c r="A3" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="32"/>
+      <c r="B3" s="62"/>
       <c r="C3" s="13"/>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="36"/>
-      <c r="F3" s="37"/>
-    </row>
-    <row r="4" spans="1:10" ht="15">
+      <c r="E3" s="66"/>
+      <c r="F3" s="67"/>
+    </row>
+    <row r="4" spans="1:10" ht="14.4">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
@@ -10150,7 +10129,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="58" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="9"/>
@@ -10161,8 +10140,8 @@
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
     </row>
-    <row r="6" spans="1:10" ht="15">
-      <c r="A6" s="26"/>
+    <row r="6" spans="1:10" ht="14.4">
+      <c r="A6" s="59"/>
       <c r="B6" s="5">
         <v>1</v>
       </c>
@@ -10189,8 +10168,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15">
-      <c r="A7" s="26"/>
+    <row r="7" spans="1:10" ht="14.4">
+      <c r="A7" s="59"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
         <v>3</v>
@@ -10199,8 +10178,8 @@
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A8" s="26"/>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="28.8">
+      <c r="A8" s="59"/>
       <c r="B8" s="5">
         <v>2</v>
       </c>
@@ -10227,8 +10206,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15">
-      <c r="A9" s="26"/>
+    <row r="9" spans="1:10" ht="14.4">
+      <c r="A9" s="59"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10" t="s">
         <v>97</v>
@@ -10237,8 +10216,8 @@
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
     </row>
-    <row r="10" spans="1:10" ht="30">
-      <c r="A10" s="26"/>
+    <row r="10" spans="1:10" ht="28.8">
+      <c r="A10" s="59"/>
       <c r="B10" s="5">
         <v>3</v>
       </c>
@@ -10265,8 +10244,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="30">
-      <c r="A11" s="26"/>
+    <row r="11" spans="1:10" ht="28.8">
+      <c r="A11" s="59"/>
       <c r="B11" s="5">
         <v>4</v>
       </c>
@@ -10278,7 +10257,7 @@
       <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A12" s="26"/>
+      <c r="A12" s="59"/>
       <c r="B12" s="5">
         <v>5</v>
       </c>
@@ -10289,8 +10268,8 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:10" ht="15">
-      <c r="A13" s="26"/>
+    <row r="13" spans="1:10" ht="14.4">
+      <c r="A13" s="59"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10" t="s">
         <v>4</v>
@@ -10299,8 +10278,8 @@
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
     </row>
-    <row r="14" spans="1:10" ht="15">
-      <c r="A14" s="26"/>
+    <row r="14" spans="1:10" ht="14.4">
+      <c r="A14" s="59"/>
       <c r="B14" s="5">
         <v>6</v>
       </c>
@@ -10328,7 +10307,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="58" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="9"/>
@@ -10339,8 +10318,8 @@
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:10" ht="15">
-      <c r="A16" s="26"/>
+    <row r="16" spans="1:10" ht="14.4">
+      <c r="A16" s="59"/>
       <c r="B16" s="5">
         <v>8</v>
       </c>
@@ -10367,8 +10346,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="25" t="s">
+    <row r="17" spans="1:10" ht="14.4">
+      <c r="A17" s="58" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="9"/>
@@ -10379,8 +10358,8 @@
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
     </row>
-    <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="26"/>
+    <row r="18" spans="1:10" ht="14.4">
+      <c r="A18" s="59"/>
       <c r="B18" s="5">
         <v>11</v>
       </c>
@@ -10407,8 +10386,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="30">
-      <c r="A19" s="26"/>
+    <row r="19" spans="1:10" ht="28.8">
+      <c r="A19" s="59"/>
       <c r="B19" s="5">
         <v>13</v>
       </c>
@@ -10419,8 +10398,8 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="1:10" ht="30">
-      <c r="A20" s="26"/>
+    <row r="20" spans="1:10" ht="28.8">
+      <c r="A20" s="59"/>
       <c r="B20" s="5">
         <v>14</v>
       </c>
@@ -10431,8 +10410,8 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="26"/>
+    <row r="21" spans="1:10" ht="14.4">
+      <c r="A21" s="59"/>
       <c r="B21" s="5">
         <v>15</v>
       </c>
@@ -10443,8 +10422,8 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="26"/>
+    <row r="22" spans="1:10" ht="14.4">
+      <c r="A22" s="59"/>
       <c r="B22" s="5">
         <v>16</v>
       </c>
@@ -10455,8 +10434,8 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
     </row>
-    <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="25" t="s">
+    <row r="23" spans="1:10" ht="14.4">
+      <c r="A23" s="58" t="s">
         <v>20</v>
       </c>
       <c r="B23" s="9"/>
@@ -10467,8 +10446,8 @@
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
     </row>
-    <row r="24" spans="1:10" ht="30">
-      <c r="A24" s="26"/>
+    <row r="24" spans="1:10" ht="28.8">
+      <c r="A24" s="59"/>
       <c r="B24" s="20">
         <v>17</v>
       </c>
@@ -10495,8 +10474,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="30">
-      <c r="A25" s="26"/>
+    <row r="25" spans="1:10" ht="28.8">
+      <c r="A25" s="59"/>
       <c r="B25" s="5">
         <v>18</v>
       </c>
@@ -10507,8 +10486,8 @@
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
     </row>
-    <row r="26" spans="1:10" ht="15">
-      <c r="A26" s="26"/>
+    <row r="26" spans="1:10" ht="14.4">
+      <c r="A26" s="59"/>
       <c r="B26" s="5">
         <v>19</v>
       </c>
@@ -10519,8 +10498,8 @@
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:10" ht="15">
-      <c r="A27" s="26"/>
+    <row r="27" spans="1:10" ht="14.4">
+      <c r="A27" s="59"/>
       <c r="B27" s="5">
         <v>21</v>
       </c>
@@ -10531,8 +10510,8 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:10" ht="15">
-      <c r="A28" s="26"/>
+    <row r="28" spans="1:10" ht="14.4">
+      <c r="A28" s="59"/>
       <c r="B28" s="5">
         <v>22</v>
       </c>
@@ -10543,8 +10522,8 @@
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
     </row>
-    <row r="29" spans="1:10" ht="15">
-      <c r="A29" s="27" t="s">
+    <row r="29" spans="1:10" ht="14.4">
+      <c r="A29" s="60" t="s">
         <v>11</v>
       </c>
       <c r="B29" s="9"/>
@@ -10555,8 +10534,8 @@
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="1:10" ht="15">
-      <c r="A30" s="27"/>
+    <row r="30" spans="1:10" ht="14.4">
+      <c r="A30" s="60"/>
       <c r="B30" s="5">
         <v>24</v>
       </c>
@@ -10583,8 +10562,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="30">
-      <c r="A31" s="27"/>
+    <row r="31" spans="1:10" ht="28.8">
+      <c r="A31" s="60"/>
       <c r="B31" s="5">
         <v>26</v>
       </c>
@@ -10595,8 +10574,8 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
     </row>
-    <row r="32" spans="1:10" ht="15">
-      <c r="A32" s="27"/>
+    <row r="32" spans="1:10" ht="14.4">
+      <c r="A32" s="60"/>
       <c r="B32" s="5">
         <v>27</v>
       </c>
@@ -10607,8 +10586,8 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:10" ht="15">
-      <c r="A33" s="27"/>
+    <row r="33" spans="1:10" ht="14.4">
+      <c r="A33" s="60"/>
       <c r="B33" s="5">
         <v>28</v>
       </c>
@@ -10619,8 +10598,8 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:10" ht="15">
-      <c r="A34" s="27"/>
+    <row r="34" spans="1:10" ht="14.4">
+      <c r="A34" s="60"/>
       <c r="B34" s="5">
         <v>29</v>
       </c>
@@ -10632,7 +10611,7 @@
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1">
-      <c r="A35" s="28" t="s">
+      <c r="A35" s="56" t="s">
         <v>30</v>
       </c>
       <c r="B35" s="9"/>
@@ -10643,8 +10622,8 @@
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:10" ht="30">
-      <c r="A36" s="29"/>
+    <row r="36" spans="1:10" ht="28.8">
+      <c r="A36" s="57"/>
       <c r="B36" s="5">
         <v>30</v>
       </c>
@@ -10671,8 +10650,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15">
-      <c r="A37" s="29"/>
+    <row r="37" spans="1:10" ht="14.4">
+      <c r="A37" s="57"/>
       <c r="B37" s="5">
         <v>31</v>
       </c>
@@ -10683,8 +10662,8 @@
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
     </row>
-    <row r="38" spans="1:10" ht="30">
-      <c r="A38" s="29"/>
+    <row r="38" spans="1:10" ht="28.8">
+      <c r="A38" s="57"/>
       <c r="B38" s="5">
         <v>32</v>
       </c>
@@ -10695,8 +10674,8 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:10" ht="15">
-      <c r="A39" s="29"/>
+    <row r="39" spans="1:10" ht="14.4">
+      <c r="A39" s="57"/>
       <c r="B39" s="5"/>
       <c r="C39" s="8" t="s">
         <v>105</v>
@@ -10705,8 +10684,8 @@
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
     </row>
-    <row r="40" spans="1:10" ht="15">
-      <c r="A40" s="29"/>
+    <row r="40" spans="1:10" ht="14.4">
+      <c r="A40" s="57"/>
       <c r="B40" s="9"/>
       <c r="C40" s="10" t="s">
         <v>15</v>
@@ -10715,8 +10694,8 @@
       <c r="E40" s="12"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:10" ht="15">
-      <c r="A41" s="29"/>
+    <row r="41" spans="1:10" ht="14.4">
+      <c r="A41" s="57"/>
       <c r="B41" s="5">
         <v>33</v>
       </c>
@@ -10743,8 +10722,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15">
-      <c r="A42" s="29"/>
+    <row r="42" spans="1:10" ht="14.4">
+      <c r="A42" s="57"/>
       <c r="B42" s="5">
         <v>34</v>
       </c>
@@ -10755,47 +10734,47 @@
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
     </row>
-    <row r="51" spans="2:3" ht="15">
+    <row r="51" spans="2:3" ht="14.4">
       <c r="B51"/>
       <c r="C51"/>
     </row>
-    <row r="52" spans="2:3" ht="15">
+    <row r="52" spans="2:3" ht="14.4">
       <c r="B52"/>
       <c r="C52"/>
     </row>
-    <row r="53" spans="2:3" ht="15">
+    <row r="53" spans="2:3" ht="14.4">
       <c r="B53"/>
       <c r="C53"/>
     </row>
-    <row r="54" spans="2:3" ht="15">
+    <row r="54" spans="2:3" ht="14.4">
       <c r="B54"/>
       <c r="C54"/>
     </row>
-    <row r="55" spans="2:3" ht="15">
+    <row r="55" spans="2:3" ht="14.4">
       <c r="B55"/>
       <c r="C55"/>
     </row>
-    <row r="56" spans="2:3" ht="15">
+    <row r="56" spans="2:3" ht="14.4">
       <c r="B56"/>
       <c r="C56"/>
     </row>
-    <row r="57" spans="2:3" ht="15">
+    <row r="57" spans="2:3" ht="14.4">
       <c r="B57"/>
       <c r="C57"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:F3"/>
     <mergeCell ref="A5:A14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A17:A22"/>
     <mergeCell ref="A29:A34"/>
     <mergeCell ref="A35:A42"/>
     <mergeCell ref="A23:A28"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:F3"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23 D15 D17 D40 D35 D29" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -10813,55 +10792,55 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J58"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="21.140625" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="71.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.7109375" customWidth="1"/>
-    <col min="6" max="6" width="32.7109375" customWidth="1"/>
+    <col min="1" max="1" width="21.109375" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="71.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.6640625" customWidth="1"/>
+    <col min="6" max="6" width="32.6640625" customWidth="1"/>
     <col min="7" max="10" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
     </row>
     <row r="2" spans="1:10" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="32"/>
+      <c r="B2" s="62"/>
       <c r="C2" s="14"/>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="34"/>
+      <c r="E2" s="64"/>
       <c r="F2" s="19" t="e">
         <f>COUNTIF(D5:D43,"Sim")/(COUNTA(D5:D43)-COUNTIF(D5:D43,"NA"))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" thickBot="1">
-      <c r="A3" s="32" t="s">
+    <row r="3" spans="1:10" ht="15" thickBot="1">
+      <c r="A3" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="32"/>
+      <c r="B3" s="62"/>
       <c r="C3" s="13"/>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="36"/>
-      <c r="F3" s="37"/>
-    </row>
-    <row r="4" spans="1:10" ht="15">
+      <c r="E3" s="66"/>
+      <c r="F3" s="67"/>
+    </row>
+    <row r="4" spans="1:10" ht="14.4">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
@@ -10882,7 +10861,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="58" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="9"/>
@@ -10893,8 +10872,8 @@
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
     </row>
-    <row r="6" spans="1:10" ht="15">
-      <c r="A6" s="26"/>
+    <row r="6" spans="1:10" ht="14.4">
+      <c r="A6" s="59"/>
       <c r="B6" s="5">
         <v>1</v>
       </c>
@@ -10921,8 +10900,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15">
-      <c r="A7" s="26"/>
+    <row r="7" spans="1:10" ht="14.4">
+      <c r="A7" s="59"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
         <v>3</v>
@@ -10931,8 +10910,8 @@
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A8" s="26"/>
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="28.8">
+      <c r="A8" s="59"/>
       <c r="B8" s="5">
         <v>2</v>
       </c>
@@ -10959,8 +10938,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15">
-      <c r="A9" s="26"/>
+    <row r="9" spans="1:10" ht="14.4">
+      <c r="A9" s="59"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10" t="s">
         <v>14</v>
@@ -10969,8 +10948,8 @@
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
     </row>
-    <row r="10" spans="1:10" ht="30">
-      <c r="A10" s="26"/>
+    <row r="10" spans="1:10" ht="28.8">
+      <c r="A10" s="59"/>
       <c r="B10" s="5">
         <v>3</v>
       </c>
@@ -10997,8 +10976,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="30">
-      <c r="A11" s="26"/>
+    <row r="11" spans="1:10" ht="28.8">
+      <c r="A11" s="59"/>
       <c r="B11" s="5">
         <v>4</v>
       </c>
@@ -11010,7 +10989,7 @@
       <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:10" ht="29.25" customHeight="1">
-      <c r="A12" s="26"/>
+      <c r="A12" s="59"/>
       <c r="B12" s="5">
         <v>5</v>
       </c>
@@ -11021,8 +11000,8 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:10" ht="15">
-      <c r="A13" s="26"/>
+    <row r="13" spans="1:10" ht="14.4">
+      <c r="A13" s="59"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10" t="s">
         <v>4</v>
@@ -11031,8 +11010,8 @@
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
     </row>
-    <row r="14" spans="1:10" ht="15">
-      <c r="A14" s="26"/>
+    <row r="14" spans="1:10" ht="14.4">
+      <c r="A14" s="59"/>
       <c r="B14" s="5">
         <v>6</v>
       </c>
@@ -11060,7 +11039,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="58" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="9"/>
@@ -11071,8 +11050,8 @@
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:10" ht="15">
-      <c r="A16" s="26"/>
+    <row r="16" spans="1:10" ht="14.4">
+      <c r="A16" s="59"/>
       <c r="B16" s="5">
         <v>8</v>
       </c>
@@ -11100,7 +11079,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="58" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="9"/>
@@ -11111,8 +11090,8 @@
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
     </row>
-    <row r="18" spans="1:10" ht="30">
-      <c r="A18" s="26"/>
+    <row r="18" spans="1:10" ht="14.4">
+      <c r="A18" s="59"/>
       <c r="B18" s="5">
         <v>9</v>
       </c>
@@ -11139,8 +11118,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="26"/>
+    <row r="19" spans="1:10" ht="14.4">
+      <c r="A19" s="59"/>
       <c r="B19" s="5">
         <v>10</v>
       </c>
@@ -11151,8 +11130,8 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="1:10" ht="30">
-      <c r="A20" s="26"/>
+    <row r="20" spans="1:10" ht="28.8">
+      <c r="A20" s="59"/>
       <c r="B20" s="5">
         <v>11</v>
       </c>
@@ -11163,8 +11142,8 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="30"/>
+    <row r="21" spans="1:10" ht="14.4">
+      <c r="A21" s="68"/>
       <c r="B21" s="5">
         <v>13</v>
       </c>
@@ -11175,8 +11154,8 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:10" ht="15">
-      <c r="A22" s="25" t="s">
+    <row r="22" spans="1:10" ht="14.4">
+      <c r="A22" s="58" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="9"/>
@@ -11187,8 +11166,8 @@
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
     </row>
-    <row r="23" spans="1:10" ht="15">
-      <c r="A23" s="26"/>
+    <row r="23" spans="1:10" ht="14.4">
+      <c r="A23" s="59"/>
       <c r="B23" s="5">
         <v>14</v>
       </c>
@@ -11215,8 +11194,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15">
-      <c r="A24" s="26"/>
+    <row r="24" spans="1:10" ht="14.4">
+      <c r="A24" s="59"/>
       <c r="B24" s="5">
         <v>15</v>
       </c>
@@ -11228,7 +11207,7 @@
       <c r="F24" s="8"/>
     </row>
     <row r="25" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="58" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="9"/>
@@ -11239,8 +11218,8 @@
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="1:10" s="1" customFormat="1" ht="30">
-      <c r="A26" s="26"/>
+    <row r="26" spans="1:10" s="1" customFormat="1" ht="28.8">
+      <c r="A26" s="59"/>
       <c r="B26" s="20">
         <v>24</v>
       </c>
@@ -11267,8 +11246,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="1" customFormat="1" ht="45">
-      <c r="A27" s="26"/>
+    <row r="27" spans="1:10" s="1" customFormat="1" ht="43.2">
+      <c r="A27" s="59"/>
       <c r="B27" s="5">
         <v>25</v>
       </c>
@@ -11279,8 +11258,8 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:10" ht="15">
-      <c r="A28" s="26"/>
+    <row r="28" spans="1:10" ht="14.4">
+      <c r="A28" s="59"/>
       <c r="B28" s="9"/>
       <c r="C28" s="10" t="s">
         <v>10</v>
@@ -11289,8 +11268,8 @@
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:10" ht="30">
-      <c r="A29" s="26"/>
+    <row r="29" spans="1:10" ht="28.8">
+      <c r="A29" s="59"/>
       <c r="B29" s="20">
         <v>26</v>
       </c>
@@ -11317,8 +11296,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15">
-      <c r="A30" s="27" t="s">
+    <row r="30" spans="1:10" ht="14.4">
+      <c r="A30" s="60" t="s">
         <v>11</v>
       </c>
       <c r="B30" s="9"/>
@@ -11329,8 +11308,8 @@
       <c r="E30" s="12"/>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:10" ht="15">
-      <c r="A31" s="27"/>
+    <row r="31" spans="1:10" ht="14.4">
+      <c r="A31" s="60"/>
       <c r="B31" s="5">
         <v>19</v>
       </c>
@@ -11357,8 +11336,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="30">
-      <c r="A32" s="27"/>
+    <row r="32" spans="1:10" ht="28.8">
+      <c r="A32" s="60"/>
       <c r="B32" s="5">
         <v>20</v>
       </c>
@@ -11369,8 +11348,8 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:10" ht="15">
-      <c r="A33" s="27"/>
+    <row r="33" spans="1:10" ht="14.4">
+      <c r="A33" s="60"/>
       <c r="B33" s="5">
         <v>21</v>
       </c>
@@ -11381,8 +11360,8 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:10" ht="15">
-      <c r="A34" s="27"/>
+    <row r="34" spans="1:10" ht="14.4">
+      <c r="A34" s="60"/>
       <c r="B34" s="5">
         <v>24</v>
       </c>
@@ -11393,8 +11372,8 @@
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
     </row>
-    <row r="35" spans="1:10" ht="15">
-      <c r="A35" s="27"/>
+    <row r="35" spans="1:10" ht="14.4">
+      <c r="A35" s="60"/>
       <c r="B35" s="5">
         <v>25</v>
       </c>
@@ -11406,7 +11385,7 @@
       <c r="F35" s="8"/>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1">
-      <c r="A36" s="28" t="s">
+      <c r="A36" s="56" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="9"/>
@@ -11417,8 +11396,8 @@
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:10" ht="30">
-      <c r="A37" s="29"/>
+    <row r="37" spans="1:10" ht="28.8">
+      <c r="A37" s="57"/>
       <c r="B37" s="5">
         <v>26</v>
       </c>
@@ -11445,8 +11424,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15">
-      <c r="A38" s="29"/>
+    <row r="38" spans="1:10" ht="14.4">
+      <c r="A38" s="57"/>
       <c r="B38" s="5">
         <v>27</v>
       </c>
@@ -11457,8 +11436,8 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:10" ht="30">
-      <c r="A39" s="29"/>
+    <row r="39" spans="1:10" ht="28.8">
+      <c r="A39" s="57"/>
       <c r="B39" s="5">
         <v>28</v>
       </c>
@@ -11469,8 +11448,8 @@
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
     </row>
-    <row r="40" spans="1:10" ht="15">
-      <c r="A40" s="29"/>
+    <row r="40" spans="1:10" ht="14.4">
+      <c r="A40" s="57"/>
       <c r="B40" s="5"/>
       <c r="C40" s="8" t="s">
         <v>105</v>
@@ -11479,8 +11458,8 @@
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
     </row>
-    <row r="41" spans="1:10" ht="15">
-      <c r="A41" s="29"/>
+    <row r="41" spans="1:10" ht="14.4">
+      <c r="A41" s="57"/>
       <c r="B41" s="9"/>
       <c r="C41" s="10" t="s">
         <v>15</v>
@@ -11489,8 +11468,8 @@
       <c r="E41" s="12"/>
       <c r="F41" s="12"/>
     </row>
-    <row r="42" spans="1:10" ht="15">
-      <c r="A42" s="29"/>
+    <row r="42" spans="1:10" ht="14.4">
+      <c r="A42" s="57"/>
       <c r="B42" s="5">
         <v>29</v>
       </c>
@@ -11517,8 +11496,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15">
-      <c r="A43" s="29"/>
+    <row r="43" spans="1:10" ht="14.4">
+      <c r="A43" s="57"/>
       <c r="B43" s="5">
         <v>30</v>
       </c>
@@ -11529,36 +11508,41 @@
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
     </row>
-    <row r="52" spans="2:3" ht="15">
+    <row r="52" spans="2:3" ht="14.4">
       <c r="B52"/>
       <c r="C52"/>
     </row>
-    <row r="53" spans="2:3" ht="15">
+    <row r="53" spans="2:3" ht="14.4">
       <c r="B53"/>
       <c r="C53"/>
     </row>
-    <row r="54" spans="2:3" ht="15">
+    <row r="54" spans="2:3" ht="14.4">
       <c r="B54"/>
       <c r="C54"/>
     </row>
-    <row r="55" spans="2:3" ht="15">
+    <row r="55" spans="2:3" ht="14.4">
       <c r="B55"/>
       <c r="C55"/>
     </row>
-    <row r="56" spans="2:3" ht="15">
+    <row r="56" spans="2:3" ht="14.4">
       <c r="B56"/>
       <c r="C56"/>
     </row>
-    <row r="57" spans="2:3" ht="15">
+    <row r="57" spans="2:3" ht="14.4">
       <c r="B57"/>
       <c r="C57"/>
     </row>
-    <row r="58" spans="2:3" ht="15">
+    <row r="58" spans="2:3" ht="14.4">
       <c r="B58"/>
       <c r="C58"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A30:A35"/>
+    <mergeCell ref="A36:A43"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A25:A29"/>
     <mergeCell ref="A5:A14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A1:F1"/>
@@ -11566,11 +11550,6 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A30:A35"/>
-    <mergeCell ref="A36:A43"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A25:A29"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25 D17 D15 D22 D41 D36 D30 D28" xr:uid="{00000000-0002-0000-0400-000000000000}">

--- a/6.Gerenciamento de Projeto/CARREGAJA - Checklist de Projeto.xlsx
+++ b/6.Gerenciamento de Projeto/CARREGAJA - Checklist de Projeto.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{D1506729-BD29-4FDC-A8F6-3BD22061EEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{204189F8-024C-49FA-A128-1306996FEC74}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077A368B-FBA1-43EB-B3C8-DAD3BA2D068B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="666" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="960" yWindow="960" windowWidth="21600" windowHeight="11235" tabRatio="666" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicadores" sheetId="6" r:id="rId1"/>
@@ -713,7 +713,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="127">
   <si>
     <t>Ambiente</t>
   </si>
@@ -1057,9 +1057,6 @@
     <t>Foram realizados os testes de aceitação por parte do usuário final?</t>
   </si>
   <si>
-    <t>31/08/2026</t>
-  </si>
-  <si>
     <t>Henrique de Almeida Marangoni Inacio (Scrum Master)</t>
   </si>
   <si>
@@ -1075,10 +1072,28 @@
     <t>O Glossário é a subseção 1.3 do Visão, onde o template o posiciona. O SpinOff não prevê template autônomo para ele.</t>
   </si>
   <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>Protótipo não produzido</t>
+    <t>26/09/2026</t>
+  </si>
+  <si>
+    <t>O Documento de Requisitos, não previsto no SpinOff, tem template próprio: 1.Requisitos/Template - Documento de Requisitos.dotx.</t>
+  </si>
+  <si>
+    <t>Visão reduzido a uma visão geral na versão 4.0, após a apresentação da Iniciação; o detalhamento passou ao Documento de Requisitos.</t>
+  </si>
+  <si>
+    <t>Modelo mantido em CARREGAJA - Modelos de Análise e Design.asta, no formato do Template - Modelos Analise e Design do SpinOff, com os dois atores, os doze casos de uso UC01–UC12, cada um com descrição, e as relações de inclusão.</t>
+  </si>
+  <si>
+    <t>Protótipo não produzido: é saída de Detalhar Requisitos, da Elaboração.</t>
+  </si>
+  <si>
+    <t>Não houve reunião de levantamento a registrar: o projeto não dispõe de cliente externo (RE-16).</t>
+  </si>
+  <si>
+    <t>Não se aplica pelo mesmo motivo do item 16 (RE-16).</t>
+  </si>
+  <si>
+    <t>Plano de entregas com 7 sprints, o número calculado na aba Planejamento da PCP (6,13, arredondado para cima).</t>
   </si>
 </sst>
 </file>
@@ -1709,7 +1724,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.96153846153846156</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -1941,7 +1956,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
@@ -2167,7 +2182,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -7416,13 +7431,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18">
+    <row r="1" spans="1:2" ht="18.75">
       <c r="A1" s="55" t="s">
         <v>70</v>
       </c>
@@ -7442,7 +7457,7 @@
       </c>
       <c r="B3" s="18">
         <f>'Ver-Iniciação1'!$F$2</f>
-        <v>0.96153846153846156</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7487,16 +7502,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6B2C1B-A599-4159-99C1-DE703E343043}">
   <dimension ref="A1:R37"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" customWidth="1"/>
-    <col min="2" max="2" width="8.109375" customWidth="1"/>
-    <col min="3" max="3" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.88671875" customWidth="1"/>
-    <col min="5" max="5" width="6.44140625" customWidth="1"/>
-    <col min="6" max="6" width="6.88671875" customWidth="1"/>
-    <col min="14" max="14" width="13.109375" customWidth="1"/>
-    <col min="16" max="16" width="11.33203125" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -7537,7 +7552,7 @@
       </c>
       <c r="B2" s="22">
         <f>('Ver-Iniciação1'!$G$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="22">
         <f>('Ver-Iniciação1'!$H$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
@@ -7545,7 +7560,7 @@
       </c>
       <c r="D2" s="22">
         <f>('Ver-Iniciação1'!$I$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="22">
         <f>('Ver-Iniciação1'!$J$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
@@ -8520,19 +8535,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="76.109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" customWidth="1"/>
-    <col min="5" max="6" width="47.5546875" customWidth="1"/>
-    <col min="7" max="7" width="7.5546875" customWidth="1"/>
-    <col min="8" max="8" width="8.5546875" customWidth="1"/>
-    <col min="9" max="10" width="7.5546875" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="76.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="5" max="6" width="47.5703125" customWidth="1"/>
+    <col min="7" max="7" width="7.5703125" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" customWidth="1"/>
+    <col min="9" max="10" width="7.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" ht="18">
       <c r="A1" s="46" t="s">
         <v>16</v>
       </c>
@@ -8552,7 +8567,7 @@
       </c>
       <c r="B2" s="47"/>
       <c r="C2" s="40" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D2" s="53" t="s">
         <v>44</v>
@@ -8560,7 +8575,7 @@
       <c r="E2" s="54"/>
       <c r="F2" s="42">
         <f>COUNTIF(D5:D41,"Sim")/(COUNTA(D5:D41)-COUNTIF(D5:D41,"NA"))</f>
-        <v>0.96153846153846156</v>
+        <v>1</v>
       </c>
       <c r="G2" s="39"/>
       <c r="H2" s="39"/>
@@ -8573,7 +8588,7 @@
       </c>
       <c r="B3" s="47"/>
       <c r="C3" s="41" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>43</v>
@@ -8585,7 +8600,7 @@
       <c r="I3" s="39"/>
       <c r="J3" s="39"/>
     </row>
-    <row r="4" spans="1:10" ht="28.8">
+    <row r="4" spans="1:10" ht="30">
       <c r="A4" s="25" t="s">
         <v>22</v>
       </c>
@@ -8609,7 +8624,7 @@
       <c r="I4" s="28"/>
       <c r="J4" s="28"/>
     </row>
-    <row r="5" spans="1:10" ht="14.4">
+    <row r="5" spans="1:10" ht="15">
       <c r="A5" s="48" t="s">
         <v>0</v>
       </c>
@@ -8622,7 +8637,7 @@
       <c r="F5" s="31"/>
       <c r="G5" s="28">
         <f>COUNTIF(D6,"Sim")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="28">
         <f>COUNTIF(D6,"Parcialmente")</f>
@@ -8630,14 +8645,14 @@
       </c>
       <c r="I5" s="28">
         <f>COUNTIF(D6,"Não")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="28">
         <f>COUNTIF(D6,"NA")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="14.4">
+    <row r="6" spans="1:10" ht="60">
       <c r="A6" s="49"/>
       <c r="B6" s="32">
         <v>1</v>
@@ -8646,16 +8661,18 @@
         <v>33</v>
       </c>
       <c r="D6" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
       <c r="G6" s="28"/>
       <c r="H6" s="28"/>
       <c r="I6" s="28"/>
       <c r="J6" s="28"/>
     </row>
-    <row r="7" spans="1:10" ht="14.4">
+    <row r="7" spans="1:10" ht="15">
       <c r="A7" s="48" t="s">
         <v>17</v>
       </c>
@@ -8683,7 +8700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="28.8">
+    <row r="8" spans="1:10" ht="30">
       <c r="A8" s="45"/>
       <c r="B8" s="35">
         <v>2</v>
@@ -8692,7 +8709,7 @@
         <v>72</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E8" s="33"/>
       <c r="F8" s="33"/>
@@ -8701,7 +8718,7 @@
       <c r="I8" s="28"/>
       <c r="J8" s="28"/>
     </row>
-    <row r="9" spans="1:10" ht="14.4">
+    <row r="9" spans="1:10" ht="15">
       <c r="A9" s="45"/>
       <c r="B9" s="32">
         <v>3</v>
@@ -8710,7 +8727,7 @@
         <v>31</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E9" s="33"/>
       <c r="F9" s="33"/>
@@ -8719,7 +8736,7 @@
       <c r="I9" s="28"/>
       <c r="J9" s="28"/>
     </row>
-    <row r="10" spans="1:10" ht="14.4">
+    <row r="10" spans="1:10" ht="15">
       <c r="A10" s="45"/>
       <c r="B10" s="32">
         <v>4</v>
@@ -8728,7 +8745,7 @@
         <v>77</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E10" s="33"/>
       <c r="F10" s="33"/>
@@ -8737,7 +8754,7 @@
       <c r="I10" s="28"/>
       <c r="J10" s="28"/>
     </row>
-    <row r="11" spans="1:10" s="1" customFormat="1" ht="14.4">
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="45">
       <c r="A11" s="45"/>
       <c r="B11" s="32">
         <v>5</v>
@@ -8746,16 +8763,18 @@
         <v>32</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
+      <c r="F11" s="33" t="s">
+        <v>121</v>
+      </c>
       <c r="G11" s="37"/>
       <c r="H11" s="37"/>
       <c r="I11" s="37"/>
       <c r="J11" s="37"/>
     </row>
-    <row r="12" spans="1:10" ht="28.8">
+    <row r="12" spans="1:10" ht="30">
       <c r="A12" s="45"/>
       <c r="B12" s="32">
         <v>6</v>
@@ -8764,7 +8783,7 @@
         <v>40</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E12" s="33"/>
       <c r="F12" s="33"/>
@@ -8773,7 +8792,7 @@
       <c r="I12" s="28"/>
       <c r="J12" s="28"/>
     </row>
-    <row r="13" spans="1:10" ht="14.4">
+    <row r="13" spans="1:10" ht="15">
       <c r="A13" s="45"/>
       <c r="B13" s="29"/>
       <c r="C13" s="30" t="s">
@@ -8799,7 +8818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="28.8">
+    <row r="14" spans="1:10" ht="75">
       <c r="A14" s="45"/>
       <c r="B14" s="38">
         <v>7</v>
@@ -8808,16 +8827,18 @@
         <v>72</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
+      <c r="F14" s="33" t="s">
+        <v>122</v>
+      </c>
       <c r="G14" s="28"/>
       <c r="H14" s="28"/>
       <c r="I14" s="28"/>
       <c r="J14" s="28"/>
     </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" ht="28.8">
+    <row r="15" spans="1:10" s="1" customFormat="1" ht="30">
       <c r="A15" s="45"/>
       <c r="B15" s="32">
         <v>8</v>
@@ -8826,7 +8847,7 @@
         <v>34</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E15" s="33"/>
       <c r="F15" s="33"/>
@@ -8835,7 +8856,7 @@
       <c r="I15" s="37"/>
       <c r="J15" s="37"/>
     </row>
-    <row r="16" spans="1:10" s="1" customFormat="1" ht="28.8">
+    <row r="16" spans="1:10" s="1" customFormat="1" ht="30">
       <c r="A16" s="45"/>
       <c r="B16" s="32">
         <v>9</v>
@@ -8844,7 +8865,7 @@
         <v>79</v>
       </c>
       <c r="D16" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E16" s="33"/>
       <c r="F16" s="33"/>
@@ -8853,7 +8874,7 @@
       <c r="I16" s="37"/>
       <c r="J16" s="37"/>
     </row>
-    <row r="17" spans="1:10" s="1" customFormat="1" ht="28.8">
+    <row r="17" spans="1:10" s="1" customFormat="1" ht="30">
       <c r="A17" s="45"/>
       <c r="B17" s="38">
         <v>10</v>
@@ -8862,10 +8883,10 @@
         <v>76</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F17" s="33"/>
       <c r="G17" s="37"/>
@@ -8873,7 +8894,7 @@
       <c r="I17" s="37"/>
       <c r="J17" s="37"/>
     </row>
-    <row r="18" spans="1:10" s="1" customFormat="1" ht="28.8">
+    <row r="18" spans="1:10" s="1" customFormat="1" ht="30">
       <c r="A18" s="45"/>
       <c r="B18" s="32">
         <v>11</v>
@@ -8882,18 +8903,18 @@
         <v>75</v>
       </c>
       <c r="D18" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E18" s="33"/>
       <c r="F18" s="33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G18" s="37"/>
       <c r="H18" s="37"/>
       <c r="I18" s="37"/>
       <c r="J18" s="37"/>
     </row>
-    <row r="19" spans="1:10" ht="14.4">
+    <row r="19" spans="1:10" ht="15">
       <c r="A19" s="45"/>
       <c r="B19" s="29"/>
       <c r="C19" s="30" t="s">
@@ -8919,7 +8940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="28.8">
+    <row r="20" spans="1:10" ht="30">
       <c r="A20" s="45"/>
       <c r="B20" s="38">
         <v>12</v>
@@ -8928,7 +8949,7 @@
         <v>78</v>
       </c>
       <c r="D20" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E20" s="33"/>
       <c r="F20" s="33"/>
@@ -8937,7 +8958,7 @@
       <c r="I20" s="28"/>
       <c r="J20" s="28"/>
     </row>
-    <row r="21" spans="1:10" ht="28.8">
+    <row r="21" spans="1:10" ht="45">
       <c r="A21" s="45"/>
       <c r="B21" s="32">
         <v>13</v>
@@ -8946,7 +8967,7 @@
         <v>80</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E21" s="33"/>
       <c r="F21" s="33"/>
@@ -8955,7 +8976,7 @@
       <c r="I21" s="28"/>
       <c r="J21" s="28"/>
     </row>
-    <row r="22" spans="1:10" ht="14.4">
+    <row r="22" spans="1:10" ht="15">
       <c r="A22" s="45"/>
       <c r="B22" s="29"/>
       <c r="C22" s="30" t="s">
@@ -8981,7 +9002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="43.2">
+    <row r="23" spans="1:10" ht="45">
       <c r="A23" s="45"/>
       <c r="B23" s="38">
         <v>14</v>
@@ -8990,18 +9011,18 @@
         <v>72</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E23" s="33"/>
       <c r="F23" s="33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G23" s="28"/>
       <c r="H23" s="28"/>
       <c r="I23" s="28"/>
       <c r="J23" s="28"/>
     </row>
-    <row r="24" spans="1:10" ht="14.4">
+    <row r="24" spans="1:10" ht="15">
       <c r="A24" s="45"/>
       <c r="B24" s="32">
         <v>15</v>
@@ -9010,7 +9031,7 @@
         <v>35</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E24" s="33"/>
       <c r="F24" s="33"/>
@@ -9019,7 +9040,7 @@
       <c r="I24" s="28"/>
       <c r="J24" s="28"/>
     </row>
-    <row r="25" spans="1:10" ht="14.4">
+    <row r="25" spans="1:10" ht="15">
       <c r="A25" s="45"/>
       <c r="B25" s="29"/>
       <c r="C25" s="30" t="s">
@@ -9045,7 +9066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="28.8">
+    <row r="26" spans="1:10" ht="30">
       <c r="A26" s="45"/>
       <c r="B26" s="38">
         <v>16</v>
@@ -9054,16 +9075,18 @@
         <v>72</v>
       </c>
       <c r="D26" s="34" t="s">
-        <v>117</v>
-      </c>
-      <c r="E26" s="33"/>
+        <v>116</v>
+      </c>
+      <c r="E26" s="33" t="s">
+        <v>124</v>
+      </c>
       <c r="F26" s="33"/>
       <c r="G26" s="28"/>
       <c r="H26" s="28"/>
       <c r="I26" s="28"/>
       <c r="J26" s="28"/>
     </row>
-    <row r="27" spans="1:10" ht="14.4">
+    <row r="27" spans="1:10" ht="30">
       <c r="A27" s="45"/>
       <c r="B27" s="32">
         <v>17</v>
@@ -9072,16 +9095,18 @@
         <v>37</v>
       </c>
       <c r="D27" s="34" t="s">
-        <v>117</v>
-      </c>
-      <c r="E27" s="33"/>
+        <v>116</v>
+      </c>
+      <c r="E27" s="33" t="s">
+        <v>125</v>
+      </c>
       <c r="F27" s="33"/>
       <c r="G27" s="28"/>
       <c r="H27" s="28"/>
       <c r="I27" s="28"/>
       <c r="J27" s="28"/>
     </row>
-    <row r="28" spans="1:10" ht="14.4">
+    <row r="28" spans="1:10" ht="15">
       <c r="A28" s="45"/>
       <c r="B28" s="29"/>
       <c r="C28" s="30" t="s">
@@ -9107,7 +9132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="28.8">
+    <row r="29" spans="1:10" ht="30">
       <c r="A29" s="45"/>
       <c r="B29" s="38">
         <v>21</v>
@@ -9116,7 +9141,7 @@
         <v>72</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E29" s="33"/>
       <c r="F29" s="33"/>
@@ -9125,7 +9150,7 @@
       <c r="I29" s="28"/>
       <c r="J29" s="28"/>
     </row>
-    <row r="30" spans="1:10" ht="14.4">
+    <row r="30" spans="1:10" ht="15">
       <c r="A30" s="45"/>
       <c r="B30" s="32">
         <v>22</v>
@@ -9134,7 +9159,7 @@
         <v>41</v>
       </c>
       <c r="D30" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E30" s="33"/>
       <c r="F30" s="33"/>
@@ -9143,7 +9168,7 @@
       <c r="I30" s="28"/>
       <c r="J30" s="28"/>
     </row>
-    <row r="31" spans="1:10" ht="14.4">
+    <row r="31" spans="1:10" ht="15">
       <c r="A31" s="45"/>
       <c r="B31" s="32">
         <v>23</v>
@@ -9152,7 +9177,7 @@
         <v>86</v>
       </c>
       <c r="D31" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E31" s="33"/>
       <c r="F31" s="33"/>
@@ -9161,7 +9186,7 @@
       <c r="I31" s="28"/>
       <c r="J31" s="28"/>
     </row>
-    <row r="32" spans="1:10" ht="14.4">
+    <row r="32" spans="1:10" ht="15">
       <c r="A32" s="45"/>
       <c r="B32" s="32">
         <v>24</v>
@@ -9170,7 +9195,7 @@
         <v>82</v>
       </c>
       <c r="D32" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E32" s="33"/>
       <c r="F32" s="33"/>
@@ -9179,7 +9204,7 @@
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
     </row>
-    <row r="33" spans="1:10" ht="14.4">
+    <row r="33" spans="1:10" ht="15">
       <c r="A33" s="45"/>
       <c r="B33" s="32">
         <v>25</v>
@@ -9188,7 +9213,7 @@
         <v>83</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E33" s="33"/>
       <c r="F33" s="33"/>
@@ -9197,7 +9222,7 @@
       <c r="I33" s="28"/>
       <c r="J33" s="28"/>
     </row>
-    <row r="34" spans="1:10" ht="28.8">
+    <row r="34" spans="1:10" ht="45">
       <c r="A34" s="45"/>
       <c r="B34" s="32">
         <v>26</v>
@@ -9206,16 +9231,18 @@
         <v>87</v>
       </c>
       <c r="D34" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E34" s="28"/>
-      <c r="F34" s="33"/>
+      <c r="F34" s="33" t="s">
+        <v>126</v>
+      </c>
       <c r="G34" s="28"/>
       <c r="H34" s="28"/>
       <c r="I34" s="28"/>
       <c r="J34" s="28"/>
     </row>
-    <row r="35" spans="1:10" ht="28.8">
+    <row r="35" spans="1:10" ht="30">
       <c r="A35" s="45"/>
       <c r="B35" s="32">
         <v>27</v>
@@ -9224,7 +9251,7 @@
         <v>84</v>
       </c>
       <c r="D35" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E35" s="33"/>
       <c r="F35" s="33"/>
@@ -9233,7 +9260,7 @@
       <c r="I35" s="28"/>
       <c r="J35" s="28"/>
     </row>
-    <row r="36" spans="1:10" ht="28.8">
+    <row r="36" spans="1:10" ht="30">
       <c r="A36" s="45"/>
       <c r="B36" s="32">
         <v>28</v>
@@ -9242,18 +9269,18 @@
         <v>85</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E36" s="33"/>
       <c r="F36" s="33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G36" s="28"/>
       <c r="H36" s="28"/>
       <c r="I36" s="28"/>
       <c r="J36" s="28"/>
     </row>
-    <row r="37" spans="1:10" ht="14.4">
+    <row r="37" spans="1:10" ht="15">
       <c r="A37" s="43" t="s">
         <v>30</v>
       </c>
@@ -9281,7 +9308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="28.8">
+    <row r="38" spans="1:10" ht="30">
       <c r="A38" s="44"/>
       <c r="B38" s="38">
         <v>30</v>
@@ -9290,7 +9317,7 @@
         <v>73</v>
       </c>
       <c r="D38" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E38" s="33"/>
       <c r="F38" s="33"/>
@@ -9299,7 +9326,7 @@
       <c r="I38" s="28"/>
       <c r="J38" s="28"/>
     </row>
-    <row r="39" spans="1:10" ht="28.8">
+    <row r="39" spans="1:10" ht="30">
       <c r="A39" s="44"/>
       <c r="B39" s="32">
         <v>31</v>
@@ -9308,7 +9335,7 @@
         <v>38</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E39" s="33"/>
       <c r="F39" s="33"/>
@@ -9317,7 +9344,7 @@
       <c r="I39" s="28"/>
       <c r="J39" s="28"/>
     </row>
-    <row r="40" spans="1:10" ht="14.4">
+    <row r="40" spans="1:10" ht="15">
       <c r="A40" s="44"/>
       <c r="B40" s="32">
         <v>32</v>
@@ -9326,7 +9353,7 @@
         <v>39</v>
       </c>
       <c r="D40" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E40" s="33"/>
       <c r="F40" s="33"/>
@@ -9335,7 +9362,7 @@
       <c r="I40" s="28"/>
       <c r="J40" s="28"/>
     </row>
-    <row r="41" spans="1:10" ht="28.8">
+    <row r="41" spans="1:10" ht="30">
       <c r="A41" s="44"/>
       <c r="B41" s="32">
         <v>33</v>
@@ -9344,7 +9371,7 @@
         <v>42</v>
       </c>
       <c r="D41" s="34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E41" s="33"/>
       <c r="F41" s="33"/>
@@ -9379,14 +9406,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="21.109375" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" style="4" customWidth="1"/>
     <col min="3" max="3" width="68" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.6640625" customWidth="1"/>
-    <col min="6" max="6" width="32.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="6" max="6" width="32.7109375" customWidth="1"/>
     <col min="7" max="10" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9415,7 +9442,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" thickBot="1">
+    <row r="3" spans="1:10" ht="15.75" thickBot="1">
       <c r="A3" s="62" t="s">
         <v>26</v>
       </c>
@@ -9427,7 +9454,7 @@
       <c r="E3" s="66"/>
       <c r="F3" s="67"/>
     </row>
-    <row r="4" spans="1:10" ht="14.4">
+    <row r="4" spans="1:10" ht="15">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
@@ -9459,7 +9486,7 @@
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
     </row>
-    <row r="6" spans="1:10" ht="14.4">
+    <row r="6" spans="1:10" ht="15">
       <c r="A6" s="59"/>
       <c r="B6" s="5">
         <v>1</v>
@@ -9487,7 +9514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="14.4">
+    <row r="7" spans="1:10" ht="15">
       <c r="A7" s="59"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
@@ -9497,7 +9524,7 @@
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="28.8">
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="30">
       <c r="A8" s="59"/>
       <c r="B8" s="5">
         <v>2</v>
@@ -9525,7 +9552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="1" customFormat="1" ht="28.8">
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="30">
       <c r="A9" s="59"/>
       <c r="B9" s="5">
         <v>3</v>
@@ -9541,7 +9568,7 @@
       <c r="I9"/>
       <c r="J9"/>
     </row>
-    <row r="10" spans="1:10" ht="14.4">
+    <row r="10" spans="1:10" ht="15">
       <c r="A10" s="59"/>
       <c r="B10" s="9"/>
       <c r="C10" s="10" t="s">
@@ -9551,7 +9578,7 @@
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
     </row>
-    <row r="11" spans="1:10" ht="28.8">
+    <row r="11" spans="1:10" ht="30">
       <c r="A11" s="59"/>
       <c r="B11" s="20">
         <v>4</v>
@@ -9579,7 +9606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="28.8">
+    <row r="12" spans="1:10" ht="30">
       <c r="A12" s="59"/>
       <c r="B12" s="20">
         <v>5</v>
@@ -9591,7 +9618,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:10" ht="14.4">
+    <row r="13" spans="1:10" ht="30">
       <c r="A13" s="59"/>
       <c r="B13" s="5">
         <v>6</v>
@@ -9603,7 +9630,7 @@
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
     </row>
-    <row r="14" spans="1:10" ht="28.8">
+    <row r="14" spans="1:10" ht="30">
       <c r="A14" s="59"/>
       <c r="B14" s="5">
         <v>7</v>
@@ -9615,7 +9642,7 @@
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
     </row>
-    <row r="15" spans="1:10" ht="14.4">
+    <row r="15" spans="1:10" ht="15">
       <c r="A15" s="59"/>
       <c r="B15" s="9"/>
       <c r="C15" s="10" t="s">
@@ -9625,7 +9652,7 @@
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:10" ht="14.4">
+    <row r="16" spans="1:10" ht="15">
       <c r="A16" s="59"/>
       <c r="B16" s="5">
         <v>7</v>
@@ -9665,7 +9692,7 @@
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
     </row>
-    <row r="18" spans="1:10" ht="28.8">
+    <row r="18" spans="1:10" ht="30">
       <c r="A18" s="59"/>
       <c r="B18" s="5">
         <v>9</v>
@@ -9693,7 +9720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="28.8">
+    <row r="19" spans="1:10" ht="30">
       <c r="A19" s="59"/>
       <c r="B19" s="20">
         <v>10</v>
@@ -9705,7 +9732,7 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="1:10" s="1" customFormat="1" ht="28.8">
+    <row r="20" spans="1:10" s="1" customFormat="1" ht="30">
       <c r="A20" s="59"/>
       <c r="B20" s="5">
         <v>11</v>
@@ -9717,7 +9744,7 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:10" ht="28.8">
+    <row r="21" spans="1:10" ht="45">
       <c r="A21" s="59"/>
       <c r="B21" s="5">
         <v>12</v>
@@ -9729,7 +9756,7 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:10" ht="14.4">
+    <row r="22" spans="1:10" ht="15">
       <c r="A22" s="58" t="s">
         <v>19</v>
       </c>
@@ -9741,7 +9768,7 @@
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
     </row>
-    <row r="23" spans="1:10" ht="28.8">
+    <row r="23" spans="1:10" ht="30">
       <c r="A23" s="59"/>
       <c r="B23" s="5">
         <v>17</v>
@@ -9769,7 +9796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="28.8">
+    <row r="24" spans="1:10" ht="30">
       <c r="A24" s="59"/>
       <c r="B24" s="5">
         <v>18</v>
@@ -9781,7 +9808,7 @@
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
     </row>
-    <row r="25" spans="1:10" ht="28.8">
+    <row r="25" spans="1:10" ht="30">
       <c r="A25" s="59"/>
       <c r="B25" s="5">
         <v>19</v>
@@ -9793,7 +9820,7 @@
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
     </row>
-    <row r="26" spans="1:10" ht="14.4">
+    <row r="26" spans="1:10" ht="15">
       <c r="A26" s="59"/>
       <c r="B26" s="5">
         <v>21</v>
@@ -9805,7 +9832,7 @@
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:10" ht="14.4">
+    <row r="27" spans="1:10" ht="15">
       <c r="A27" s="59"/>
       <c r="B27" s="5">
         <v>22</v>
@@ -9817,7 +9844,7 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:10" ht="14.4">
+    <row r="28" spans="1:10" ht="15">
       <c r="A28" s="60" t="s">
         <v>11</v>
       </c>
@@ -9829,7 +9856,7 @@
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:10" ht="14.4">
+    <row r="29" spans="1:10" ht="15">
       <c r="A29" s="60"/>
       <c r="B29" s="5">
         <v>23</v>
@@ -9857,7 +9884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="14.4">
+    <row r="30" spans="1:10" ht="15">
       <c r="A30" s="60"/>
       <c r="B30" s="5">
         <v>24</v>
@@ -9869,7 +9896,7 @@
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
     </row>
-    <row r="31" spans="1:10" ht="28.8">
+    <row r="31" spans="1:10" ht="30">
       <c r="A31" s="60"/>
       <c r="B31" s="5">
         <v>25</v>
@@ -9881,7 +9908,7 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
     </row>
-    <row r="32" spans="1:10" ht="14.4">
+    <row r="32" spans="1:10" ht="15">
       <c r="A32" s="60"/>
       <c r="B32" s="5">
         <v>26</v>
@@ -9893,7 +9920,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:10" ht="14.4">
+    <row r="33" spans="1:10" ht="15">
       <c r="A33" s="60"/>
       <c r="B33" s="5">
         <v>27</v>
@@ -9905,7 +9932,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:10" ht="14.4">
+    <row r="34" spans="1:10" ht="15">
       <c r="A34" s="60"/>
       <c r="B34" s="5">
         <v>28</v>
@@ -9929,7 +9956,7 @@
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:10" ht="28.8">
+    <row r="36" spans="1:10" ht="30">
       <c r="A36" s="57"/>
       <c r="B36" s="5">
         <v>29</v>
@@ -9957,7 +9984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="14.4">
+    <row r="37" spans="1:10" ht="15">
       <c r="A37" s="57"/>
       <c r="B37" s="5">
         <v>30</v>
@@ -9969,7 +9996,7 @@
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
     </row>
-    <row r="38" spans="1:10" ht="28.8">
+    <row r="38" spans="1:10" ht="30">
       <c r="A38" s="57"/>
       <c r="B38" s="5">
         <v>31</v>
@@ -9981,7 +10008,7 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:10" ht="14.4">
+    <row r="39" spans="1:10" ht="15">
       <c r="A39" s="57"/>
       <c r="B39" s="9"/>
       <c r="C39" s="10" t="s">
@@ -9991,7 +10018,7 @@
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:10" ht="14.4">
+    <row r="40" spans="1:10" ht="15">
       <c r="A40" s="57"/>
       <c r="B40" s="5">
         <v>32</v>
@@ -10019,7 +10046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="14.4">
+    <row r="41" spans="1:10" ht="15">
       <c r="A41" s="57"/>
       <c r="B41" s="5">
         <v>33</v>
@@ -10060,15 +10087,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J57"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="21.109375" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="71.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.6640625" customWidth="1"/>
-    <col min="6" max="6" width="32.6640625" customWidth="1"/>
-    <col min="7" max="10" width="9.109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="71.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="6" max="6" width="32.7109375" customWidth="1"/>
+    <col min="7" max="10" width="9.140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1">
@@ -10096,7 +10123,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" thickBot="1">
+    <row r="3" spans="1:10" ht="15.75" thickBot="1">
       <c r="A3" s="62" t="s">
         <v>26</v>
       </c>
@@ -10108,7 +10135,7 @@
       <c r="E3" s="66"/>
       <c r="F3" s="67"/>
     </row>
-    <row r="4" spans="1:10" ht="14.4">
+    <row r="4" spans="1:10" ht="15">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
@@ -10140,7 +10167,7 @@
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
     </row>
-    <row r="6" spans="1:10" ht="14.4">
+    <row r="6" spans="1:10" ht="15">
       <c r="A6" s="59"/>
       <c r="B6" s="5">
         <v>1</v>
@@ -10168,7 +10195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="14.4">
+    <row r="7" spans="1:10" ht="15">
       <c r="A7" s="59"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
@@ -10178,7 +10205,7 @@
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="28.8">
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="30">
       <c r="A8" s="59"/>
       <c r="B8" s="5">
         <v>2</v>
@@ -10206,7 +10233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="14.4">
+    <row r="9" spans="1:10" ht="15">
       <c r="A9" s="59"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10" t="s">
@@ -10216,7 +10243,7 @@
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
     </row>
-    <row r="10" spans="1:10" ht="28.8">
+    <row r="10" spans="1:10" ht="30">
       <c r="A10" s="59"/>
       <c r="B10" s="5">
         <v>3</v>
@@ -10244,7 +10271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="28.8">
+    <row r="11" spans="1:10" ht="30">
       <c r="A11" s="59"/>
       <c r="B11" s="5">
         <v>4</v>
@@ -10268,7 +10295,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:10" ht="14.4">
+    <row r="13" spans="1:10" ht="15">
       <c r="A13" s="59"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10" t="s">
@@ -10278,7 +10305,7 @@
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
     </row>
-    <row r="14" spans="1:10" ht="14.4">
+    <row r="14" spans="1:10" ht="15">
       <c r="A14" s="59"/>
       <c r="B14" s="5">
         <v>6</v>
@@ -10318,7 +10345,7 @@
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:10" ht="14.4">
+    <row r="16" spans="1:10" ht="15">
       <c r="A16" s="59"/>
       <c r="B16" s="5">
         <v>8</v>
@@ -10346,7 +10373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="14.4">
+    <row r="17" spans="1:10" ht="15">
       <c r="A17" s="58" t="s">
         <v>19</v>
       </c>
@@ -10358,7 +10385,7 @@
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
     </row>
-    <row r="18" spans="1:10" ht="14.4">
+    <row r="18" spans="1:10" ht="15">
       <c r="A18" s="59"/>
       <c r="B18" s="5">
         <v>11</v>
@@ -10386,7 +10413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="28.8">
+    <row r="19" spans="1:10" ht="30">
       <c r="A19" s="59"/>
       <c r="B19" s="5">
         <v>13</v>
@@ -10398,7 +10425,7 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="1:10" ht="28.8">
+    <row r="20" spans="1:10" ht="30">
       <c r="A20" s="59"/>
       <c r="B20" s="5">
         <v>14</v>
@@ -10410,7 +10437,7 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:10" ht="14.4">
+    <row r="21" spans="1:10" ht="15">
       <c r="A21" s="59"/>
       <c r="B21" s="5">
         <v>15</v>
@@ -10422,7 +10449,7 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:10" ht="14.4">
+    <row r="22" spans="1:10" ht="15">
       <c r="A22" s="59"/>
       <c r="B22" s="5">
         <v>16</v>
@@ -10434,7 +10461,7 @@
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
     </row>
-    <row r="23" spans="1:10" ht="14.4">
+    <row r="23" spans="1:10" ht="15">
       <c r="A23" s="58" t="s">
         <v>20</v>
       </c>
@@ -10446,7 +10473,7 @@
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
     </row>
-    <row r="24" spans="1:10" ht="28.8">
+    <row r="24" spans="1:10" ht="30">
       <c r="A24" s="59"/>
       <c r="B24" s="20">
         <v>17</v>
@@ -10474,7 +10501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="28.8">
+    <row r="25" spans="1:10" ht="30">
       <c r="A25" s="59"/>
       <c r="B25" s="5">
         <v>18</v>
@@ -10486,7 +10513,7 @@
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
     </row>
-    <row r="26" spans="1:10" ht="14.4">
+    <row r="26" spans="1:10" ht="15">
       <c r="A26" s="59"/>
       <c r="B26" s="5">
         <v>19</v>
@@ -10498,7 +10525,7 @@
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" spans="1:10" ht="14.4">
+    <row r="27" spans="1:10" ht="15">
       <c r="A27" s="59"/>
       <c r="B27" s="5">
         <v>21</v>
@@ -10510,7 +10537,7 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:10" ht="14.4">
+    <row r="28" spans="1:10" ht="15">
       <c r="A28" s="59"/>
       <c r="B28" s="5">
         <v>22</v>
@@ -10522,7 +10549,7 @@
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
     </row>
-    <row r="29" spans="1:10" ht="14.4">
+    <row r="29" spans="1:10" ht="15">
       <c r="A29" s="60" t="s">
         <v>11</v>
       </c>
@@ -10534,7 +10561,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="1:10" ht="14.4">
+    <row r="30" spans="1:10" ht="15">
       <c r="A30" s="60"/>
       <c r="B30" s="5">
         <v>24</v>
@@ -10562,7 +10589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="28.8">
+    <row r="31" spans="1:10" ht="30">
       <c r="A31" s="60"/>
       <c r="B31" s="5">
         <v>26</v>
@@ -10574,7 +10601,7 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
     </row>
-    <row r="32" spans="1:10" ht="14.4">
+    <row r="32" spans="1:10" ht="15">
       <c r="A32" s="60"/>
       <c r="B32" s="5">
         <v>27</v>
@@ -10586,7 +10613,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:10" ht="14.4">
+    <row r="33" spans="1:10" ht="15">
       <c r="A33" s="60"/>
       <c r="B33" s="5">
         <v>28</v>
@@ -10598,7 +10625,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:10" ht="14.4">
+    <row r="34" spans="1:10" ht="15">
       <c r="A34" s="60"/>
       <c r="B34" s="5">
         <v>29</v>
@@ -10622,7 +10649,7 @@
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:10" ht="28.8">
+    <row r="36" spans="1:10" ht="30">
       <c r="A36" s="57"/>
       <c r="B36" s="5">
         <v>30</v>
@@ -10650,7 +10677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="14.4">
+    <row r="37" spans="1:10" ht="15">
       <c r="A37" s="57"/>
       <c r="B37" s="5">
         <v>31</v>
@@ -10662,7 +10689,7 @@
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
     </row>
-    <row r="38" spans="1:10" ht="28.8">
+    <row r="38" spans="1:10" ht="30">
       <c r="A38" s="57"/>
       <c r="B38" s="5">
         <v>32</v>
@@ -10674,7 +10701,7 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:10" ht="14.4">
+    <row r="39" spans="1:10" ht="15">
       <c r="A39" s="57"/>
       <c r="B39" s="5"/>
       <c r="C39" s="8" t="s">
@@ -10684,7 +10711,7 @@
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
     </row>
-    <row r="40" spans="1:10" ht="14.4">
+    <row r="40" spans="1:10" ht="15">
       <c r="A40" s="57"/>
       <c r="B40" s="9"/>
       <c r="C40" s="10" t="s">
@@ -10694,7 +10721,7 @@
       <c r="E40" s="12"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:10" ht="14.4">
+    <row r="41" spans="1:10" ht="15">
       <c r="A41" s="57"/>
       <c r="B41" s="5">
         <v>33</v>
@@ -10722,7 +10749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="14.4">
+    <row r="42" spans="1:10" ht="15">
       <c r="A42" s="57"/>
       <c r="B42" s="5">
         <v>34</v>
@@ -10734,47 +10761,47 @@
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
     </row>
-    <row r="51" spans="2:3" ht="14.4">
+    <row r="51" spans="2:3" ht="15">
       <c r="B51"/>
       <c r="C51"/>
     </row>
-    <row r="52" spans="2:3" ht="14.4">
+    <row r="52" spans="2:3" ht="15">
       <c r="B52"/>
       <c r="C52"/>
     </row>
-    <row r="53" spans="2:3" ht="14.4">
+    <row r="53" spans="2:3" ht="15">
       <c r="B53"/>
       <c r="C53"/>
     </row>
-    <row r="54" spans="2:3" ht="14.4">
+    <row r="54" spans="2:3" ht="15">
       <c r="B54"/>
       <c r="C54"/>
     </row>
-    <row r="55" spans="2:3" ht="14.4">
+    <row r="55" spans="2:3" ht="15">
       <c r="B55"/>
       <c r="C55"/>
     </row>
-    <row r="56" spans="2:3" ht="14.4">
+    <row r="56" spans="2:3" ht="15">
       <c r="B56"/>
       <c r="C56"/>
     </row>
-    <row r="57" spans="2:3" ht="14.4">
+    <row r="57" spans="2:3" ht="15">
       <c r="B57"/>
       <c r="C57"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:F3"/>
     <mergeCell ref="A5:A14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A17:A22"/>
     <mergeCell ref="A29:A34"/>
     <mergeCell ref="A35:A42"/>
     <mergeCell ref="A23:A28"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:F3"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23 D15 D17 D40 D35 D29" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -10792,14 +10819,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J58"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="21.109375" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="71.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.6640625" customWidth="1"/>
-    <col min="6" max="6" width="32.6640625" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="71.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="6" max="6" width="32.7109375" customWidth="1"/>
     <col min="7" max="10" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10828,7 +10855,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" thickBot="1">
+    <row r="3" spans="1:10" ht="15.75" thickBot="1">
       <c r="A3" s="62" t="s">
         <v>26</v>
       </c>
@@ -10840,7 +10867,7 @@
       <c r="E3" s="66"/>
       <c r="F3" s="67"/>
     </row>
-    <row r="4" spans="1:10" ht="14.4">
+    <row r="4" spans="1:10" ht="15">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
@@ -10872,7 +10899,7 @@
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
     </row>
-    <row r="6" spans="1:10" ht="14.4">
+    <row r="6" spans="1:10" ht="15">
       <c r="A6" s="59"/>
       <c r="B6" s="5">
         <v>1</v>
@@ -10900,7 +10927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="14.4">
+    <row r="7" spans="1:10" ht="15">
       <c r="A7" s="59"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
@@ -10910,7 +10937,7 @@
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="28.8">
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="30">
       <c r="A8" s="59"/>
       <c r="B8" s="5">
         <v>2</v>
@@ -10938,7 +10965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="14.4">
+    <row r="9" spans="1:10" ht="15">
       <c r="A9" s="59"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10" t="s">
@@ -10948,7 +10975,7 @@
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
     </row>
-    <row r="10" spans="1:10" ht="28.8">
+    <row r="10" spans="1:10" ht="30">
       <c r="A10" s="59"/>
       <c r="B10" s="5">
         <v>3</v>
@@ -10976,7 +11003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="28.8">
+    <row r="11" spans="1:10" ht="30">
       <c r="A11" s="59"/>
       <c r="B11" s="5">
         <v>4</v>
@@ -11000,7 +11027,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
     </row>
-    <row r="13" spans="1:10" ht="14.4">
+    <row r="13" spans="1:10" ht="15">
       <c r="A13" s="59"/>
       <c r="B13" s="9"/>
       <c r="C13" s="10" t="s">
@@ -11010,7 +11037,7 @@
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
     </row>
-    <row r="14" spans="1:10" ht="14.4">
+    <row r="14" spans="1:10" ht="15">
       <c r="A14" s="59"/>
       <c r="B14" s="5">
         <v>6</v>
@@ -11050,7 +11077,7 @@
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:10" ht="14.4">
+    <row r="16" spans="1:10" ht="15">
       <c r="A16" s="59"/>
       <c r="B16" s="5">
         <v>8</v>
@@ -11090,7 +11117,7 @@
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
     </row>
-    <row r="18" spans="1:10" ht="14.4">
+    <row r="18" spans="1:10" ht="30">
       <c r="A18" s="59"/>
       <c r="B18" s="5">
         <v>9</v>
@@ -11118,7 +11145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="14.4">
+    <row r="19" spans="1:10" ht="15">
       <c r="A19" s="59"/>
       <c r="B19" s="5">
         <v>10</v>
@@ -11130,7 +11157,7 @@
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
     </row>
-    <row r="20" spans="1:10" ht="28.8">
+    <row r="20" spans="1:10" ht="30">
       <c r="A20" s="59"/>
       <c r="B20" s="5">
         <v>11</v>
@@ -11142,7 +11169,7 @@
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
     </row>
-    <row r="21" spans="1:10" ht="14.4">
+    <row r="21" spans="1:10" ht="15">
       <c r="A21" s="68"/>
       <c r="B21" s="5">
         <v>13</v>
@@ -11154,7 +11181,7 @@
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
     </row>
-    <row r="22" spans="1:10" ht="14.4">
+    <row r="22" spans="1:10" ht="15">
       <c r="A22" s="58" t="s">
         <v>20</v>
       </c>
@@ -11166,7 +11193,7 @@
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
     </row>
-    <row r="23" spans="1:10" ht="14.4">
+    <row r="23" spans="1:10" ht="15">
       <c r="A23" s="59"/>
       <c r="B23" s="5">
         <v>14</v>
@@ -11194,7 +11221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="14.4">
+    <row r="24" spans="1:10" ht="15">
       <c r="A24" s="59"/>
       <c r="B24" s="5">
         <v>15</v>
@@ -11218,7 +11245,7 @@
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="1:10" s="1" customFormat="1" ht="28.8">
+    <row r="26" spans="1:10" s="1" customFormat="1" ht="30">
       <c r="A26" s="59"/>
       <c r="B26" s="20">
         <v>24</v>
@@ -11246,7 +11273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="1" customFormat="1" ht="43.2">
+    <row r="27" spans="1:10" s="1" customFormat="1" ht="45">
       <c r="A27" s="59"/>
       <c r="B27" s="5">
         <v>25</v>
@@ -11258,7 +11285,7 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
     </row>
-    <row r="28" spans="1:10" ht="14.4">
+    <row r="28" spans="1:10" ht="15">
       <c r="A28" s="59"/>
       <c r="B28" s="9"/>
       <c r="C28" s="10" t="s">
@@ -11268,7 +11295,7 @@
       <c r="E28" s="12"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:10" ht="28.8">
+    <row r="29" spans="1:10" ht="30">
       <c r="A29" s="59"/>
       <c r="B29" s="20">
         <v>26</v>
@@ -11296,7 +11323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="14.4">
+    <row r="30" spans="1:10" ht="15">
       <c r="A30" s="60" t="s">
         <v>11</v>
       </c>
@@ -11308,7 +11335,7 @@
       <c r="E30" s="12"/>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:10" ht="14.4">
+    <row r="31" spans="1:10" ht="15">
       <c r="A31" s="60"/>
       <c r="B31" s="5">
         <v>19</v>
@@ -11336,7 +11363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="28.8">
+    <row r="32" spans="1:10" ht="30">
       <c r="A32" s="60"/>
       <c r="B32" s="5">
         <v>20</v>
@@ -11348,7 +11375,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33" spans="1:10" ht="14.4">
+    <row r="33" spans="1:10" ht="15">
       <c r="A33" s="60"/>
       <c r="B33" s="5">
         <v>21</v>
@@ -11360,7 +11387,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
     </row>
-    <row r="34" spans="1:10" ht="14.4">
+    <row r="34" spans="1:10" ht="15">
       <c r="A34" s="60"/>
       <c r="B34" s="5">
         <v>24</v>
@@ -11372,7 +11399,7 @@
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
     </row>
-    <row r="35" spans="1:10" ht="14.4">
+    <row r="35" spans="1:10" ht="15">
       <c r="A35" s="60"/>
       <c r="B35" s="5">
         <v>25</v>
@@ -11396,7 +11423,7 @@
       <c r="E36" s="12"/>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:10" ht="28.8">
+    <row r="37" spans="1:10" ht="30">
       <c r="A37" s="57"/>
       <c r="B37" s="5">
         <v>26</v>
@@ -11424,7 +11451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="14.4">
+    <row r="38" spans="1:10" ht="15">
       <c r="A38" s="57"/>
       <c r="B38" s="5">
         <v>27</v>
@@ -11436,7 +11463,7 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39" spans="1:10" ht="28.8">
+    <row r="39" spans="1:10" ht="30">
       <c r="A39" s="57"/>
       <c r="B39" s="5">
         <v>28</v>
@@ -11448,7 +11475,7 @@
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
     </row>
-    <row r="40" spans="1:10" ht="14.4">
+    <row r="40" spans="1:10" ht="15">
       <c r="A40" s="57"/>
       <c r="B40" s="5"/>
       <c r="C40" s="8" t="s">
@@ -11458,7 +11485,7 @@
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
     </row>
-    <row r="41" spans="1:10" ht="14.4">
+    <row r="41" spans="1:10" ht="15">
       <c r="A41" s="57"/>
       <c r="B41" s="9"/>
       <c r="C41" s="10" t="s">
@@ -11468,7 +11495,7 @@
       <c r="E41" s="12"/>
       <c r="F41" s="12"/>
     </row>
-    <row r="42" spans="1:10" ht="14.4">
+    <row r="42" spans="1:10" ht="15">
       <c r="A42" s="57"/>
       <c r="B42" s="5">
         <v>29</v>
@@ -11496,7 +11523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="14.4">
+    <row r="43" spans="1:10" ht="15">
       <c r="A43" s="57"/>
       <c r="B43" s="5">
         <v>30</v>
@@ -11508,41 +11535,36 @@
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
     </row>
-    <row r="52" spans="2:3" ht="14.4">
+    <row r="52" spans="2:3" ht="15">
       <c r="B52"/>
       <c r="C52"/>
     </row>
-    <row r="53" spans="2:3" ht="14.4">
+    <row r="53" spans="2:3" ht="15">
       <c r="B53"/>
       <c r="C53"/>
     </row>
-    <row r="54" spans="2:3" ht="14.4">
+    <row r="54" spans="2:3" ht="15">
       <c r="B54"/>
       <c r="C54"/>
     </row>
-    <row r="55" spans="2:3" ht="14.4">
+    <row r="55" spans="2:3" ht="15">
       <c r="B55"/>
       <c r="C55"/>
     </row>
-    <row r="56" spans="2:3" ht="14.4">
+    <row r="56" spans="2:3" ht="15">
       <c r="B56"/>
       <c r="C56"/>
     </row>
-    <row r="57" spans="2:3" ht="14.4">
+    <row r="57" spans="2:3" ht="15">
       <c r="B57"/>
       <c r="C57"/>
     </row>
-    <row r="58" spans="2:3" ht="14.4">
+    <row r="58" spans="2:3" ht="15">
       <c r="B58"/>
       <c r="C58"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A30:A35"/>
-    <mergeCell ref="A36:A43"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A25:A29"/>
     <mergeCell ref="A5:A14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A1:F1"/>
@@ -11550,6 +11572,11 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A30:A35"/>
+    <mergeCell ref="A36:A43"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A25:A29"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25 D17 D15 D22 D41 D36 D30 D28" xr:uid="{00000000-0002-0000-0400-000000000000}">

--- a/6.Gerenciamento de Projeto/CARREGAJA - Checklist de Projeto.xlsx
+++ b/6.Gerenciamento de Projeto/CARREGAJA - Checklist de Projeto.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077A368B-FBA1-43EB-B3C8-DAD3BA2D068B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10FDBE1-5024-4C05-929B-C2422D6F8954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="960" windowWidth="21600" windowHeight="11235" tabRatio="666" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="666" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Indicadores" sheetId="6" r:id="rId1"/>
@@ -713,7 +713,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="114">
   <si>
     <t>Ambiente</t>
   </si>
@@ -1055,45 +1055,6 @@
   </si>
   <si>
     <t>Foram realizados os testes de aceitação por parte do usuário final?</t>
-  </si>
-  <si>
-    <t>Henrique de Almeida Marangoni Inacio (Scrum Master)</t>
-  </si>
-  <si>
-    <t>Sim</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Aprovado pelo Product Owner, que atua como representante do cliente (RE-16).</t>
-  </si>
-  <si>
-    <t>O Glossário é a subseção 1.3 do Visão, onde o template o posiciona. O SpinOff não prevê template autônomo para ele.</t>
-  </si>
-  <si>
-    <t>26/09/2026</t>
-  </si>
-  <si>
-    <t>O Documento de Requisitos, não previsto no SpinOff, tem template próprio: 1.Requisitos/Template - Documento de Requisitos.dotx.</t>
-  </si>
-  <si>
-    <t>Visão reduzido a uma visão geral na versão 4.0, após a apresentação da Iniciação; o detalhamento passou ao Documento de Requisitos.</t>
-  </si>
-  <si>
-    <t>Modelo mantido em CARREGAJA - Modelos de Análise e Design.asta, no formato do Template - Modelos Analise e Design do SpinOff, com os dois atores, os doze casos de uso UC01–UC12, cada um com descrição, e as relações de inclusão.</t>
-  </si>
-  <si>
-    <t>Protótipo não produzido: é saída de Detalhar Requisitos, da Elaboração.</t>
-  </si>
-  <si>
-    <t>Não houve reunião de levantamento a registrar: o projeto não dispõe de cliente externo (RE-16).</t>
-  </si>
-  <si>
-    <t>Não se aplica pelo mesmo motivo do item 16 (RE-16).</t>
-  </si>
-  <si>
-    <t>Plano de entregas com 7 sprints, o número calculado na aba Planejamento da PCP (6,13, arredondado para cima).</t>
   </si>
 </sst>
 </file>
@@ -1724,7 +1685,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -1956,19 +1917,19 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.8</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -1980,10 +1941,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -2301,7 +2262,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2310,7 +2271,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -7455,9 +7416,9 @@
       <c r="A3" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="18" t="e">
         <f>'Ver-Iniciação1'!$F$2</f>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7550,21 +7511,21 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22">
+      <c r="B2" s="22" t="e">
         <f>('Ver-Iniciação1'!$G$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
-        <v>1</v>
-      </c>
-      <c r="C2" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C2" s="22" t="e">
         <f>('Ver-Iniciação1'!$H$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
-        <v>0</v>
-      </c>
-      <c r="D2" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D2" s="22" t="e">
         <f>('Ver-Iniciação1'!$I$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
-        <v>0</v>
-      </c>
-      <c r="E2" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E2" s="22" t="e">
         <f>('Ver-Iniciação1'!$J$5/SUM('Ver-Iniciação1'!$G$5:'Ver-Iniciação1'!$J$5))</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N2" t="s">
         <v>2</v>
@@ -7590,21 +7551,21 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="22">
+      <c r="B3" s="22" t="e">
         <f>('Ver-Iniciação1'!$G$7/SUM('Ver-Iniciação1'!$G$7:'Ver-Iniciação1'!$J$7))</f>
-        <v>1</v>
-      </c>
-      <c r="C3" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C3" s="22" t="e">
         <f>('Ver-Iniciação1'!$H$7/SUM('Ver-Iniciação1'!$G$7:'Ver-Iniciação1'!$J$7))</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D3" s="22" t="e">
         <f>('Ver-Iniciação1'!$I$7/SUM('Ver-Iniciação1'!$G$7:'Ver-Iniciação1'!$J$7))</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E3" s="22" t="e">
         <f>('Ver-Iniciação1'!$J$7/SUM('Ver-Iniciação1'!$G$7:'Ver-Iniciação1'!$J$7))</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N3" t="s">
         <v>3</v>
@@ -7630,21 +7591,21 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="22">
+      <c r="B4" s="22" t="e">
         <f>('Ver-Iniciação1'!$G$13/SUM('Ver-Iniciação1'!$G$13:'Ver-Iniciação1'!$J$13))</f>
-        <v>0.8</v>
-      </c>
-      <c r="C4" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C4" s="22" t="e">
         <f>('Ver-Iniciação1'!$H$13/SUM('Ver-Iniciação1'!$G$13:'Ver-Iniciação1'!$J$13))</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D4" s="22" t="e">
         <f>('Ver-Iniciação1'!$I$13/SUM('Ver-Iniciação1'!$G$13:'Ver-Iniciação1'!$J$13))</f>
-        <v>0</v>
-      </c>
-      <c r="E4" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E4" s="22" t="e">
         <f>('Ver-Iniciação1'!$J$13/SUM('Ver-Iniciação1'!$G$13:'Ver-Iniciação1'!$J$13))</f>
-        <v>0.2</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N4" t="s">
         <v>14</v>
@@ -7670,21 +7631,21 @@
       <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="22" t="e">
         <f>('Ver-Iniciação1'!$G$19/SUM('Ver-Iniciação1'!$G$19:'Ver-Iniciação1'!$J$19))</f>
-        <v>1</v>
-      </c>
-      <c r="C5" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C5" s="22" t="e">
         <f>('Ver-Iniciação1'!$H$19/SUM('Ver-Iniciação1'!$G$19:'Ver-Iniciação1'!$J$19))</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D5" s="22" t="e">
         <f>('Ver-Iniciação1'!$I$19/SUM('Ver-Iniciação1'!$G$19:'Ver-Iniciação1'!$J$19))</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E5" s="22" t="e">
         <f>('Ver-Iniciação1'!$J$19/SUM('Ver-Iniciação1'!$G$19:'Ver-Iniciação1'!$J$19))</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N5" t="s">
         <v>4</v>
@@ -7710,21 +7671,21 @@
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="22" t="e">
         <f>('Ver-Iniciação1'!$G$22/SUM('Ver-Iniciação1'!$G$22:'Ver-Iniciação1'!$J$22))</f>
-        <v>1</v>
-      </c>
-      <c r="C6" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C6" s="22" t="e">
         <f>('Ver-Iniciação1'!$H$22/SUM('Ver-Iniciação1'!$G$22:'Ver-Iniciação1'!$J$22))</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D6" s="22" t="e">
         <f>('Ver-Iniciação1'!$I$22/SUM('Ver-Iniciação1'!$G$22:'Ver-Iniciação1'!$J$22))</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E6" s="22" t="e">
         <f>('Ver-Iniciação1'!$J$22/SUM('Ver-Iniciação1'!$G$22:'Ver-Iniciação1'!$J$22))</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N6" t="s">
         <v>36</v>
@@ -7750,21 +7711,21 @@
       <c r="A7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="22" t="e">
         <f>('Ver-Iniciação1'!$G$25/SUM('Ver-Iniciação1'!$G$25:'Ver-Iniciação1'!$J$25))</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C7" s="22" t="e">
         <f>('Ver-Iniciação1'!$H$25/SUM('Ver-Iniciação1'!$G$25:'Ver-Iniciação1'!$J$25))</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D7" s="22" t="e">
         <f>('Ver-Iniciação1'!$I$25/SUM('Ver-Iniciação1'!$G$25:'Ver-Iniciação1'!$J$25))</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E7" s="22" t="e">
         <f>('Ver-Iniciação1'!$J$25/SUM('Ver-Iniciação1'!$G$25:'Ver-Iniciação1'!$J$25))</f>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N7" t="s">
         <v>5</v>
@@ -7870,21 +7831,21 @@
       <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="22" t="e">
         <f>('Ver-Iniciação1'!$G$28/SUM('Ver-Iniciação1'!$G$28:'Ver-Iniciação1'!$J$28))</f>
-        <v>1</v>
-      </c>
-      <c r="C10" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C10" s="22" t="e">
         <f>('Ver-Iniciação1'!$H$28/SUM('Ver-Iniciação1'!$G$28:'Ver-Iniciação1'!$J$28))</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D10" s="22" t="e">
         <f>('Ver-Iniciação1'!$I$28/SUM('Ver-Iniciação1'!$G$28:'Ver-Iniciação1'!$J$28))</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E10" s="22" t="e">
         <f>('Ver-Iniciação1'!$J$28/SUM('Ver-Iniciação1'!$G$28:'Ver-Iniciação1'!$J$28))</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N10" t="s">
         <v>13</v>
@@ -7910,21 +7871,21 @@
       <c r="A11" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="22" t="e">
         <f>('Ver-Iniciação1'!$G$37/SUM('Ver-Iniciação1'!$G$37:'Ver-Iniciação1'!$J$37))</f>
-        <v>1</v>
-      </c>
-      <c r="C11" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C11" s="22" t="e">
         <f>('Ver-Iniciação1'!$H$37/SUM('Ver-Iniciação1'!$G$37:'Ver-Iniciação1'!$J$37))</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D11" s="22" t="e">
         <f>('Ver-Iniciação1'!$I$37/SUM('Ver-Iniciação1'!$G$37:'Ver-Iniciação1'!$J$37))</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E11" s="22" t="e">
         <f>('Ver-Iniciação1'!$J$37/SUM('Ver-Iniciação1'!$G$37:'Ver-Iniciação1'!$J$37))</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N11" t="s">
         <v>56</v>
@@ -8566,16 +8527,14 @@
         <v>25</v>
       </c>
       <c r="B2" s="47"/>
-      <c r="C2" s="40" t="s">
-        <v>119</v>
-      </c>
+      <c r="C2" s="40"/>
       <c r="D2" s="53" t="s">
         <v>44</v>
       </c>
       <c r="E2" s="54"/>
-      <c r="F2" s="42">
+      <c r="F2" s="42" t="e">
         <f>COUNTIF(D5:D41,"Sim")/(COUNTA(D5:D41)-COUNTIF(D5:D41,"NA"))</f>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G2" s="39"/>
       <c r="H2" s="39"/>
@@ -8587,9 +8546,7 @@
         <v>26</v>
       </c>
       <c r="B3" s="47"/>
-      <c r="C3" s="41" t="s">
-        <v>114</v>
-      </c>
+      <c r="C3" s="41"/>
       <c r="D3" s="50" t="s">
         <v>43</v>
       </c>
@@ -8637,7 +8594,7 @@
       <c r="F5" s="31"/>
       <c r="G5" s="28">
         <f>COUNTIF(D6,"Sim")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="28">
         <f>COUNTIF(D6,"Parcialmente")</f>
@@ -8652,7 +8609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="60">
+    <row r="6" spans="1:10" ht="15">
       <c r="A6" s="49"/>
       <c r="B6" s="32">
         <v>1</v>
@@ -8660,13 +8617,9 @@
       <c r="C6" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D6" s="34"/>
       <c r="E6" s="33"/>
-      <c r="F6" s="33" t="s">
-        <v>120</v>
-      </c>
+      <c r="F6" s="33"/>
       <c r="G6" s="28"/>
       <c r="H6" s="28"/>
       <c r="I6" s="28"/>
@@ -8685,7 +8638,7 @@
       <c r="F7" s="31"/>
       <c r="G7" s="28">
         <f>COUNTIF(D8:D12,"Sim")</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H7" s="28">
         <f>COUNTIF(D8:D12,"Parcialmente")</f>
@@ -8708,9 +8661,7 @@
       <c r="C8" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D8" s="34"/>
       <c r="E8" s="33"/>
       <c r="F8" s="33"/>
       <c r="G8" s="28"/>
@@ -8726,9 +8677,7 @@
       <c r="C9" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D9" s="34"/>
       <c r="E9" s="33"/>
       <c r="F9" s="33"/>
       <c r="G9" s="28"/>
@@ -8744,9 +8693,7 @@
       <c r="C10" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D10" s="34"/>
       <c r="E10" s="33"/>
       <c r="F10" s="33"/>
       <c r="G10" s="28"/>
@@ -8754,7 +8701,7 @@
       <c r="I10" s="28"/>
       <c r="J10" s="28"/>
     </row>
-    <row r="11" spans="1:10" s="1" customFormat="1" ht="45">
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="15">
       <c r="A11" s="45"/>
       <c r="B11" s="32">
         <v>5</v>
@@ -8762,13 +8709,9 @@
       <c r="C11" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D11" s="34"/>
       <c r="E11" s="33"/>
-      <c r="F11" s="33" t="s">
-        <v>121</v>
-      </c>
+      <c r="F11" s="33"/>
       <c r="G11" s="37"/>
       <c r="H11" s="37"/>
       <c r="I11" s="37"/>
@@ -8782,9 +8725,7 @@
       <c r="C12" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D12" s="34"/>
       <c r="E12" s="33"/>
       <c r="F12" s="33"/>
       <c r="G12" s="28"/>
@@ -8803,7 +8744,7 @@
       <c r="F13" s="31"/>
       <c r="G13" s="28">
         <f>COUNTIF(D14:D18,"Sim")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H13" s="28">
         <f>COUNTIF(D14:D18,"Parcialmente")</f>
@@ -8815,10 +8756,10 @@
       </c>
       <c r="J13" s="28">
         <f>COUNTIF(D14:D18,"NA")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="30">
       <c r="A14" s="45"/>
       <c r="B14" s="38">
         <v>7</v>
@@ -8826,13 +8767,9 @@
       <c r="C14" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D14" s="34"/>
       <c r="E14" s="33"/>
-      <c r="F14" s="33" t="s">
-        <v>122</v>
-      </c>
+      <c r="F14" s="33"/>
       <c r="G14" s="28"/>
       <c r="H14" s="28"/>
       <c r="I14" s="28"/>
@@ -8846,9 +8783,7 @@
       <c r="C15" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D15" s="34"/>
       <c r="E15" s="33"/>
       <c r="F15" s="33"/>
       <c r="G15" s="37"/>
@@ -8864,9 +8799,7 @@
       <c r="C16" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D16" s="34"/>
       <c r="E16" s="33"/>
       <c r="F16" s="33"/>
       <c r="G16" s="37"/>
@@ -8882,19 +8815,15 @@
       <c r="C17" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>123</v>
-      </c>
+      <c r="D17" s="34"/>
+      <c r="E17" s="33"/>
       <c r="F17" s="33"/>
       <c r="G17" s="37"/>
       <c r="H17" s="37"/>
       <c r="I17" s="37"/>
       <c r="J17" s="37"/>
     </row>
-    <row r="18" spans="1:10" s="1" customFormat="1" ht="30">
+    <row r="18" spans="1:10" s="1" customFormat="1" ht="15">
       <c r="A18" s="45"/>
       <c r="B18" s="32">
         <v>11</v>
@@ -8902,13 +8831,9 @@
       <c r="C18" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D18" s="34"/>
       <c r="E18" s="33"/>
-      <c r="F18" s="33" t="s">
-        <v>117</v>
-      </c>
+      <c r="F18" s="33"/>
       <c r="G18" s="37"/>
       <c r="H18" s="37"/>
       <c r="I18" s="37"/>
@@ -8925,7 +8850,7 @@
       <c r="F19" s="31"/>
       <c r="G19" s="28">
         <f>COUNTIF(D20:D21,"Sim")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19" s="28">
         <f>COUNTIF(D20:D21,"Parcialmente")</f>
@@ -8948,9 +8873,7 @@
       <c r="C20" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="D20" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D20" s="34"/>
       <c r="E20" s="33"/>
       <c r="F20" s="33"/>
       <c r="G20" s="28"/>
@@ -8966,9 +8889,7 @@
       <c r="C21" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="D21" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D21" s="34"/>
       <c r="E21" s="33"/>
       <c r="F21" s="33"/>
       <c r="G21" s="28"/>
@@ -8987,7 +8908,7 @@
       <c r="F22" s="31"/>
       <c r="G22" s="28">
         <f>COUNTIF(D23:D24,"Sim")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22" s="28">
         <f>COUNTIF(D23:D24,"Parcialmente")</f>
@@ -9002,7 +8923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="45">
+    <row r="23" spans="1:10" ht="30">
       <c r="A23" s="45"/>
       <c r="B23" s="38">
         <v>14</v>
@@ -9010,13 +8931,9 @@
       <c r="C23" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D23" s="34"/>
       <c r="E23" s="33"/>
-      <c r="F23" s="33" t="s">
-        <v>118</v>
-      </c>
+      <c r="F23" s="33"/>
       <c r="G23" s="28"/>
       <c r="H23" s="28"/>
       <c r="I23" s="28"/>
@@ -9030,9 +8947,7 @@
       <c r="C24" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D24" s="34"/>
       <c r="E24" s="33"/>
       <c r="F24" s="33"/>
       <c r="G24" s="28"/>
@@ -9063,7 +8978,7 @@
       </c>
       <c r="J25" s="28">
         <f>COUNTIF(D26:D27,"NA")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="30">
@@ -9074,19 +8989,15 @@
       <c r="C26" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" s="33" t="s">
-        <v>124</v>
-      </c>
+      <c r="D26" s="34"/>
+      <c r="E26" s="33"/>
       <c r="F26" s="33"/>
       <c r="G26" s="28"/>
       <c r="H26" s="28"/>
       <c r="I26" s="28"/>
       <c r="J26" s="28"/>
     </row>
-    <row r="27" spans="1:10" ht="30">
+    <row r="27" spans="1:10" ht="15">
       <c r="A27" s="45"/>
       <c r="B27" s="32">
         <v>17</v>
@@ -9094,12 +9005,8 @@
       <c r="C27" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27" s="33" t="s">
-        <v>125</v>
-      </c>
+      <c r="D27" s="34"/>
+      <c r="E27" s="33"/>
       <c r="F27" s="33"/>
       <c r="G27" s="28"/>
       <c r="H27" s="28"/>
@@ -9117,7 +9024,7 @@
       <c r="F28" s="31"/>
       <c r="G28" s="28">
         <f>COUNTIF(D29:D36,"Sim")</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H28" s="28">
         <f>COUNTIF(D29:D36,"Parcialmente")</f>
@@ -9140,9 +9047,7 @@
       <c r="C29" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D29" s="34"/>
       <c r="E29" s="33"/>
       <c r="F29" s="33"/>
       <c r="G29" s="28"/>
@@ -9158,9 +9063,7 @@
       <c r="C30" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D30" s="34"/>
       <c r="E30" s="33"/>
       <c r="F30" s="33"/>
       <c r="G30" s="28"/>
@@ -9176,9 +9079,7 @@
       <c r="C31" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D31" s="34"/>
       <c r="E31" s="33"/>
       <c r="F31" s="33"/>
       <c r="G31" s="28"/>
@@ -9194,9 +9095,7 @@
       <c r="C32" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="D32" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D32" s="34"/>
       <c r="E32" s="33"/>
       <c r="F32" s="33"/>
       <c r="G32" s="28"/>
@@ -9212,9 +9111,7 @@
       <c r="C33" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="D33" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D33" s="34"/>
       <c r="E33" s="33"/>
       <c r="F33" s="33"/>
       <c r="G33" s="28"/>
@@ -9222,7 +9119,7 @@
       <c r="I33" s="28"/>
       <c r="J33" s="28"/>
     </row>
-    <row r="34" spans="1:10" ht="45">
+    <row r="34" spans="1:10" ht="30">
       <c r="A34" s="45"/>
       <c r="B34" s="32">
         <v>26</v>
@@ -9230,13 +9127,9 @@
       <c r="C34" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="D34" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D34" s="34"/>
       <c r="E34" s="28"/>
-      <c r="F34" s="33" t="s">
-        <v>126</v>
-      </c>
+      <c r="F34" s="33"/>
       <c r="G34" s="28"/>
       <c r="H34" s="28"/>
       <c r="I34" s="28"/>
@@ -9250,9 +9143,7 @@
       <c r="C35" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D35" s="34"/>
       <c r="E35" s="33"/>
       <c r="F35" s="33"/>
       <c r="G35" s="28"/>
@@ -9260,7 +9151,7 @@
       <c r="I35" s="28"/>
       <c r="J35" s="28"/>
     </row>
-    <row r="36" spans="1:10" ht="30">
+    <row r="36" spans="1:10" ht="15">
       <c r="A36" s="45"/>
       <c r="B36" s="32">
         <v>28</v>
@@ -9268,13 +9159,9 @@
       <c r="C36" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="D36" s="33" t="s">
-        <v>115</v>
-      </c>
+      <c r="D36" s="33"/>
       <c r="E36" s="33"/>
-      <c r="F36" s="33" t="s">
-        <v>117</v>
-      </c>
+      <c r="F36" s="33"/>
       <c r="G36" s="28"/>
       <c r="H36" s="28"/>
       <c r="I36" s="28"/>
@@ -9293,7 +9180,7 @@
       <c r="F37" s="31"/>
       <c r="G37" s="28">
         <f>COUNTIF(D38:D41,"Sim")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H37" s="28">
         <f>COUNTIF(D38:D41,"Parcialmente")</f>
@@ -9316,9 +9203,7 @@
       <c r="C38" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="D38" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D38" s="34"/>
       <c r="E38" s="33"/>
       <c r="F38" s="33"/>
       <c r="G38" s="28"/>
@@ -9334,9 +9219,7 @@
       <c r="C39" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="D39" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D39" s="34"/>
       <c r="E39" s="33"/>
       <c r="F39" s="33"/>
       <c r="G39" s="28"/>
@@ -9352,9 +9235,7 @@
       <c r="C40" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="D40" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D40" s="34"/>
       <c r="E40" s="33"/>
       <c r="F40" s="33"/>
       <c r="G40" s="28"/>
@@ -9370,9 +9251,7 @@
       <c r="C41" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="34" t="s">
-        <v>115</v>
-      </c>
+      <c r="D41" s="34"/>
       <c r="E41" s="33"/>
       <c r="F41" s="33"/>
       <c r="G41" s="28"/>
@@ -10791,17 +10670,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:F3"/>
     <mergeCell ref="A5:A14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A17:A22"/>
     <mergeCell ref="A29:A34"/>
     <mergeCell ref="A35:A42"/>
     <mergeCell ref="A23:A28"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:F3"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23 D15 D17 D40 D35 D29" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -11565,6 +11444,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A30:A35"/>
+    <mergeCell ref="A36:A43"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A25:A29"/>
     <mergeCell ref="A5:A14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A1:F1"/>
@@ -11572,11 +11456,6 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A30:A35"/>
-    <mergeCell ref="A36:A43"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A25:A29"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25 D17 D15 D22 D41 D36 D30 D28" xr:uid="{00000000-0002-0000-0400-000000000000}">
